--- a/tcmb_kur_verileri.xlsx
+++ b/tcmb_kur_verileri.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="534">
   <si>
     <t xml:space="preserve">Tarih</t>
   </si>
@@ -1580,6 +1580,48 @@
   </si>
   <si>
     <t xml:space="preserve">01-06-2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02-06-2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">03-06-2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04-06-2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05-06-2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06-06-2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07-06-2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">08-06-2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09-06-2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10-06-2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11-06-2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12-06-2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13-06-2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14-06-2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15-06-2026</t>
   </si>
 </sst>
 </file>
@@ -1669,7 +1711,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1690,10 +1732,6 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1707,6 +1745,15 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -1826,7 +1873,7 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.25"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="8.47"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="8.47"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="8.47"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1841,13 +1888,13 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="0"/>
+      <c r="B2" s="1"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="5" t="n">
@@ -1858,7 +1905,7 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="5" t="n">
@@ -1869,19 +1916,19 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="0"/>
+      <c r="B5" s="1"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="0"/>
+      <c r="B6" s="1"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B7" s="5" t="n">
@@ -1892,7 +1939,7 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B8" s="5" t="n">
@@ -1903,7 +1950,7 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B9" s="5" t="n">
@@ -1914,7 +1961,7 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B10" s="5" t="n">
@@ -1925,7 +1972,7 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B11" s="5" t="n">
@@ -1936,19 +1983,19 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="0"/>
+      <c r="B12" s="1"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="0"/>
+      <c r="B13" s="1"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="A14" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B14" s="5" t="n">
@@ -1959,7 +2006,7 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+      <c r="A15" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B15" s="5" t="n">
@@ -1970,7 +2017,7 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+      <c r="A16" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B16" s="5" t="n">
@@ -1981,7 +2028,7 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+      <c r="A17" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B17" s="5" t="n">
@@ -1992,7 +2039,7 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+      <c r="A18" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B18" s="5" t="n">
@@ -2003,19 +2050,19 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+      <c r="A19" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B19" s="0"/>
+      <c r="B19" s="1"/>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+      <c r="A20" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B20" s="0"/>
+      <c r="B20" s="1"/>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
+      <c r="A21" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B21" s="5" t="n">
@@ -2026,7 +2073,7 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
+      <c r="A22" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B22" s="5" t="n">
@@ -2037,7 +2084,7 @@
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
+      <c r="A23" s="1" t="s">
         <v>24</v>
       </c>
       <c r="B23" s="5" t="n">
@@ -2048,7 +2095,7 @@
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
+      <c r="A24" s="1" t="s">
         <v>25</v>
       </c>
       <c r="B24" s="5" t="n">
@@ -2059,7 +2106,7 @@
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
+      <c r="A25" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B25" s="5" t="n">
@@ -2070,19 +2117,19 @@
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
+      <c r="A26" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B26" s="0"/>
+      <c r="B26" s="1"/>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
+      <c r="A27" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B27" s="0"/>
+      <c r="B27" s="1"/>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
+      <c r="A28" s="1" t="s">
         <v>29</v>
       </c>
       <c r="B28" s="5" t="n">
@@ -2093,7 +2140,7 @@
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="s">
+      <c r="A29" s="1" t="s">
         <v>30</v>
       </c>
       <c r="B29" s="5" t="n">
@@ -2104,7 +2151,7 @@
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="s">
+      <c r="A30" s="1" t="s">
         <v>31</v>
       </c>
       <c r="B30" s="5" t="n">
@@ -2115,7 +2162,7 @@
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="s">
+      <c r="A31" s="1" t="s">
         <v>32</v>
       </c>
       <c r="B31" s="5" t="n">
@@ -2126,7 +2173,7 @@
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="s">
+      <c r="A32" s="1" t="s">
         <v>33</v>
       </c>
       <c r="B32" s="5" t="n">
@@ -2137,19 +2184,19 @@
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="s">
+      <c r="A33" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B33" s="0"/>
+      <c r="B33" s="1"/>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="s">
+      <c r="A34" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B34" s="0"/>
+      <c r="B34" s="1"/>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="s">
+      <c r="A35" s="1" t="s">
         <v>36</v>
       </c>
       <c r="B35" s="5" t="n">
@@ -2160,7 +2207,7 @@
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="0" t="s">
+      <c r="A36" s="1" t="s">
         <v>37</v>
       </c>
       <c r="B36" s="5" t="n">
@@ -2171,7 +2218,7 @@
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="0" t="s">
+      <c r="A37" s="1" t="s">
         <v>38</v>
       </c>
       <c r="B37" s="5" t="n">
@@ -2182,7 +2229,7 @@
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="0" t="s">
+      <c r="A38" s="1" t="s">
         <v>39</v>
       </c>
       <c r="B38" s="5" t="n">
@@ -2193,7 +2240,7 @@
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="0" t="s">
+      <c r="A39" s="1" t="s">
         <v>40</v>
       </c>
       <c r="B39" s="5" t="n">
@@ -2204,19 +2251,19 @@
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="0" t="s">
+      <c r="A40" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B40" s="0"/>
+      <c r="B40" s="1"/>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="0" t="s">
+      <c r="A41" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B41" s="0"/>
+      <c r="B41" s="1"/>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="0" t="s">
+      <c r="A42" s="1" t="s">
         <v>43</v>
       </c>
       <c r="B42" s="5" t="n">
@@ -2227,7 +2274,7 @@
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="0" t="s">
+      <c r="A43" s="1" t="s">
         <v>44</v>
       </c>
       <c r="B43" s="5" t="n">
@@ -2238,7 +2285,7 @@
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="0" t="s">
+      <c r="A44" s="1" t="s">
         <v>45</v>
       </c>
       <c r="B44" s="5" t="n">
@@ -2249,7 +2296,7 @@
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="0" t="s">
+      <c r="A45" s="1" t="s">
         <v>46</v>
       </c>
       <c r="B45" s="5" t="n">
@@ -2260,7 +2307,7 @@
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="0" t="s">
+      <c r="A46" s="1" t="s">
         <v>47</v>
       </c>
       <c r="B46" s="5" t="n">
@@ -2271,19 +2318,19 @@
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="0" t="s">
+      <c r="A47" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B47" s="0"/>
+      <c r="B47" s="1"/>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="0" t="s">
+      <c r="A48" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B48" s="0"/>
+      <c r="B48" s="1"/>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="0" t="s">
+      <c r="A49" s="1" t="s">
         <v>50</v>
       </c>
       <c r="B49" s="5" t="n">
@@ -2294,7 +2341,7 @@
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="0" t="s">
+      <c r="A50" s="1" t="s">
         <v>51</v>
       </c>
       <c r="B50" s="5" t="n">
@@ -2305,7 +2352,7 @@
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="0" t="s">
+      <c r="A51" s="1" t="s">
         <v>52</v>
       </c>
       <c r="B51" s="5" t="n">
@@ -2316,7 +2363,7 @@
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="0" t="s">
+      <c r="A52" s="1" t="s">
         <v>53</v>
       </c>
       <c r="B52" s="5" t="n">
@@ -2327,7 +2374,7 @@
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="0" t="s">
+      <c r="A53" s="1" t="s">
         <v>54</v>
       </c>
       <c r="B53" s="5" t="n">
@@ -2338,19 +2385,19 @@
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="0" t="s">
+      <c r="A54" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B54" s="0"/>
+      <c r="B54" s="1"/>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="0" t="s">
+      <c r="A55" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B55" s="0"/>
+      <c r="B55" s="1"/>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="0" t="s">
+      <c r="A56" s="1" t="s">
         <v>57</v>
       </c>
       <c r="B56" s="5" t="n">
@@ -2361,7 +2408,7 @@
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="0" t="s">
+      <c r="A57" s="1" t="s">
         <v>58</v>
       </c>
       <c r="B57" s="5" t="n">
@@ -2372,7 +2419,7 @@
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="0" t="s">
+      <c r="A58" s="1" t="s">
         <v>59</v>
       </c>
       <c r="B58" s="5" t="n">
@@ -2383,7 +2430,7 @@
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="0" t="s">
+      <c r="A59" s="1" t="s">
         <v>60</v>
       </c>
       <c r="B59" s="5" t="n">
@@ -2394,7 +2441,7 @@
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="0" t="s">
+      <c r="A60" s="1" t="s">
         <v>61</v>
       </c>
       <c r="B60" s="5" t="n">
@@ -2405,19 +2452,19 @@
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="0" t="s">
+      <c r="A61" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B61" s="0"/>
+      <c r="B61" s="1"/>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="0" t="s">
+      <c r="A62" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B62" s="0"/>
+      <c r="B62" s="1"/>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="0" t="s">
+      <c r="A63" s="1" t="s">
         <v>64</v>
       </c>
       <c r="B63" s="5" t="n">
@@ -2428,7 +2475,7 @@
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="0" t="s">
+      <c r="A64" s="1" t="s">
         <v>65</v>
       </c>
       <c r="B64" s="5" t="n">
@@ -2439,7 +2486,7 @@
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="0" t="s">
+      <c r="A65" s="1" t="s">
         <v>66</v>
       </c>
       <c r="B65" s="5" t="n">
@@ -2450,7 +2497,7 @@
       </c>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="0" t="s">
+      <c r="A66" s="1" t="s">
         <v>67</v>
       </c>
       <c r="B66" s="5" t="n">
@@ -2461,7 +2508,7 @@
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="0" t="s">
+      <c r="A67" s="1" t="s">
         <v>68</v>
       </c>
       <c r="B67" s="5" t="n">
@@ -2472,19 +2519,19 @@
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="0" t="s">
+      <c r="A68" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B68" s="0"/>
+      <c r="B68" s="1"/>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="0" t="s">
+      <c r="A69" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B69" s="0"/>
+      <c r="B69" s="1"/>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="0" t="s">
+      <c r="A70" s="1" t="s">
         <v>71</v>
       </c>
       <c r="B70" s="5" t="n">
@@ -2495,7 +2542,7 @@
       </c>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="0" t="s">
+      <c r="A71" s="1" t="s">
         <v>72</v>
       </c>
       <c r="B71" s="5" t="n">
@@ -2506,7 +2553,7 @@
       </c>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="0" t="s">
+      <c r="A72" s="1" t="s">
         <v>73</v>
       </c>
       <c r="B72" s="5" t="n">
@@ -2517,7 +2564,7 @@
       </c>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="0" t="s">
+      <c r="A73" s="1" t="s">
         <v>74</v>
       </c>
       <c r="B73" s="5" t="n">
@@ -2528,7 +2575,7 @@
       </c>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="0" t="s">
+      <c r="A74" s="1" t="s">
         <v>75</v>
       </c>
       <c r="B74" s="5" t="n">
@@ -2539,19 +2586,19 @@
       </c>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="0" t="s">
+      <c r="A75" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B75" s="0"/>
+      <c r="B75" s="1"/>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="0" t="s">
+      <c r="A76" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B76" s="0"/>
+      <c r="B76" s="1"/>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="0" t="s">
+      <c r="A77" s="1" t="s">
         <v>78</v>
       </c>
       <c r="B77" s="5" t="n">
@@ -2562,7 +2609,7 @@
       </c>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="0" t="s">
+      <c r="A78" s="1" t="s">
         <v>79</v>
       </c>
       <c r="B78" s="5" t="n">
@@ -2573,7 +2620,7 @@
       </c>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="0" t="s">
+      <c r="A79" s="1" t="s">
         <v>80</v>
       </c>
       <c r="B79" s="5" t="n">
@@ -2584,7 +2631,7 @@
       </c>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="0" t="s">
+      <c r="A80" s="1" t="s">
         <v>81</v>
       </c>
       <c r="B80" s="5" t="n">
@@ -2595,7 +2642,7 @@
       </c>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="0" t="s">
+      <c r="A81" s="1" t="s">
         <v>82</v>
       </c>
       <c r="B81" s="5" t="n">
@@ -2606,19 +2653,19 @@
       </c>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="0" t="s">
+      <c r="A82" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B82" s="0"/>
+      <c r="B82" s="1"/>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="0" t="s">
+      <c r="A83" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B83" s="0"/>
+      <c r="B83" s="1"/>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="0" t="s">
+      <c r="A84" s="1" t="s">
         <v>85</v>
       </c>
       <c r="B84" s="5" t="n">
@@ -2629,7 +2676,7 @@
       </c>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="0" t="s">
+      <c r="A85" s="1" t="s">
         <v>86</v>
       </c>
       <c r="B85" s="5" t="n">
@@ -2640,7 +2687,7 @@
       </c>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="0" t="s">
+      <c r="A86" s="1" t="s">
         <v>87</v>
       </c>
       <c r="B86" s="5" t="n">
@@ -2651,7 +2698,7 @@
       </c>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="0" t="s">
+      <c r="A87" s="1" t="s">
         <v>88</v>
       </c>
       <c r="B87" s="5" t="n">
@@ -2662,7 +2709,7 @@
       </c>
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="0" t="s">
+      <c r="A88" s="1" t="s">
         <v>89</v>
       </c>
       <c r="B88" s="5" t="n">
@@ -2673,31 +2720,31 @@
       </c>
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="0" t="s">
+      <c r="A89" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B89" s="0"/>
+      <c r="B89" s="1"/>
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="0" t="s">
+      <c r="A90" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B90" s="0"/>
+      <c r="B90" s="1"/>
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="0" t="s">
+      <c r="A91" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="B91" s="0"/>
+      <c r="B91" s="1"/>
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="0" t="s">
+      <c r="A92" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="B92" s="0"/>
+      <c r="B92" s="1"/>
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="0" t="s">
+      <c r="A93" s="1" t="s">
         <v>94</v>
       </c>
       <c r="B93" s="5" t="n">
@@ -2708,7 +2755,7 @@
       </c>
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="0" t="s">
+      <c r="A94" s="1" t="s">
         <v>95</v>
       </c>
       <c r="B94" s="5" t="n">
@@ -2719,7 +2766,7 @@
       </c>
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="0" t="s">
+      <c r="A95" s="1" t="s">
         <v>96</v>
       </c>
       <c r="B95" s="5" t="n">
@@ -2730,19 +2777,19 @@
       </c>
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="0" t="s">
+      <c r="A96" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="B96" s="0"/>
+      <c r="B96" s="1"/>
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="0" t="s">
+      <c r="A97" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B97" s="0"/>
+      <c r="B97" s="1"/>
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="0" t="s">
+      <c r="A98" s="1" t="s">
         <v>99</v>
       </c>
       <c r="B98" s="5" t="n">
@@ -2753,7 +2800,7 @@
       </c>
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="0" t="s">
+      <c r="A99" s="1" t="s">
         <v>100</v>
       </c>
       <c r="B99" s="5" t="n">
@@ -2764,7 +2811,7 @@
       </c>
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="0" t="s">
+      <c r="A100" s="1" t="s">
         <v>101</v>
       </c>
       <c r="B100" s="5" t="n">
@@ -2775,7 +2822,7 @@
       </c>
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="0" t="s">
+      <c r="A101" s="1" t="s">
         <v>102</v>
       </c>
       <c r="B101" s="5" t="n">
@@ -2786,7 +2833,7 @@
       </c>
     </row>
     <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="0" t="s">
+      <c r="A102" s="1" t="s">
         <v>103</v>
       </c>
       <c r="B102" s="5" t="n">
@@ -2797,19 +2844,19 @@
       </c>
     </row>
     <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="0" t="s">
+      <c r="A103" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="B103" s="0"/>
+      <c r="B103" s="1"/>
     </row>
     <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="0" t="s">
+      <c r="A104" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B104" s="0"/>
+      <c r="B104" s="1"/>
     </row>
     <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="0" t="s">
+      <c r="A105" s="1" t="s">
         <v>106</v>
       </c>
       <c r="B105" s="5" t="n">
@@ -2820,7 +2867,7 @@
       </c>
     </row>
     <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="0" t="s">
+      <c r="A106" s="1" t="s">
         <v>107</v>
       </c>
       <c r="B106" s="5" t="n">
@@ -2831,7 +2878,7 @@
       </c>
     </row>
     <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="0" t="s">
+      <c r="A107" s="1" t="s">
         <v>108</v>
       </c>
       <c r="B107" s="5" t="n">
@@ -2842,7 +2889,7 @@
       </c>
     </row>
     <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="0" t="s">
+      <c r="A108" s="1" t="s">
         <v>109</v>
       </c>
       <c r="B108" s="5" t="n">
@@ -2853,7 +2900,7 @@
       </c>
     </row>
     <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="0" t="s">
+      <c r="A109" s="1" t="s">
         <v>110</v>
       </c>
       <c r="B109" s="5" t="n">
@@ -2864,19 +2911,19 @@
       </c>
     </row>
     <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="0" t="s">
+      <c r="A110" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="B110" s="0"/>
+      <c r="B110" s="1"/>
     </row>
     <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="0" t="s">
+      <c r="A111" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B111" s="0"/>
+      <c r="B111" s="1"/>
     </row>
     <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="0" t="s">
+      <c r="A112" s="1" t="s">
         <v>113</v>
       </c>
       <c r="B112" s="5" t="n">
@@ -2887,7 +2934,7 @@
       </c>
     </row>
     <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="0" t="s">
+      <c r="A113" s="1" t="s">
         <v>114</v>
       </c>
       <c r="B113" s="5" t="n">
@@ -2898,13 +2945,13 @@
       </c>
     </row>
     <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="0" t="s">
+      <c r="A114" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="B114" s="0"/>
+      <c r="B114" s="1"/>
     </row>
     <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="0" t="s">
+      <c r="A115" s="1" t="s">
         <v>116</v>
       </c>
       <c r="B115" s="5" t="n">
@@ -2915,7 +2962,7 @@
       </c>
     </row>
     <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="0" t="s">
+      <c r="A116" s="1" t="s">
         <v>117</v>
       </c>
       <c r="B116" s="5" t="n">
@@ -2926,19 +2973,19 @@
       </c>
     </row>
     <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="0" t="s">
+      <c r="A117" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B117" s="0"/>
+      <c r="B117" s="1"/>
     </row>
     <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="0" t="s">
+      <c r="A118" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="B118" s="0"/>
+      <c r="B118" s="1"/>
     </row>
     <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="0" t="s">
+      <c r="A119" s="1" t="s">
         <v>120</v>
       </c>
       <c r="B119" s="5" t="n">
@@ -2949,7 +2996,7 @@
       </c>
     </row>
     <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="0" t="s">
+      <c r="A120" s="1" t="s">
         <v>121</v>
       </c>
       <c r="B120" s="5" t="n">
@@ -2960,7 +3007,7 @@
       </c>
     </row>
     <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="0" t="s">
+      <c r="A121" s="1" t="s">
         <v>122</v>
       </c>
       <c r="B121" s="5" t="n">
@@ -2971,13 +3018,13 @@
       </c>
     </row>
     <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="0" t="s">
+      <c r="A122" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B122" s="0"/>
+      <c r="B122" s="1"/>
     </row>
     <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="0" t="s">
+      <c r="A123" s="1" t="s">
         <v>124</v>
       </c>
       <c r="B123" s="5" t="n">
@@ -2988,19 +3035,19 @@
       </c>
     </row>
     <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="0" t="s">
+      <c r="A124" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="B124" s="0"/>
+      <c r="B124" s="1"/>
     </row>
     <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="0" t="s">
+      <c r="A125" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B125" s="0"/>
+      <c r="B125" s="1"/>
     </row>
     <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="0" t="s">
+      <c r="A126" s="1" t="s">
         <v>127</v>
       </c>
       <c r="B126" s="5" t="n">
@@ -3011,7 +3058,7 @@
       </c>
     </row>
     <row r="127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="0" t="s">
+      <c r="A127" s="1" t="s">
         <v>128</v>
       </c>
       <c r="B127" s="5" t="n">
@@ -3022,7 +3069,7 @@
       </c>
     </row>
     <row r="128" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="0" t="s">
+      <c r="A128" s="1" t="s">
         <v>129</v>
       </c>
       <c r="B128" s="5" t="n">
@@ -3033,7 +3080,7 @@
       </c>
     </row>
     <row r="129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="0" t="s">
+      <c r="A129" s="1" t="s">
         <v>130</v>
       </c>
       <c r="B129" s="5" t="n">
@@ -3044,7 +3091,7 @@
       </c>
     </row>
     <row r="130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="0" t="s">
+      <c r="A130" s="1" t="s">
         <v>131</v>
       </c>
       <c r="B130" s="5" t="n">
@@ -3055,19 +3102,19 @@
       </c>
     </row>
     <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="0" t="s">
+      <c r="A131" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="B131" s="0"/>
+      <c r="B131" s="1"/>
     </row>
     <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="0" t="s">
+      <c r="A132" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="B132" s="0"/>
+      <c r="B132" s="1"/>
     </row>
     <row r="133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="0" t="s">
+      <c r="A133" s="1" t="s">
         <v>134</v>
       </c>
       <c r="B133" s="5" t="n">
@@ -3078,7 +3125,7 @@
       </c>
     </row>
     <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A134" s="0" t="s">
+      <c r="A134" s="1" t="s">
         <v>135</v>
       </c>
       <c r="B134" s="5" t="n">
@@ -3089,7 +3136,7 @@
       </c>
     </row>
     <row r="135" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="0" t="s">
+      <c r="A135" s="1" t="s">
         <v>136</v>
       </c>
       <c r="B135" s="5" t="n">
@@ -3100,7 +3147,7 @@
       </c>
     </row>
     <row r="136" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="0" t="s">
+      <c r="A136" s="1" t="s">
         <v>137</v>
       </c>
       <c r="B136" s="5" t="n">
@@ -3111,7 +3158,7 @@
       </c>
     </row>
     <row r="137" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="0" t="s">
+      <c r="A137" s="1" t="s">
         <v>138</v>
       </c>
       <c r="B137" s="5" t="n">
@@ -3122,25 +3169,25 @@
       </c>
     </row>
     <row r="138" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="0" t="s">
+      <c r="A138" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B138" s="0"/>
+      <c r="B138" s="1"/>
     </row>
     <row r="139" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A139" s="0" t="s">
+      <c r="A139" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B139" s="0"/>
+      <c r="B139" s="1"/>
     </row>
     <row r="140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A140" s="0" t="s">
+      <c r="A140" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="B140" s="0"/>
+      <c r="B140" s="1"/>
     </row>
     <row r="141" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A141" s="0" t="s">
+      <c r="A141" s="1" t="s">
         <v>142</v>
       </c>
       <c r="B141" s="5" t="n">
@@ -3151,7 +3198,7 @@
       </c>
     </row>
     <row r="142" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A142" s="0" t="s">
+      <c r="A142" s="1" t="s">
         <v>143</v>
       </c>
       <c r="B142" s="5" t="n">
@@ -3162,7 +3209,7 @@
       </c>
     </row>
     <row r="143" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A143" s="0" t="s">
+      <c r="A143" s="1" t="s">
         <v>144</v>
       </c>
       <c r="B143" s="5" t="n">
@@ -3173,7 +3220,7 @@
       </c>
     </row>
     <row r="144" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A144" s="0" t="s">
+      <c r="A144" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B144" s="5" t="n">
@@ -3184,19 +3231,19 @@
       </c>
     </row>
     <row r="145" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A145" s="0" t="s">
+      <c r="A145" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="B145" s="0"/>
+      <c r="B145" s="1"/>
     </row>
     <row r="146" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A146" s="0" t="s">
+      <c r="A146" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="B146" s="0"/>
+      <c r="B146" s="1"/>
     </row>
     <row r="147" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A147" s="0" t="s">
+      <c r="A147" s="1" t="s">
         <v>148</v>
       </c>
       <c r="B147" s="5" t="n">
@@ -3207,7 +3254,7 @@
       </c>
     </row>
     <row r="148" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A148" s="0" t="s">
+      <c r="A148" s="1" t="s">
         <v>149</v>
       </c>
       <c r="B148" s="5" t="n">
@@ -3218,7 +3265,7 @@
       </c>
     </row>
     <row r="149" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A149" s="0" t="s">
+      <c r="A149" s="1" t="s">
         <v>150</v>
       </c>
       <c r="B149" s="5" t="n">
@@ -3229,7 +3276,7 @@
       </c>
     </row>
     <row r="150" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A150" s="0" t="s">
+      <c r="A150" s="1" t="s">
         <v>151</v>
       </c>
       <c r="B150" s="5" t="n">
@@ -3240,7 +3287,7 @@
       </c>
     </row>
     <row r="151" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A151" s="0" t="s">
+      <c r="A151" s="1" t="s">
         <v>152</v>
       </c>
       <c r="B151" s="5" t="n">
@@ -3251,19 +3298,19 @@
       </c>
     </row>
     <row r="152" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A152" s="0" t="s">
+      <c r="A152" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="B152" s="0"/>
+      <c r="B152" s="1"/>
     </row>
     <row r="153" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A153" s="0" t="s">
+      <c r="A153" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B153" s="0"/>
+      <c r="B153" s="1"/>
     </row>
     <row r="154" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A154" s="0" t="s">
+      <c r="A154" s="1" t="s">
         <v>155</v>
       </c>
       <c r="B154" s="5" t="n">
@@ -3274,7 +3321,7 @@
       </c>
     </row>
     <row r="155" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A155" s="0" t="s">
+      <c r="A155" s="1" t="s">
         <v>156</v>
       </c>
       <c r="B155" s="5" t="n">
@@ -3285,7 +3332,7 @@
       </c>
     </row>
     <row r="156" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A156" s="0" t="s">
+      <c r="A156" s="1" t="s">
         <v>157</v>
       </c>
       <c r="B156" s="5" t="n">
@@ -3296,7 +3343,7 @@
       </c>
     </row>
     <row r="157" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A157" s="0" t="s">
+      <c r="A157" s="1" t="s">
         <v>158</v>
       </c>
       <c r="B157" s="5" t="n">
@@ -3307,31 +3354,31 @@
       </c>
     </row>
     <row r="158" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A158" s="0" t="s">
+      <c r="A158" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="B158" s="0"/>
+      <c r="B158" s="1"/>
     </row>
     <row r="159" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A159" s="0" t="s">
+      <c r="A159" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="B159" s="0"/>
+      <c r="B159" s="1"/>
     </row>
     <row r="160" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A160" s="0" t="s">
+      <c r="A160" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="B160" s="0"/>
+      <c r="B160" s="1"/>
     </row>
     <row r="161" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A161" s="0" t="s">
+      <c r="A161" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="B161" s="0"/>
+      <c r="B161" s="1"/>
     </row>
     <row r="162" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A162" s="0" t="s">
+      <c r="A162" s="1" t="s">
         <v>163</v>
       </c>
       <c r="B162" s="5" t="n">
@@ -3342,7 +3389,7 @@
       </c>
     </row>
     <row r="163" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A163" s="0" t="s">
+      <c r="A163" s="1" t="s">
         <v>164</v>
       </c>
       <c r="B163" s="5" t="n">
@@ -3353,7 +3400,7 @@
       </c>
     </row>
     <row r="164" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A164" s="0" t="s">
+      <c r="A164" s="1" t="s">
         <v>165</v>
       </c>
       <c r="B164" s="5" t="n">
@@ -3364,7 +3411,7 @@
       </c>
     </row>
     <row r="165" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A165" s="0" t="s">
+      <c r="A165" s="1" t="s">
         <v>166</v>
       </c>
       <c r="B165" s="5" t="n">
@@ -3375,19 +3422,19 @@
       </c>
     </row>
     <row r="166" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A166" s="0" t="s">
+      <c r="A166" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="B166" s="0"/>
+      <c r="B166" s="1"/>
     </row>
     <row r="167" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A167" s="0" t="s">
+      <c r="A167" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="B167" s="0"/>
+      <c r="B167" s="1"/>
     </row>
     <row r="168" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A168" s="0" t="s">
+      <c r="A168" s="1" t="s">
         <v>169</v>
       </c>
       <c r="B168" s="5" t="n">
@@ -3398,7 +3445,7 @@
       </c>
     </row>
     <row r="169" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A169" s="0" t="s">
+      <c r="A169" s="1" t="s">
         <v>170</v>
       </c>
       <c r="B169" s="5" t="n">
@@ -3409,7 +3456,7 @@
       </c>
     </row>
     <row r="170" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A170" s="0" t="s">
+      <c r="A170" s="1" t="s">
         <v>171</v>
       </c>
       <c r="B170" s="5" t="n">
@@ -3420,7 +3467,7 @@
       </c>
     </row>
     <row r="171" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A171" s="0" t="s">
+      <c r="A171" s="1" t="s">
         <v>172</v>
       </c>
       <c r="B171" s="5" t="n">
@@ -3431,7 +3478,7 @@
       </c>
     </row>
     <row r="172" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A172" s="0" t="s">
+      <c r="A172" s="1" t="s">
         <v>173</v>
       </c>
       <c r="B172" s="5" t="n">
@@ -3442,19 +3489,19 @@
       </c>
     </row>
     <row r="173" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A173" s="0" t="s">
+      <c r="A173" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="B173" s="0"/>
+      <c r="B173" s="1"/>
     </row>
     <row r="174" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A174" s="0" t="s">
+      <c r="A174" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="B174" s="0"/>
+      <c r="B174" s="1"/>
     </row>
     <row r="175" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A175" s="0" t="s">
+      <c r="A175" s="1" t="s">
         <v>176</v>
       </c>
       <c r="B175" s="5" t="n">
@@ -3465,7 +3512,7 @@
       </c>
     </row>
     <row r="176" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A176" s="0" t="s">
+      <c r="A176" s="1" t="s">
         <v>177</v>
       </c>
       <c r="B176" s="5" t="n">
@@ -3476,7 +3523,7 @@
       </c>
     </row>
     <row r="177" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A177" s="0" t="s">
+      <c r="A177" s="1" t="s">
         <v>178</v>
       </c>
       <c r="B177" s="5" t="n">
@@ -3487,7 +3534,7 @@
       </c>
     </row>
     <row r="178" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A178" s="0" t="s">
+      <c r="A178" s="1" t="s">
         <v>179</v>
       </c>
       <c r="B178" s="5" t="n">
@@ -3498,7 +3545,7 @@
       </c>
     </row>
     <row r="179" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A179" s="0" t="s">
+      <c r="A179" s="1" t="s">
         <v>180</v>
       </c>
       <c r="B179" s="5" t="n">
@@ -3509,19 +3556,19 @@
       </c>
     </row>
     <row r="180" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A180" s="0" t="s">
+      <c r="A180" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="B180" s="0"/>
+      <c r="B180" s="1"/>
     </row>
     <row r="181" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A181" s="0" t="s">
+      <c r="A181" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="B181" s="0"/>
+      <c r="B181" s="1"/>
     </row>
     <row r="182" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A182" s="0" t="s">
+      <c r="A182" s="1" t="s">
         <v>183</v>
       </c>
       <c r="B182" s="5" t="n">
@@ -3532,7 +3579,7 @@
       </c>
     </row>
     <row r="183" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A183" s="0" t="s">
+      <c r="A183" s="1" t="s">
         <v>184</v>
       </c>
       <c r="B183" s="5" t="n">
@@ -3543,7 +3590,7 @@
       </c>
     </row>
     <row r="184" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A184" s="0" t="s">
+      <c r="A184" s="1" t="s">
         <v>185</v>
       </c>
       <c r="B184" s="5" t="n">
@@ -3554,7 +3601,7 @@
       </c>
     </row>
     <row r="185" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A185" s="0" t="s">
+      <c r="A185" s="1" t="s">
         <v>186</v>
       </c>
       <c r="B185" s="5" t="n">
@@ -3565,7 +3612,7 @@
       </c>
     </row>
     <row r="186" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A186" s="0" t="s">
+      <c r="A186" s="1" t="s">
         <v>187</v>
       </c>
       <c r="B186" s="5" t="n">
@@ -3576,19 +3623,19 @@
       </c>
     </row>
     <row r="187" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A187" s="0" t="s">
+      <c r="A187" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="B187" s="0"/>
+      <c r="B187" s="1"/>
     </row>
     <row r="188" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A188" s="0" t="s">
+      <c r="A188" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="B188" s="0"/>
+      <c r="B188" s="1"/>
     </row>
     <row r="189" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A189" s="0" t="s">
+      <c r="A189" s="1" t="s">
         <v>190</v>
       </c>
       <c r="B189" s="5" t="n">
@@ -3599,7 +3646,7 @@
       </c>
     </row>
     <row r="190" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A190" s="0" t="s">
+      <c r="A190" s="1" t="s">
         <v>191</v>
       </c>
       <c r="B190" s="5" t="n">
@@ -3610,7 +3657,7 @@
       </c>
     </row>
     <row r="191" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A191" s="0" t="s">
+      <c r="A191" s="1" t="s">
         <v>192</v>
       </c>
       <c r="B191" s="5" t="n">
@@ -3621,7 +3668,7 @@
       </c>
     </row>
     <row r="192" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A192" s="0" t="s">
+      <c r="A192" s="1" t="s">
         <v>193</v>
       </c>
       <c r="B192" s="5" t="n">
@@ -3632,7 +3679,7 @@
       </c>
     </row>
     <row r="193" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A193" s="0" t="s">
+      <c r="A193" s="1" t="s">
         <v>194</v>
       </c>
       <c r="B193" s="5" t="n">
@@ -3643,19 +3690,19 @@
       </c>
     </row>
     <row r="194" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A194" s="0" t="s">
+      <c r="A194" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="B194" s="0"/>
+      <c r="B194" s="1"/>
     </row>
     <row r="195" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A195" s="0" t="s">
+      <c r="A195" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="B195" s="0"/>
+      <c r="B195" s="1"/>
     </row>
     <row r="196" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A196" s="0" t="s">
+      <c r="A196" s="1" t="s">
         <v>197</v>
       </c>
       <c r="B196" s="5" t="n">
@@ -3666,13 +3713,13 @@
       </c>
     </row>
     <row r="197" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A197" s="0" t="s">
+      <c r="A197" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="B197" s="0"/>
+      <c r="B197" s="1"/>
     </row>
     <row r="198" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A198" s="0" t="s">
+      <c r="A198" s="1" t="s">
         <v>199</v>
       </c>
       <c r="B198" s="5" t="n">
@@ -3683,7 +3730,7 @@
       </c>
     </row>
     <row r="199" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A199" s="0" t="s">
+      <c r="A199" s="1" t="s">
         <v>200</v>
       </c>
       <c r="B199" s="5" t="n">
@@ -3694,7 +3741,7 @@
       </c>
     </row>
     <row r="200" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A200" s="0" t="s">
+      <c r="A200" s="1" t="s">
         <v>201</v>
       </c>
       <c r="B200" s="5" t="n">
@@ -3705,19 +3752,19 @@
       </c>
     </row>
     <row r="201" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A201" s="0" t="s">
+      <c r="A201" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="B201" s="0"/>
+      <c r="B201" s="1"/>
     </row>
     <row r="202" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A202" s="0" t="s">
+      <c r="A202" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="B202" s="0"/>
+      <c r="B202" s="1"/>
     </row>
     <row r="203" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A203" s="0" t="s">
+      <c r="A203" s="1" t="s">
         <v>204</v>
       </c>
       <c r="B203" s="5" t="n">
@@ -3728,7 +3775,7 @@
       </c>
     </row>
     <row r="204" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A204" s="0" t="s">
+      <c r="A204" s="1" t="s">
         <v>205</v>
       </c>
       <c r="B204" s="5" t="n">
@@ -3739,7 +3786,7 @@
       </c>
     </row>
     <row r="205" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A205" s="0" t="s">
+      <c r="A205" s="1" t="s">
         <v>206</v>
       </c>
       <c r="B205" s="5" t="n">
@@ -3750,7 +3797,7 @@
       </c>
     </row>
     <row r="206" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A206" s="0" t="s">
+      <c r="A206" s="1" t="s">
         <v>207</v>
       </c>
       <c r="B206" s="5" t="n">
@@ -3761,7 +3808,7 @@
       </c>
     </row>
     <row r="207" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A207" s="0" t="s">
+      <c r="A207" s="1" t="s">
         <v>208</v>
       </c>
       <c r="B207" s="5" t="n">
@@ -3772,19 +3819,19 @@
       </c>
     </row>
     <row r="208" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A208" s="0" t="s">
+      <c r="A208" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B208" s="0"/>
+      <c r="B208" s="1"/>
     </row>
     <row r="209" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A209" s="0" t="s">
+      <c r="A209" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="B209" s="0"/>
+      <c r="B209" s="1"/>
     </row>
     <row r="210" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A210" s="0" t="s">
+      <c r="A210" s="1" t="s">
         <v>211</v>
       </c>
       <c r="B210" s="5" t="n">
@@ -3795,7 +3842,7 @@
       </c>
     </row>
     <row r="211" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A211" s="0" t="s">
+      <c r="A211" s="1" t="s">
         <v>212</v>
       </c>
       <c r="B211" s="5" t="n">
@@ -3806,7 +3853,7 @@
       </c>
     </row>
     <row r="212" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A212" s="0" t="s">
+      <c r="A212" s="1" t="s">
         <v>213</v>
       </c>
       <c r="B212" s="5" t="n">
@@ -3817,7 +3864,7 @@
       </c>
     </row>
     <row r="213" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A213" s="0" t="s">
+      <c r="A213" s="1" t="s">
         <v>214</v>
       </c>
       <c r="B213" s="5" t="n">
@@ -3828,7 +3875,7 @@
       </c>
     </row>
     <row r="214" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A214" s="0" t="s">
+      <c r="A214" s="1" t="s">
         <v>215</v>
       </c>
       <c r="B214" s="5" t="n">
@@ -3839,19 +3886,19 @@
       </c>
     </row>
     <row r="215" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A215" s="0" t="s">
+      <c r="A215" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="B215" s="0"/>
+      <c r="B215" s="1"/>
     </row>
     <row r="216" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A216" s="0" t="s">
+      <c r="A216" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="B216" s="0"/>
+      <c r="B216" s="1"/>
     </row>
     <row r="217" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A217" s="0" t="s">
+      <c r="A217" s="1" t="s">
         <v>218</v>
       </c>
       <c r="B217" s="5" t="n">
@@ -3862,7 +3909,7 @@
       </c>
     </row>
     <row r="218" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A218" s="0" t="s">
+      <c r="A218" s="1" t="s">
         <v>219</v>
       </c>
       <c r="B218" s="5" t="n">
@@ -3873,7 +3920,7 @@
       </c>
     </row>
     <row r="219" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A219" s="0" t="s">
+      <c r="A219" s="1" t="s">
         <v>220</v>
       </c>
       <c r="B219" s="5" t="n">
@@ -3884,7 +3931,7 @@
       </c>
     </row>
     <row r="220" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A220" s="0" t="s">
+      <c r="A220" s="1" t="s">
         <v>221</v>
       </c>
       <c r="B220" s="5" t="n">
@@ -3895,7 +3942,7 @@
       </c>
     </row>
     <row r="221" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A221" s="0" t="s">
+      <c r="A221" s="1" t="s">
         <v>222</v>
       </c>
       <c r="B221" s="5" t="n">
@@ -3906,19 +3953,19 @@
       </c>
     </row>
     <row r="222" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A222" s="0" t="s">
+      <c r="A222" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="B222" s="0"/>
+      <c r="B222" s="1"/>
     </row>
     <row r="223" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A223" s="0" t="s">
+      <c r="A223" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="B223" s="0"/>
+      <c r="B223" s="1"/>
     </row>
     <row r="224" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A224" s="0" t="s">
+      <c r="A224" s="1" t="s">
         <v>225</v>
       </c>
       <c r="B224" s="5" t="n">
@@ -3929,7 +3976,7 @@
       </c>
     </row>
     <row r="225" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A225" s="0" t="s">
+      <c r="A225" s="1" t="s">
         <v>226</v>
       </c>
       <c r="B225" s="5" t="n">
@@ -3940,7 +3987,7 @@
       </c>
     </row>
     <row r="226" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A226" s="0" t="s">
+      <c r="A226" s="1" t="s">
         <v>227</v>
       </c>
       <c r="B226" s="5" t="n">
@@ -3951,7 +3998,7 @@
       </c>
     </row>
     <row r="227" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A227" s="0" t="s">
+      <c r="A227" s="1" t="s">
         <v>228</v>
       </c>
       <c r="B227" s="5" t="n">
@@ -3962,7 +4009,7 @@
       </c>
     </row>
     <row r="228" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A228" s="0" t="s">
+      <c r="A228" s="1" t="s">
         <v>229</v>
       </c>
       <c r="B228" s="5" t="n">
@@ -3973,19 +4020,19 @@
       </c>
     </row>
     <row r="229" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A229" s="0" t="s">
+      <c r="A229" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="B229" s="0"/>
+      <c r="B229" s="1"/>
     </row>
     <row r="230" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A230" s="0" t="s">
+      <c r="A230" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="B230" s="0"/>
+      <c r="B230" s="1"/>
     </row>
     <row r="231" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A231" s="0" t="s">
+      <c r="A231" s="1" t="s">
         <v>232</v>
       </c>
       <c r="B231" s="5" t="n">
@@ -3996,7 +4043,7 @@
       </c>
     </row>
     <row r="232" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A232" s="0" t="s">
+      <c r="A232" s="1" t="s">
         <v>233</v>
       </c>
       <c r="B232" s="5" t="n">
@@ -4007,7 +4054,7 @@
       </c>
     </row>
     <row r="233" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A233" s="0" t="s">
+      <c r="A233" s="1" t="s">
         <v>234</v>
       </c>
       <c r="B233" s="5" t="n">
@@ -4018,7 +4065,7 @@
       </c>
     </row>
     <row r="234" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A234" s="0" t="s">
+      <c r="A234" s="1" t="s">
         <v>235</v>
       </c>
       <c r="B234" s="5" t="n">
@@ -4029,7 +4076,7 @@
       </c>
     </row>
     <row r="235" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A235" s="0" t="s">
+      <c r="A235" s="1" t="s">
         <v>236</v>
       </c>
       <c r="B235" s="5" t="n">
@@ -4040,19 +4087,19 @@
       </c>
     </row>
     <row r="236" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A236" s="0" t="s">
+      <c r="A236" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="B236" s="0"/>
+      <c r="B236" s="1"/>
     </row>
     <row r="237" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A237" s="0" t="s">
+      <c r="A237" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="B237" s="0"/>
+      <c r="B237" s="1"/>
     </row>
     <row r="238" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A238" s="0" t="s">
+      <c r="A238" s="1" t="s">
         <v>239</v>
       </c>
       <c r="B238" s="5" t="n">
@@ -4063,7 +4110,7 @@
       </c>
     </row>
     <row r="239" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A239" s="0" t="s">
+      <c r="A239" s="1" t="s">
         <v>240</v>
       </c>
       <c r="B239" s="5" t="n">
@@ -4074,7 +4121,7 @@
       </c>
     </row>
     <row r="240" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A240" s="0" t="s">
+      <c r="A240" s="1" t="s">
         <v>241</v>
       </c>
       <c r="B240" s="5" t="n">
@@ -4085,7 +4132,7 @@
       </c>
     </row>
     <row r="241" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A241" s="0" t="s">
+      <c r="A241" s="1" t="s">
         <v>242</v>
       </c>
       <c r="B241" s="5" t="n">
@@ -4096,7 +4143,7 @@
       </c>
     </row>
     <row r="242" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A242" s="0" t="s">
+      <c r="A242" s="1" t="s">
         <v>243</v>
       </c>
       <c r="B242" s="5" t="n">
@@ -4107,19 +4154,19 @@
       </c>
     </row>
     <row r="243" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A243" s="0" t="s">
+      <c r="A243" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="B243" s="0"/>
+      <c r="B243" s="1"/>
     </row>
     <row r="244" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A244" s="0" t="s">
+      <c r="A244" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="B244" s="0"/>
+      <c r="B244" s="1"/>
     </row>
     <row r="245" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A245" s="0" t="s">
+      <c r="A245" s="1" t="s">
         <v>246</v>
       </c>
       <c r="B245" s="5" t="n">
@@ -4130,7 +4177,7 @@
       </c>
     </row>
     <row r="246" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A246" s="0" t="s">
+      <c r="A246" s="1" t="s">
         <v>247</v>
       </c>
       <c r="B246" s="5" t="n">
@@ -4141,7 +4188,7 @@
       </c>
     </row>
     <row r="247" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A247" s="0" t="s">
+      <c r="A247" s="1" t="s">
         <v>248</v>
       </c>
       <c r="B247" s="5" t="n">
@@ -4152,7 +4199,7 @@
       </c>
     </row>
     <row r="248" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A248" s="0" t="s">
+      <c r="A248" s="1" t="s">
         <v>249</v>
       </c>
       <c r="B248" s="5" t="n">
@@ -4163,7 +4210,7 @@
       </c>
     </row>
     <row r="249" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A249" s="0" t="s">
+      <c r="A249" s="1" t="s">
         <v>250</v>
       </c>
       <c r="B249" s="5" t="n">
@@ -4174,19 +4221,19 @@
       </c>
     </row>
     <row r="250" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A250" s="0" t="s">
+      <c r="A250" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="B250" s="0"/>
+      <c r="B250" s="1"/>
     </row>
     <row r="251" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A251" s="0" t="s">
+      <c r="A251" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="B251" s="0"/>
+      <c r="B251" s="1"/>
     </row>
     <row r="252" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A252" s="0" t="s">
+      <c r="A252" s="1" t="s">
         <v>253</v>
       </c>
       <c r="B252" s="5" t="n">
@@ -4197,7 +4244,7 @@
       </c>
     </row>
     <row r="253" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A253" s="0" t="s">
+      <c r="A253" s="1" t="s">
         <v>254</v>
       </c>
       <c r="B253" s="5" t="n">
@@ -4208,7 +4255,7 @@
       </c>
     </row>
     <row r="254" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A254" s="0" t="s">
+      <c r="A254" s="1" t="s">
         <v>255</v>
       </c>
       <c r="B254" s="5" t="n">
@@ -4219,7 +4266,7 @@
       </c>
     </row>
     <row r="255" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A255" s="0" t="s">
+      <c r="A255" s="1" t="s">
         <v>256</v>
       </c>
       <c r="B255" s="5" t="n">
@@ -4230,7 +4277,7 @@
       </c>
     </row>
     <row r="256" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A256" s="0" t="s">
+      <c r="A256" s="1" t="s">
         <v>257</v>
       </c>
       <c r="B256" s="5" t="n">
@@ -4241,19 +4288,19 @@
       </c>
     </row>
     <row r="257" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A257" s="0" t="s">
+      <c r="A257" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="B257" s="0"/>
+      <c r="B257" s="1"/>
     </row>
     <row r="258" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A258" s="0" t="s">
+      <c r="A258" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="B258" s="0"/>
+      <c r="B258" s="1"/>
     </row>
     <row r="259" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A259" s="0" t="s">
+      <c r="A259" s="1" t="s">
         <v>260</v>
       </c>
       <c r="B259" s="5" t="n">
@@ -4264,7 +4311,7 @@
       </c>
     </row>
     <row r="260" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A260" s="0" t="s">
+      <c r="A260" s="1" t="s">
         <v>261</v>
       </c>
       <c r="B260" s="5" t="n">
@@ -4275,7 +4322,7 @@
       </c>
     </row>
     <row r="261" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A261" s="0" t="s">
+      <c r="A261" s="1" t="s">
         <v>262</v>
       </c>
       <c r="B261" s="5" t="n">
@@ -4286,7 +4333,7 @@
       </c>
     </row>
     <row r="262" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A262" s="0" t="s">
+      <c r="A262" s="1" t="s">
         <v>263</v>
       </c>
       <c r="B262" s="5" t="n">
@@ -4297,7 +4344,7 @@
       </c>
     </row>
     <row r="263" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A263" s="0" t="s">
+      <c r="A263" s="1" t="s">
         <v>264</v>
       </c>
       <c r="B263" s="5" t="n">
@@ -4308,19 +4355,19 @@
       </c>
     </row>
     <row r="264" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A264" s="0" t="s">
+      <c r="A264" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="B264" s="0"/>
+      <c r="B264" s="1"/>
     </row>
     <row r="265" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A265" s="0" t="s">
+      <c r="A265" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="B265" s="0"/>
+      <c r="B265" s="1"/>
     </row>
     <row r="266" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A266" s="0" t="s">
+      <c r="A266" s="1" t="s">
         <v>267</v>
       </c>
       <c r="B266" s="5" t="n">
@@ -4331,7 +4378,7 @@
       </c>
     </row>
     <row r="267" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A267" s="0" t="s">
+      <c r="A267" s="1" t="s">
         <v>268</v>
       </c>
       <c r="B267" s="5" t="n">
@@ -4342,7 +4389,7 @@
       </c>
     </row>
     <row r="268" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A268" s="0" t="s">
+      <c r="A268" s="1" t="s">
         <v>269</v>
       </c>
       <c r="B268" s="5" t="n">
@@ -4353,7 +4400,7 @@
       </c>
     </row>
     <row r="269" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A269" s="0" t="s">
+      <c r="A269" s="1" t="s">
         <v>270</v>
       </c>
       <c r="B269" s="5" t="n">
@@ -4364,7 +4411,7 @@
       </c>
     </row>
     <row r="270" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A270" s="0" t="s">
+      <c r="A270" s="1" t="s">
         <v>271</v>
       </c>
       <c r="B270" s="5" t="n">
@@ -4375,19 +4422,19 @@
       </c>
     </row>
     <row r="271" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A271" s="0" t="s">
+      <c r="A271" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="B271" s="0"/>
+      <c r="B271" s="1"/>
     </row>
     <row r="272" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A272" s="0" t="s">
+      <c r="A272" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="B272" s="0"/>
+      <c r="B272" s="1"/>
     </row>
     <row r="273" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A273" s="0" t="s">
+      <c r="A273" s="1" t="s">
         <v>274</v>
       </c>
       <c r="B273" s="5" t="n">
@@ -4398,7 +4445,7 @@
       </c>
     </row>
     <row r="274" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A274" s="0" t="s">
+      <c r="A274" s="1" t="s">
         <v>275</v>
       </c>
       <c r="B274" s="5" t="n">
@@ -4409,7 +4456,7 @@
       </c>
     </row>
     <row r="275" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A275" s="0" t="s">
+      <c r="A275" s="1" t="s">
         <v>276</v>
       </c>
       <c r="B275" s="5" t="n">
@@ -4420,7 +4467,7 @@
       </c>
     </row>
     <row r="276" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A276" s="0" t="s">
+      <c r="A276" s="1" t="s">
         <v>277</v>
       </c>
       <c r="B276" s="5" t="n">
@@ -4431,7 +4478,7 @@
       </c>
     </row>
     <row r="277" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A277" s="0" t="s">
+      <c r="A277" s="1" t="s">
         <v>278</v>
       </c>
       <c r="B277" s="5" t="n">
@@ -4442,19 +4489,19 @@
       </c>
     </row>
     <row r="278" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A278" s="0" t="s">
+      <c r="A278" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="B278" s="0"/>
+      <c r="B278" s="1"/>
     </row>
     <row r="279" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A279" s="0" t="s">
+      <c r="A279" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="B279" s="0"/>
+      <c r="B279" s="1"/>
     </row>
     <row r="280" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A280" s="0" t="s">
+      <c r="A280" s="1" t="s">
         <v>281</v>
       </c>
       <c r="B280" s="5" t="n">
@@ -4465,7 +4512,7 @@
       </c>
     </row>
     <row r="281" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A281" s="0" t="s">
+      <c r="A281" s="1" t="s">
         <v>282</v>
       </c>
       <c r="B281" s="5" t="n">
@@ -4476,7 +4523,7 @@
       </c>
     </row>
     <row r="282" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A282" s="0" t="s">
+      <c r="A282" s="1" t="s">
         <v>283</v>
       </c>
       <c r="B282" s="5" t="n">
@@ -4487,7 +4534,7 @@
       </c>
     </row>
     <row r="283" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A283" s="0" t="s">
+      <c r="A283" s="1" t="s">
         <v>284</v>
       </c>
       <c r="B283" s="5" t="n">
@@ -4498,7 +4545,7 @@
       </c>
     </row>
     <row r="284" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A284" s="0" t="s">
+      <c r="A284" s="1" t="s">
         <v>285</v>
       </c>
       <c r="B284" s="5" t="n">
@@ -4509,19 +4556,19 @@
       </c>
     </row>
     <row r="285" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A285" s="0" t="s">
+      <c r="A285" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="B285" s="0"/>
+      <c r="B285" s="1"/>
     </row>
     <row r="286" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A286" s="0" t="s">
+      <c r="A286" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="B286" s="0"/>
+      <c r="B286" s="1"/>
     </row>
     <row r="287" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A287" s="0" t="s">
+      <c r="A287" s="1" t="s">
         <v>288</v>
       </c>
       <c r="B287" s="5" t="n">
@@ -4532,7 +4579,7 @@
       </c>
     </row>
     <row r="288" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A288" s="0" t="s">
+      <c r="A288" s="1" t="s">
         <v>289</v>
       </c>
       <c r="B288" s="5" t="n">
@@ -4543,7 +4590,7 @@
       </c>
     </row>
     <row r="289" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A289" s="0" t="s">
+      <c r="A289" s="1" t="s">
         <v>290</v>
       </c>
       <c r="B289" s="5" t="n">
@@ -4554,7 +4601,7 @@
       </c>
     </row>
     <row r="290" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A290" s="0" t="s">
+      <c r="A290" s="1" t="s">
         <v>291</v>
       </c>
       <c r="B290" s="5" t="n">
@@ -4565,7 +4612,7 @@
       </c>
     </row>
     <row r="291" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A291" s="0" t="s">
+      <c r="A291" s="1" t="s">
         <v>292</v>
       </c>
       <c r="B291" s="5" t="n">
@@ -4576,19 +4623,19 @@
       </c>
     </row>
     <row r="292" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A292" s="0" t="s">
+      <c r="A292" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="B292" s="0"/>
+      <c r="B292" s="1"/>
     </row>
     <row r="293" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A293" s="0" t="s">
+      <c r="A293" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="B293" s="0"/>
+      <c r="B293" s="1"/>
     </row>
     <row r="294" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A294" s="0" t="s">
+      <c r="A294" s="1" t="s">
         <v>295</v>
       </c>
       <c r="B294" s="5" t="n">
@@ -4599,7 +4646,7 @@
       </c>
     </row>
     <row r="295" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A295" s="0" t="s">
+      <c r="A295" s="1" t="s">
         <v>296</v>
       </c>
       <c r="B295" s="5" t="n">
@@ -4610,7 +4657,7 @@
       </c>
     </row>
     <row r="296" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A296" s="0" t="s">
+      <c r="A296" s="1" t="s">
         <v>297</v>
       </c>
       <c r="B296" s="5" t="n">
@@ -4621,7 +4668,7 @@
       </c>
     </row>
     <row r="297" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A297" s="0" t="s">
+      <c r="A297" s="1" t="s">
         <v>298</v>
       </c>
       <c r="B297" s="5" t="n">
@@ -4632,7 +4679,7 @@
       </c>
     </row>
     <row r="298" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A298" s="0" t="s">
+      <c r="A298" s="1" t="s">
         <v>299</v>
       </c>
       <c r="B298" s="5" t="n">
@@ -4643,19 +4690,19 @@
       </c>
     </row>
     <row r="299" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A299" s="0" t="s">
+      <c r="A299" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="B299" s="0"/>
+      <c r="B299" s="1"/>
     </row>
     <row r="300" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A300" s="0" t="s">
+      <c r="A300" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="B300" s="0"/>
+      <c r="B300" s="1"/>
     </row>
     <row r="301" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A301" s="0" t="s">
+      <c r="A301" s="1" t="s">
         <v>302</v>
       </c>
       <c r="B301" s="5" t="n">
@@ -4666,7 +4713,7 @@
       </c>
     </row>
     <row r="302" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A302" s="0" t="s">
+      <c r="A302" s="1" t="s">
         <v>303</v>
       </c>
       <c r="B302" s="5" t="n">
@@ -4677,13 +4724,13 @@
       </c>
     </row>
     <row r="303" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A303" s="0" t="s">
+      <c r="A303" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="B303" s="0"/>
+      <c r="B303" s="1"/>
     </row>
     <row r="304" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A304" s="0" t="s">
+      <c r="A304" s="1" t="s">
         <v>305</v>
       </c>
       <c r="B304" s="5" t="n">
@@ -4694,7 +4741,7 @@
       </c>
     </row>
     <row r="305" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A305" s="0" t="s">
+      <c r="A305" s="1" t="s">
         <v>306</v>
       </c>
       <c r="B305" s="5" t="n">
@@ -4705,19 +4752,19 @@
       </c>
     </row>
     <row r="306" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A306" s="0" t="s">
+      <c r="A306" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="B306" s="0"/>
+      <c r="B306" s="1"/>
     </row>
     <row r="307" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A307" s="0" t="s">
+      <c r="A307" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="B307" s="0"/>
+      <c r="B307" s="1"/>
     </row>
     <row r="308" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A308" s="0" t="s">
+      <c r="A308" s="1" t="s">
         <v>309</v>
       </c>
       <c r="B308" s="5" t="n">
@@ -4728,7 +4775,7 @@
       </c>
     </row>
     <row r="309" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A309" s="0" t="s">
+      <c r="A309" s="1" t="s">
         <v>310</v>
       </c>
       <c r="B309" s="5" t="n">
@@ -4739,7 +4786,7 @@
       </c>
     </row>
     <row r="310" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A310" s="0" t="s">
+      <c r="A310" s="1" t="s">
         <v>311</v>
       </c>
       <c r="B310" s="5" t="n">
@@ -4750,7 +4797,7 @@
       </c>
     </row>
     <row r="311" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A311" s="0" t="s">
+      <c r="A311" s="1" t="s">
         <v>312</v>
       </c>
       <c r="B311" s="5" t="n">
@@ -4761,7 +4808,7 @@
       </c>
     </row>
     <row r="312" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A312" s="0" t="s">
+      <c r="A312" s="1" t="s">
         <v>313</v>
       </c>
       <c r="B312" s="5" t="n">
@@ -4772,19 +4819,19 @@
       </c>
     </row>
     <row r="313" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A313" s="0" t="s">
+      <c r="A313" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="B313" s="0"/>
+      <c r="B313" s="1"/>
     </row>
     <row r="314" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A314" s="0" t="s">
+      <c r="A314" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="B314" s="0"/>
+      <c r="B314" s="1"/>
     </row>
     <row r="315" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A315" s="0" t="s">
+      <c r="A315" s="1" t="s">
         <v>316</v>
       </c>
       <c r="B315" s="5" t="n">
@@ -4795,7 +4842,7 @@
       </c>
     </row>
     <row r="316" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A316" s="0" t="s">
+      <c r="A316" s="1" t="s">
         <v>317</v>
       </c>
       <c r="B316" s="5" t="n">
@@ -4806,7 +4853,7 @@
       </c>
     </row>
     <row r="317" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A317" s="0" t="s">
+      <c r="A317" s="1" t="s">
         <v>318</v>
       </c>
       <c r="B317" s="5" t="n">
@@ -4817,7 +4864,7 @@
       </c>
     </row>
     <row r="318" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A318" s="0" t="s">
+      <c r="A318" s="1" t="s">
         <v>319</v>
       </c>
       <c r="B318" s="5" t="n">
@@ -4828,7 +4875,7 @@
       </c>
     </row>
     <row r="319" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A319" s="0" t="s">
+      <c r="A319" s="1" t="s">
         <v>320</v>
       </c>
       <c r="B319" s="5" t="n">
@@ -4839,19 +4886,19 @@
       </c>
     </row>
     <row r="320" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A320" s="0" t="s">
+      <c r="A320" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="B320" s="0"/>
+      <c r="B320" s="1"/>
     </row>
     <row r="321" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A321" s="0" t="s">
+      <c r="A321" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="B321" s="0"/>
+      <c r="B321" s="1"/>
     </row>
     <row r="322" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A322" s="0" t="s">
+      <c r="A322" s="1" t="s">
         <v>323</v>
       </c>
       <c r="B322" s="5" t="n">
@@ -4862,7 +4909,7 @@
       </c>
     </row>
     <row r="323" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A323" s="0" t="s">
+      <c r="A323" s="1" t="s">
         <v>324</v>
       </c>
       <c r="B323" s="5" t="n">
@@ -4873,7 +4920,7 @@
       </c>
     </row>
     <row r="324" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A324" s="0" t="s">
+      <c r="A324" s="1" t="s">
         <v>325</v>
       </c>
       <c r="B324" s="5" t="n">
@@ -4884,7 +4931,7 @@
       </c>
     </row>
     <row r="325" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A325" s="0" t="s">
+      <c r="A325" s="1" t="s">
         <v>326</v>
       </c>
       <c r="B325" s="5" t="n">
@@ -4895,7 +4942,7 @@
       </c>
     </row>
     <row r="326" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A326" s="0" t="s">
+      <c r="A326" s="1" t="s">
         <v>327</v>
       </c>
       <c r="B326" s="5" t="n">
@@ -4906,19 +4953,19 @@
       </c>
     </row>
     <row r="327" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A327" s="0" t="s">
+      <c r="A327" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="B327" s="0"/>
+      <c r="B327" s="1"/>
     </row>
     <row r="328" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A328" s="0" t="s">
+      <c r="A328" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="B328" s="0"/>
+      <c r="B328" s="1"/>
     </row>
     <row r="329" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A329" s="0" t="s">
+      <c r="A329" s="1" t="s">
         <v>330</v>
       </c>
       <c r="B329" s="5" t="n">
@@ -4929,7 +4976,7 @@
       </c>
     </row>
     <row r="330" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A330" s="0" t="s">
+      <c r="A330" s="1" t="s">
         <v>331</v>
       </c>
       <c r="B330" s="5" t="n">
@@ -4940,7 +4987,7 @@
       </c>
     </row>
     <row r="331" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A331" s="0" t="s">
+      <c r="A331" s="1" t="s">
         <v>332</v>
       </c>
       <c r="B331" s="5" t="n">
@@ -4951,7 +4998,7 @@
       </c>
     </row>
     <row r="332" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A332" s="0" t="s">
+      <c r="A332" s="1" t="s">
         <v>333</v>
       </c>
       <c r="B332" s="5" t="n">
@@ -4962,7 +5009,7 @@
       </c>
     </row>
     <row r="333" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A333" s="0" t="s">
+      <c r="A333" s="1" t="s">
         <v>334</v>
       </c>
       <c r="B333" s="5" t="n">
@@ -4973,19 +5020,19 @@
       </c>
     </row>
     <row r="334" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A334" s="0" t="s">
+      <c r="A334" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="B334" s="0"/>
+      <c r="B334" s="1"/>
     </row>
     <row r="335" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A335" s="0" t="s">
+      <c r="A335" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="B335" s="0"/>
+      <c r="B335" s="1"/>
     </row>
     <row r="336" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A336" s="0" t="s">
+      <c r="A336" s="1" t="s">
         <v>337</v>
       </c>
       <c r="B336" s="5" t="n">
@@ -4996,7 +5043,7 @@
       </c>
     </row>
     <row r="337" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A337" s="0" t="s">
+      <c r="A337" s="1" t="s">
         <v>338</v>
       </c>
       <c r="B337" s="5" t="n">
@@ -5007,7 +5054,7 @@
       </c>
     </row>
     <row r="338" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A338" s="0" t="s">
+      <c r="A338" s="1" t="s">
         <v>339</v>
       </c>
       <c r="B338" s="5" t="n">
@@ -5018,7 +5065,7 @@
       </c>
     </row>
     <row r="339" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A339" s="0" t="s">
+      <c r="A339" s="1" t="s">
         <v>340</v>
       </c>
       <c r="B339" s="5" t="n">
@@ -5029,7 +5076,7 @@
       </c>
     </row>
     <row r="340" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A340" s="0" t="s">
+      <c r="A340" s="1" t="s">
         <v>341</v>
       </c>
       <c r="B340" s="5" t="n">
@@ -5040,19 +5087,19 @@
       </c>
     </row>
     <row r="341" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A341" s="0" t="s">
+      <c r="A341" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="B341" s="0"/>
+      <c r="B341" s="1"/>
     </row>
     <row r="342" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A342" s="0" t="s">
+      <c r="A342" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="B342" s="0"/>
+      <c r="B342" s="1"/>
     </row>
     <row r="343" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A343" s="0" t="s">
+      <c r="A343" s="1" t="s">
         <v>344</v>
       </c>
       <c r="B343" s="5" t="n">
@@ -5063,7 +5110,7 @@
       </c>
     </row>
     <row r="344" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A344" s="0" t="s">
+      <c r="A344" s="1" t="s">
         <v>345</v>
       </c>
       <c r="B344" s="5" t="n">
@@ -5074,7 +5121,7 @@
       </c>
     </row>
     <row r="345" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A345" s="0" t="s">
+      <c r="A345" s="1" t="s">
         <v>346</v>
       </c>
       <c r="B345" s="5" t="n">
@@ -5085,7 +5132,7 @@
       </c>
     </row>
     <row r="346" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A346" s="0" t="s">
+      <c r="A346" s="1" t="s">
         <v>347</v>
       </c>
       <c r="B346" s="5" t="n">
@@ -5096,7 +5143,7 @@
       </c>
     </row>
     <row r="347" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A347" s="0" t="s">
+      <c r="A347" s="1" t="s">
         <v>348</v>
       </c>
       <c r="B347" s="5" t="n">
@@ -5107,19 +5154,19 @@
       </c>
     </row>
     <row r="348" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A348" s="0" t="s">
+      <c r="A348" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="B348" s="0"/>
+      <c r="B348" s="1"/>
     </row>
     <row r="349" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A349" s="0" t="s">
+      <c r="A349" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="B349" s="0"/>
+      <c r="B349" s="1"/>
     </row>
     <row r="350" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A350" s="0" t="s">
+      <c r="A350" s="1" t="s">
         <v>351</v>
       </c>
       <c r="B350" s="5" t="n">
@@ -5130,7 +5177,7 @@
       </c>
     </row>
     <row r="351" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A351" s="0" t="s">
+      <c r="A351" s="1" t="s">
         <v>352</v>
       </c>
       <c r="B351" s="5" t="n">
@@ -5141,7 +5188,7 @@
       </c>
     </row>
     <row r="352" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A352" s="0" t="s">
+      <c r="A352" s="1" t="s">
         <v>353</v>
       </c>
       <c r="B352" s="5" t="n">
@@ -5152,7 +5199,7 @@
       </c>
     </row>
     <row r="353" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A353" s="0" t="s">
+      <c r="A353" s="1" t="s">
         <v>354</v>
       </c>
       <c r="B353" s="5" t="n">
@@ -5163,7 +5210,7 @@
       </c>
     </row>
     <row r="354" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A354" s="0" t="s">
+      <c r="A354" s="1" t="s">
         <v>355</v>
       </c>
       <c r="B354" s="5" t="n">
@@ -5174,19 +5221,19 @@
       </c>
     </row>
     <row r="355" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A355" s="0" t="s">
+      <c r="A355" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="B355" s="0"/>
+      <c r="B355" s="1"/>
     </row>
     <row r="356" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A356" s="0" t="s">
+      <c r="A356" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="B356" s="0"/>
+      <c r="B356" s="1"/>
     </row>
     <row r="357" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A357" s="0" t="s">
+      <c r="A357" s="1" t="s">
         <v>358</v>
       </c>
       <c r="B357" s="5" t="n">
@@ -5197,7 +5244,7 @@
       </c>
     </row>
     <row r="358" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A358" s="0" t="s">
+      <c r="A358" s="1" t="s">
         <v>359</v>
       </c>
       <c r="B358" s="5" t="n">
@@ -5208,7 +5255,7 @@
       </c>
     </row>
     <row r="359" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A359" s="0" t="s">
+      <c r="A359" s="1" t="s">
         <v>360</v>
       </c>
       <c r="B359" s="5" t="n">
@@ -5219,7 +5266,7 @@
       </c>
     </row>
     <row r="360" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A360" s="0" t="s">
+      <c r="A360" s="1" t="s">
         <v>361</v>
       </c>
       <c r="B360" s="5" t="n">
@@ -5230,7 +5277,7 @@
       </c>
     </row>
     <row r="361" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A361" s="0" t="s">
+      <c r="A361" s="1" t="s">
         <v>362</v>
       </c>
       <c r="B361" s="5" t="n">
@@ -5241,19 +5288,19 @@
       </c>
     </row>
     <row r="362" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A362" s="0" t="s">
+      <c r="A362" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="B362" s="0"/>
+      <c r="B362" s="1"/>
     </row>
     <row r="363" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A363" s="0" t="s">
+      <c r="A363" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="B363" s="0"/>
+      <c r="B363" s="1"/>
     </row>
     <row r="364" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A364" s="0" t="s">
+      <c r="A364" s="1" t="s">
         <v>365</v>
       </c>
       <c r="B364" s="5" t="n">
@@ -5264,7 +5311,7 @@
       </c>
     </row>
     <row r="365" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A365" s="0" t="s">
+      <c r="A365" s="1" t="s">
         <v>366</v>
       </c>
       <c r="B365" s="5" t="n">
@@ -5275,7 +5322,7 @@
       </c>
     </row>
     <row r="366" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A366" s="0" t="s">
+      <c r="A366" s="1" t="s">
         <v>367</v>
       </c>
       <c r="B366" s="5" t="n">
@@ -5286,13 +5333,13 @@
       </c>
     </row>
     <row r="367" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A367" s="0" t="s">
+      <c r="A367" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="B367" s="0"/>
+      <c r="B367" s="1"/>
     </row>
     <row r="368" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A368" s="0" t="s">
+      <c r="A368" s="1" t="s">
         <v>369</v>
       </c>
       <c r="B368" s="5" t="n">
@@ -5303,19 +5350,19 @@
       </c>
     </row>
     <row r="369" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A369" s="0" t="s">
+      <c r="A369" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="B369" s="0"/>
+      <c r="B369" s="1"/>
     </row>
     <row r="370" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A370" s="0" t="s">
+      <c r="A370" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="B370" s="0"/>
+      <c r="B370" s="1"/>
     </row>
     <row r="371" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A371" s="0" t="s">
+      <c r="A371" s="1" t="s">
         <v>372</v>
       </c>
       <c r="B371" s="5" t="n">
@@ -5326,7 +5373,7 @@
       </c>
     </row>
     <row r="372" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A372" s="0" t="s">
+      <c r="A372" s="1" t="s">
         <v>373</v>
       </c>
       <c r="B372" s="5" t="n">
@@ -5337,7 +5384,7 @@
       </c>
     </row>
     <row r="373" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A373" s="0" t="s">
+      <c r="A373" s="1" t="s">
         <v>374</v>
       </c>
       <c r="B373" s="5" t="n">
@@ -5348,7 +5395,7 @@
       </c>
     </row>
     <row r="374" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A374" s="0" t="s">
+      <c r="A374" s="1" t="s">
         <v>375</v>
       </c>
       <c r="B374" s="5" t="n">
@@ -5359,7 +5406,7 @@
       </c>
     </row>
     <row r="375" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A375" s="0" t="s">
+      <c r="A375" s="1" t="s">
         <v>376</v>
       </c>
       <c r="B375" s="5" t="n">
@@ -5370,19 +5417,19 @@
       </c>
     </row>
     <row r="376" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A376" s="0" t="s">
+      <c r="A376" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="B376" s="0"/>
+      <c r="B376" s="1"/>
     </row>
     <row r="377" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A377" s="0" t="s">
+      <c r="A377" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="B377" s="0"/>
+      <c r="B377" s="1"/>
     </row>
     <row r="378" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A378" s="0" t="s">
+      <c r="A378" s="1" t="s">
         <v>379</v>
       </c>
       <c r="B378" s="5" t="n">
@@ -5393,7 +5440,7 @@
       </c>
     </row>
     <row r="379" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A379" s="0" t="s">
+      <c r="A379" s="1" t="s">
         <v>380</v>
       </c>
       <c r="B379" s="5" t="n">
@@ -5404,7 +5451,7 @@
       </c>
     </row>
     <row r="380" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A380" s="0" t="s">
+      <c r="A380" s="1" t="s">
         <v>381</v>
       </c>
       <c r="B380" s="5" t="n">
@@ -5415,7 +5462,7 @@
       </c>
     </row>
     <row r="381" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A381" s="0" t="s">
+      <c r="A381" s="1" t="s">
         <v>382</v>
       </c>
       <c r="B381" s="5" t="n">
@@ -5426,7 +5473,7 @@
       </c>
     </row>
     <row r="382" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A382" s="0" t="s">
+      <c r="A382" s="1" t="s">
         <v>383</v>
       </c>
       <c r="B382" s="5" t="n">
@@ -5437,19 +5484,19 @@
       </c>
     </row>
     <row r="383" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A383" s="0" t="s">
+      <c r="A383" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="B383" s="0"/>
+      <c r="B383" s="1"/>
     </row>
     <row r="384" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A384" s="0" t="s">
+      <c r="A384" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="B384" s="0"/>
+      <c r="B384" s="1"/>
     </row>
     <row r="385" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A385" s="0" t="s">
+      <c r="A385" s="1" t="s">
         <v>386</v>
       </c>
       <c r="B385" s="5" t="n">
@@ -5460,7 +5507,7 @@
       </c>
     </row>
     <row r="386" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A386" s="0" t="s">
+      <c r="A386" s="1" t="s">
         <v>387</v>
       </c>
       <c r="B386" s="5" t="n">
@@ -5471,7 +5518,7 @@
       </c>
     </row>
     <row r="387" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A387" s="0" t="s">
+      <c r="A387" s="1" t="s">
         <v>388</v>
       </c>
       <c r="B387" s="5" t="n">
@@ -5482,7 +5529,7 @@
       </c>
     </row>
     <row r="388" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A388" s="0" t="s">
+      <c r="A388" s="1" t="s">
         <v>389</v>
       </c>
       <c r="B388" s="5" t="n">
@@ -5493,7 +5540,7 @@
       </c>
     </row>
     <row r="389" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A389" s="0" t="s">
+      <c r="A389" s="1" t="s">
         <v>390</v>
       </c>
       <c r="B389" s="5" t="n">
@@ -5504,19 +5551,19 @@
       </c>
     </row>
     <row r="390" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A390" s="0" t="s">
+      <c r="A390" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="B390" s="0"/>
+      <c r="B390" s="1"/>
     </row>
     <row r="391" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A391" s="0" t="s">
+      <c r="A391" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="B391" s="0"/>
+      <c r="B391" s="1"/>
     </row>
     <row r="392" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A392" s="0" t="s">
+      <c r="A392" s="1" t="s">
         <v>393</v>
       </c>
       <c r="B392" s="5" t="n">
@@ -5527,7 +5574,7 @@
       </c>
     </row>
     <row r="393" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A393" s="0" t="s">
+      <c r="A393" s="1" t="s">
         <v>394</v>
       </c>
       <c r="B393" s="5" t="n">
@@ -5538,7 +5585,7 @@
       </c>
     </row>
     <row r="394" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A394" s="0" t="s">
+      <c r="A394" s="1" t="s">
         <v>395</v>
       </c>
       <c r="B394" s="5" t="n">
@@ -5549,7 +5596,7 @@
       </c>
     </row>
     <row r="395" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A395" s="0" t="s">
+      <c r="A395" s="1" t="s">
         <v>396</v>
       </c>
       <c r="B395" s="5" t="n">
@@ -5560,7 +5607,7 @@
       </c>
     </row>
     <row r="396" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A396" s="0" t="s">
+      <c r="A396" s="1" t="s">
         <v>397</v>
       </c>
       <c r="B396" s="5" t="n">
@@ -5571,19 +5618,19 @@
       </c>
     </row>
     <row r="397" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A397" s="0" t="s">
+      <c r="A397" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="B397" s="0"/>
+      <c r="B397" s="1"/>
     </row>
     <row r="398" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A398" s="0" t="s">
+      <c r="A398" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="B398" s="0"/>
+      <c r="B398" s="1"/>
     </row>
     <row r="399" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A399" s="0" t="s">
+      <c r="A399" s="1" t="s">
         <v>400</v>
       </c>
       <c r="B399" s="5" t="n">
@@ -5594,7 +5641,7 @@
       </c>
     </row>
     <row r="400" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A400" s="0" t="s">
+      <c r="A400" s="1" t="s">
         <v>401</v>
       </c>
       <c r="B400" s="5" t="n">
@@ -5605,7 +5652,7 @@
       </c>
     </row>
     <row r="401" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A401" s="0" t="s">
+      <c r="A401" s="1" t="s">
         <v>402</v>
       </c>
       <c r="B401" s="5" t="n">
@@ -5616,7 +5663,7 @@
       </c>
     </row>
     <row r="402" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A402" s="0" t="s">
+      <c r="A402" s="1" t="s">
         <v>403</v>
       </c>
       <c r="B402" s="5" t="n">
@@ -5627,7 +5674,7 @@
       </c>
     </row>
     <row r="403" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A403" s="0" t="s">
+      <c r="A403" s="1" t="s">
         <v>404</v>
       </c>
       <c r="B403" s="5" t="n">
@@ -5638,19 +5685,19 @@
       </c>
     </row>
     <row r="404" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A404" s="0" t="s">
+      <c r="A404" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="B404" s="0"/>
+      <c r="B404" s="1"/>
     </row>
     <row r="405" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A405" s="0" t="s">
+      <c r="A405" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="B405" s="0"/>
+      <c r="B405" s="1"/>
     </row>
     <row r="406" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A406" s="0" t="s">
+      <c r="A406" s="1" t="s">
         <v>407</v>
       </c>
       <c r="B406" s="5" t="n">
@@ -5661,7 +5708,7 @@
       </c>
     </row>
     <row r="407" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A407" s="0" t="s">
+      <c r="A407" s="1" t="s">
         <v>408</v>
       </c>
       <c r="B407" s="5" t="n">
@@ -5672,7 +5719,7 @@
       </c>
     </row>
     <row r="408" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A408" s="0" t="s">
+      <c r="A408" s="1" t="s">
         <v>409</v>
       </c>
       <c r="B408" s="5" t="n">
@@ -5683,7 +5730,7 @@
       </c>
     </row>
     <row r="409" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A409" s="0" t="s">
+      <c r="A409" s="1" t="s">
         <v>410</v>
       </c>
       <c r="B409" s="5" t="n">
@@ -5694,7 +5741,7 @@
       </c>
     </row>
     <row r="410" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A410" s="0" t="s">
+      <c r="A410" s="1" t="s">
         <v>411</v>
       </c>
       <c r="B410" s="5" t="n">
@@ -5705,19 +5752,19 @@
       </c>
     </row>
     <row r="411" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A411" s="0" t="s">
+      <c r="A411" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="B411" s="0"/>
+      <c r="B411" s="1"/>
     </row>
     <row r="412" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A412" s="0" t="s">
+      <c r="A412" s="1" t="s">
         <v>413</v>
       </c>
-      <c r="B412" s="0"/>
+      <c r="B412" s="1"/>
     </row>
     <row r="413" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A413" s="0" t="s">
+      <c r="A413" s="1" t="s">
         <v>414</v>
       </c>
       <c r="B413" s="5" t="n">
@@ -5728,7 +5775,7 @@
       </c>
     </row>
     <row r="414" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A414" s="0" t="s">
+      <c r="A414" s="1" t="s">
         <v>415</v>
       </c>
       <c r="B414" s="5" t="n">
@@ -5739,7 +5786,7 @@
       </c>
     </row>
     <row r="415" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A415" s="0" t="s">
+      <c r="A415" s="1" t="s">
         <v>416</v>
       </c>
       <c r="B415" s="5" t="n">
@@ -5750,7 +5797,7 @@
       </c>
     </row>
     <row r="416" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A416" s="0" t="s">
+      <c r="A416" s="1" t="s">
         <v>417</v>
       </c>
       <c r="B416" s="5" t="n">
@@ -5761,7 +5808,7 @@
       </c>
     </row>
     <row r="417" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A417" s="0" t="s">
+      <c r="A417" s="1" t="s">
         <v>418</v>
       </c>
       <c r="B417" s="5" t="n">
@@ -5772,19 +5819,19 @@
       </c>
     </row>
     <row r="418" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A418" s="0" t="s">
+      <c r="A418" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="B418" s="0"/>
+      <c r="B418" s="1"/>
     </row>
     <row r="419" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A419" s="0" t="s">
+      <c r="A419" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="B419" s="0"/>
+      <c r="B419" s="1"/>
     </row>
     <row r="420" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A420" s="0" t="s">
+      <c r="A420" s="1" t="s">
         <v>421</v>
       </c>
       <c r="B420" s="5" t="n">
@@ -5795,7 +5842,7 @@
       </c>
     </row>
     <row r="421" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A421" s="0" t="s">
+      <c r="A421" s="1" t="s">
         <v>422</v>
       </c>
       <c r="B421" s="5" t="n">
@@ -5806,7 +5853,7 @@
       </c>
     </row>
     <row r="422" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A422" s="0" t="s">
+      <c r="A422" s="1" t="s">
         <v>423</v>
       </c>
       <c r="B422" s="5" t="n">
@@ -5817,7 +5864,7 @@
       </c>
     </row>
     <row r="423" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A423" s="0" t="s">
+      <c r="A423" s="1" t="s">
         <v>424</v>
       </c>
       <c r="B423" s="5" t="n">
@@ -5828,7 +5875,7 @@
       </c>
     </row>
     <row r="424" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A424" s="0" t="s">
+      <c r="A424" s="1" t="s">
         <v>425</v>
       </c>
       <c r="B424" s="5" t="n">
@@ -5839,19 +5886,19 @@
       </c>
     </row>
     <row r="425" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A425" s="0" t="s">
+      <c r="A425" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="B425" s="0"/>
+      <c r="B425" s="1"/>
     </row>
     <row r="426" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A426" s="0" t="s">
+      <c r="A426" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="B426" s="0"/>
+      <c r="B426" s="1"/>
     </row>
     <row r="427" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A427" s="0" t="s">
+      <c r="A427" s="1" t="s">
         <v>428</v>
       </c>
       <c r="B427" s="5" t="n">
@@ -5862,7 +5909,7 @@
       </c>
     </row>
     <row r="428" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A428" s="0" t="s">
+      <c r="A428" s="1" t="s">
         <v>429</v>
       </c>
       <c r="B428" s="5" t="n">
@@ -5873,7 +5920,7 @@
       </c>
     </row>
     <row r="429" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A429" s="0" t="s">
+      <c r="A429" s="1" t="s">
         <v>430</v>
       </c>
       <c r="B429" s="5" t="n">
@@ -5884,7 +5931,7 @@
       </c>
     </row>
     <row r="430" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A430" s="0" t="s">
+      <c r="A430" s="1" t="s">
         <v>431</v>
       </c>
       <c r="B430" s="5" t="n">
@@ -5895,7 +5942,7 @@
       </c>
     </row>
     <row r="431" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A431" s="0" t="s">
+      <c r="A431" s="1" t="s">
         <v>432</v>
       </c>
       <c r="B431" s="5" t="n">
@@ -5906,19 +5953,19 @@
       </c>
     </row>
     <row r="432" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A432" s="0" t="s">
+      <c r="A432" s="1" t="s">
         <v>433</v>
       </c>
-      <c r="B432" s="0"/>
+      <c r="B432" s="1"/>
     </row>
     <row r="433" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A433" s="0" t="s">
+      <c r="A433" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="B433" s="0"/>
+      <c r="B433" s="1"/>
     </row>
     <row r="434" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A434" s="0" t="s">
+      <c r="A434" s="1" t="s">
         <v>435</v>
       </c>
       <c r="B434" s="5" t="n">
@@ -5929,7 +5976,7 @@
       </c>
     </row>
     <row r="435" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A435" s="0" t="s">
+      <c r="A435" s="1" t="s">
         <v>436</v>
       </c>
       <c r="B435" s="5" t="n">
@@ -5940,7 +5987,7 @@
       </c>
     </row>
     <row r="436" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A436" s="0" t="s">
+      <c r="A436" s="1" t="s">
         <v>437</v>
       </c>
       <c r="B436" s="5" t="n">
@@ -5951,7 +5998,7 @@
       </c>
     </row>
     <row r="437" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A437" s="0" t="s">
+      <c r="A437" s="1" t="s">
         <v>438</v>
       </c>
       <c r="B437" s="5" t="n">
@@ -5962,7 +6009,7 @@
       </c>
     </row>
     <row r="438" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A438" s="0" t="s">
+      <c r="A438" s="1" t="s">
         <v>439</v>
       </c>
       <c r="B438" s="5" t="n">
@@ -5973,19 +6020,19 @@
       </c>
     </row>
     <row r="439" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A439" s="0" t="s">
+      <c r="A439" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="B439" s="0"/>
+      <c r="B439" s="1"/>
     </row>
     <row r="440" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A440" s="0" t="s">
+      <c r="A440" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="B440" s="0"/>
+      <c r="B440" s="1"/>
     </row>
     <row r="441" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A441" s="0" t="s">
+      <c r="A441" s="1" t="s">
         <v>442</v>
       </c>
       <c r="B441" s="5" t="n">
@@ -5996,7 +6043,7 @@
       </c>
     </row>
     <row r="442" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A442" s="0" t="s">
+      <c r="A442" s="1" t="s">
         <v>443</v>
       </c>
       <c r="B442" s="5" t="n">
@@ -6007,7 +6054,7 @@
       </c>
     </row>
     <row r="443" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A443" s="0" t="s">
+      <c r="A443" s="1" t="s">
         <v>444</v>
       </c>
       <c r="B443" s="5" t="n">
@@ -6018,7 +6065,7 @@
       </c>
     </row>
     <row r="444" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A444" s="0" t="s">
+      <c r="A444" s="1" t="s">
         <v>445</v>
       </c>
       <c r="B444" s="5" t="n">
@@ -6029,25 +6076,25 @@
       </c>
     </row>
     <row r="445" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A445" s="0" t="s">
+      <c r="A445" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="B445" s="0"/>
+      <c r="B445" s="1"/>
     </row>
     <row r="446" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A446" s="0" t="s">
+      <c r="A446" s="1" t="s">
         <v>447</v>
       </c>
-      <c r="B446" s="0"/>
+      <c r="B446" s="1"/>
     </row>
     <row r="447" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A447" s="0" t="s">
+      <c r="A447" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="B447" s="0"/>
+      <c r="B447" s="1"/>
     </row>
     <row r="448" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A448" s="0" t="s">
+      <c r="A448" s="1" t="s">
         <v>449</v>
       </c>
       <c r="B448" s="5" t="n">
@@ -6058,7 +6105,7 @@
       </c>
     </row>
     <row r="449" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A449" s="0" t="s">
+      <c r="A449" s="1" t="s">
         <v>450</v>
       </c>
       <c r="B449" s="5" t="n">
@@ -6069,7 +6116,7 @@
       </c>
     </row>
     <row r="450" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A450" s="0" t="s">
+      <c r="A450" s="1" t="s">
         <v>451</v>
       </c>
       <c r="B450" s="5" t="n">
@@ -6080,7 +6127,7 @@
       </c>
     </row>
     <row r="451" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A451" s="0" t="s">
+      <c r="A451" s="1" t="s">
         <v>452</v>
       </c>
       <c r="B451" s="5" t="n">
@@ -6091,7 +6138,7 @@
       </c>
     </row>
     <row r="452" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A452" s="0" t="s">
+      <c r="A452" s="1" t="s">
         <v>453</v>
       </c>
       <c r="B452" s="5" t="n">
@@ -6102,19 +6149,19 @@
       </c>
     </row>
     <row r="453" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A453" s="0" t="s">
+      <c r="A453" s="1" t="s">
         <v>454</v>
       </c>
-      <c r="B453" s="0"/>
+      <c r="B453" s="1"/>
     </row>
     <row r="454" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A454" s="0" t="s">
+      <c r="A454" s="1" t="s">
         <v>455</v>
       </c>
-      <c r="B454" s="0"/>
+      <c r="B454" s="1"/>
     </row>
     <row r="455" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A455" s="0" t="s">
+      <c r="A455" s="1" t="s">
         <v>456</v>
       </c>
       <c r="B455" s="5" t="n">
@@ -6125,7 +6172,7 @@
       </c>
     </row>
     <row r="456" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A456" s="0" t="s">
+      <c r="A456" s="1" t="s">
         <v>457</v>
       </c>
       <c r="B456" s="5" t="n">
@@ -6136,7 +6183,7 @@
       </c>
     </row>
     <row r="457" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A457" s="0" t="s">
+      <c r="A457" s="1" t="s">
         <v>458</v>
       </c>
       <c r="B457" s="5" t="n">
@@ -6147,7 +6194,7 @@
       </c>
     </row>
     <row r="458" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A458" s="0" t="s">
+      <c r="A458" s="1" t="s">
         <v>459</v>
       </c>
       <c r="B458" s="5" t="n">
@@ -6158,7 +6205,7 @@
       </c>
     </row>
     <row r="459" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A459" s="0" t="s">
+      <c r="A459" s="1" t="s">
         <v>460</v>
       </c>
       <c r="B459" s="5" t="n">
@@ -6169,19 +6216,19 @@
       </c>
     </row>
     <row r="460" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A460" s="0" t="s">
+      <c r="A460" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="B460" s="0"/>
+      <c r="B460" s="1"/>
     </row>
     <row r="461" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A461" s="0" t="s">
+      <c r="A461" s="1" t="s">
         <v>462</v>
       </c>
-      <c r="B461" s="0"/>
+      <c r="B461" s="1"/>
     </row>
     <row r="462" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A462" s="0" t="s">
+      <c r="A462" s="1" t="s">
         <v>463</v>
       </c>
       <c r="B462" s="5" t="n">
@@ -6192,7 +6239,7 @@
       </c>
     </row>
     <row r="463" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A463" s="0" t="s">
+      <c r="A463" s="1" t="s">
         <v>464</v>
       </c>
       <c r="B463" s="5" t="n">
@@ -6203,7 +6250,7 @@
       </c>
     </row>
     <row r="464" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A464" s="0" t="s">
+      <c r="A464" s="1" t="s">
         <v>465</v>
       </c>
       <c r="B464" s="5" t="n">
@@ -6214,7 +6261,7 @@
       </c>
     </row>
     <row r="465" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A465" s="0" t="s">
+      <c r="A465" s="1" t="s">
         <v>466</v>
       </c>
       <c r="B465" s="5" t="n">
@@ -6225,7 +6272,7 @@
       </c>
     </row>
     <row r="466" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A466" s="0" t="s">
+      <c r="A466" s="1" t="s">
         <v>467</v>
       </c>
       <c r="B466" s="5" t="n">
@@ -6236,19 +6283,19 @@
       </c>
     </row>
     <row r="467" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A467" s="0" t="s">
+      <c r="A467" s="1" t="s">
         <v>468</v>
       </c>
-      <c r="B467" s="0"/>
+      <c r="B467" s="1"/>
     </row>
     <row r="468" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A468" s="0" t="s">
+      <c r="A468" s="1" t="s">
         <v>469</v>
       </c>
-      <c r="B468" s="0"/>
+      <c r="B468" s="1"/>
     </row>
     <row r="469" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A469" s="0" t="s">
+      <c r="A469" s="1" t="s">
         <v>470</v>
       </c>
       <c r="B469" s="5" t="n">
@@ -6259,7 +6306,7 @@
       </c>
     </row>
     <row r="470" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A470" s="0" t="s">
+      <c r="A470" s="1" t="s">
         <v>471</v>
       </c>
       <c r="B470" s="5" t="n">
@@ -6270,7 +6317,7 @@
       </c>
     </row>
     <row r="471" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A471" s="0" t="s">
+      <c r="A471" s="1" t="s">
         <v>472</v>
       </c>
       <c r="B471" s="5" t="n">
@@ -6281,7 +6328,7 @@
       </c>
     </row>
     <row r="472" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A472" s="0" t="s">
+      <c r="A472" s="1" t="s">
         <v>473</v>
       </c>
       <c r="B472" s="5" t="n">
@@ -6292,7 +6339,7 @@
       </c>
     </row>
     <row r="473" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A473" s="0" t="s">
+      <c r="A473" s="1" t="s">
         <v>474</v>
       </c>
       <c r="B473" s="5" t="n">
@@ -6303,19 +6350,19 @@
       </c>
     </row>
     <row r="474" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A474" s="0" t="s">
+      <c r="A474" s="1" t="s">
         <v>475</v>
       </c>
-      <c r="B474" s="0"/>
+      <c r="B474" s="1"/>
     </row>
     <row r="475" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A475" s="0" t="s">
+      <c r="A475" s="1" t="s">
         <v>476</v>
       </c>
-      <c r="B475" s="0"/>
+      <c r="B475" s="1"/>
     </row>
     <row r="476" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A476" s="0" t="s">
+      <c r="A476" s="1" t="s">
         <v>477</v>
       </c>
       <c r="B476" s="5" t="n">
@@ -6326,7 +6373,7 @@
       </c>
     </row>
     <row r="477" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A477" s="0" t="s">
+      <c r="A477" s="1" t="s">
         <v>478</v>
       </c>
       <c r="B477" s="5" t="n">
@@ -6337,7 +6384,7 @@
       </c>
     </row>
     <row r="478" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A478" s="0" t="s">
+      <c r="A478" s="1" t="s">
         <v>479</v>
       </c>
       <c r="B478" s="5" t="n">
@@ -6348,13 +6395,13 @@
       </c>
     </row>
     <row r="479" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A479" s="0" t="s">
+      <c r="A479" s="1" t="s">
         <v>480</v>
       </c>
-      <c r="B479" s="0"/>
+      <c r="B479" s="1"/>
     </row>
     <row r="480" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A480" s="0" t="s">
+      <c r="A480" s="1" t="s">
         <v>481</v>
       </c>
       <c r="B480" s="5" t="n">
@@ -6365,19 +6412,19 @@
       </c>
     </row>
     <row r="481" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A481" s="0" t="s">
+      <c r="A481" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="B481" s="0"/>
+      <c r="B481" s="1"/>
     </row>
     <row r="482" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A482" s="0" t="s">
+      <c r="A482" s="1" t="s">
         <v>483</v>
       </c>
-      <c r="B482" s="0"/>
+      <c r="B482" s="1"/>
     </row>
     <row r="483" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A483" s="0" t="s">
+      <c r="A483" s="1" t="s">
         <v>484</v>
       </c>
       <c r="B483" s="5" t="n">
@@ -6388,7 +6435,7 @@
       </c>
     </row>
     <row r="484" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A484" s="0" t="s">
+      <c r="A484" s="1" t="s">
         <v>485</v>
       </c>
       <c r="B484" s="5" t="n">
@@ -6399,7 +6446,7 @@
       </c>
     </row>
     <row r="485" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A485" s="0" t="s">
+      <c r="A485" s="1" t="s">
         <v>486</v>
       </c>
       <c r="B485" s="5" t="n">
@@ -6410,7 +6457,7 @@
       </c>
     </row>
     <row r="486" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A486" s="0" t="s">
+      <c r="A486" s="1" t="s">
         <v>487</v>
       </c>
       <c r="B486" s="5" t="n">
@@ -6421,25 +6468,25 @@
       </c>
     </row>
     <row r="487" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A487" s="0" t="s">
+      <c r="A487" s="1" t="s">
         <v>488</v>
       </c>
-      <c r="B487" s="0"/>
+      <c r="B487" s="1"/>
     </row>
     <row r="488" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A488" s="0" t="s">
+      <c r="A488" s="1" t="s">
         <v>489</v>
       </c>
-      <c r="B488" s="0"/>
+      <c r="B488" s="1"/>
     </row>
     <row r="489" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A489" s="0" t="s">
+      <c r="A489" s="1" t="s">
         <v>490</v>
       </c>
-      <c r="B489" s="0"/>
+      <c r="B489" s="1"/>
     </row>
     <row r="490" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A490" s="0" t="s">
+      <c r="A490" s="1" t="s">
         <v>491</v>
       </c>
       <c r="B490" s="5" t="n">
@@ -6450,7 +6497,7 @@
       </c>
     </row>
     <row r="491" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A491" s="0" t="s">
+      <c r="A491" s="1" t="s">
         <v>492</v>
       </c>
       <c r="B491" s="5" t="n">
@@ -6461,7 +6508,7 @@
       </c>
     </row>
     <row r="492" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A492" s="0" t="s">
+      <c r="A492" s="1" t="s">
         <v>493</v>
       </c>
       <c r="B492" s="5" t="n">
@@ -6472,7 +6519,7 @@
       </c>
     </row>
     <row r="493" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A493" s="0" t="s">
+      <c r="A493" s="1" t="s">
         <v>494</v>
       </c>
       <c r="B493" s="5" t="n">
@@ -6483,7 +6530,7 @@
       </c>
     </row>
     <row r="494" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A494" s="0" t="s">
+      <c r="A494" s="1" t="s">
         <v>495</v>
       </c>
       <c r="B494" s="5" t="n">
@@ -6494,19 +6541,19 @@
       </c>
     </row>
     <row r="495" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A495" s="0" t="s">
+      <c r="A495" s="1" t="s">
         <v>496</v>
       </c>
-      <c r="B495" s="0"/>
+      <c r="B495" s="1"/>
     </row>
     <row r="496" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A496" s="0" t="s">
+      <c r="A496" s="1" t="s">
         <v>497</v>
       </c>
-      <c r="B496" s="0"/>
+      <c r="B496" s="1"/>
     </row>
     <row r="497" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A497" s="0" t="s">
+      <c r="A497" s="1" t="s">
         <v>498</v>
       </c>
       <c r="B497" s="5" t="n">
@@ -6517,7 +6564,7 @@
       </c>
     </row>
     <row r="498" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A498" s="0" t="s">
+      <c r="A498" s="1" t="s">
         <v>499</v>
       </c>
       <c r="B498" s="5" t="n">
@@ -6528,7 +6575,7 @@
       </c>
     </row>
     <row r="499" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A499" s="0" t="s">
+      <c r="A499" s="1" t="s">
         <v>500</v>
       </c>
       <c r="B499" s="5" t="n">
@@ -6539,7 +6586,7 @@
       </c>
     </row>
     <row r="500" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A500" s="0" t="s">
+      <c r="A500" s="1" t="s">
         <v>501</v>
       </c>
       <c r="B500" s="5" t="n">
@@ -6550,7 +6597,7 @@
       </c>
     </row>
     <row r="501" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A501" s="0" t="s">
+      <c r="A501" s="1" t="s">
         <v>502</v>
       </c>
       <c r="B501" s="5" t="n">
@@ -6561,19 +6608,19 @@
       </c>
     </row>
     <row r="502" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A502" s="0" t="s">
+      <c r="A502" s="1" t="s">
         <v>503</v>
       </c>
-      <c r="B502" s="0"/>
+      <c r="B502" s="1"/>
     </row>
     <row r="503" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A503" s="0" t="s">
+      <c r="A503" s="1" t="s">
         <v>504</v>
       </c>
-      <c r="B503" s="0"/>
+      <c r="B503" s="1"/>
     </row>
     <row r="504" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A504" s="0" t="s">
+      <c r="A504" s="1" t="s">
         <v>505</v>
       </c>
       <c r="B504" s="5" t="n">
@@ -6584,13 +6631,13 @@
       </c>
     </row>
     <row r="505" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A505" s="0" t="s">
+      <c r="A505" s="1" t="s">
         <v>506</v>
       </c>
-      <c r="B505" s="0"/>
+      <c r="B505" s="1"/>
     </row>
     <row r="506" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A506" s="0" t="s">
+      <c r="A506" s="1" t="s">
         <v>507</v>
       </c>
       <c r="B506" s="5" t="n">
@@ -6601,7 +6648,7 @@
       </c>
     </row>
     <row r="507" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A507" s="0" t="s">
+      <c r="A507" s="1" t="s">
         <v>508</v>
       </c>
       <c r="B507" s="5" t="n">
@@ -6612,7 +6659,7 @@
       </c>
     </row>
     <row r="508" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A508" s="0" t="s">
+      <c r="A508" s="1" t="s">
         <v>509</v>
       </c>
       <c r="B508" s="5" t="n">
@@ -6623,19 +6670,19 @@
       </c>
     </row>
     <row r="509" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A509" s="0" t="s">
+      <c r="A509" s="1" t="s">
         <v>510</v>
       </c>
-      <c r="B509" s="0"/>
+      <c r="B509" s="1"/>
     </row>
     <row r="510" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A510" s="0" t="s">
+      <c r="A510" s="1" t="s">
         <v>511</v>
       </c>
-      <c r="B510" s="0"/>
+      <c r="B510" s="1"/>
     </row>
     <row r="511" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A511" s="0" t="s">
+      <c r="A511" s="1" t="s">
         <v>512</v>
       </c>
       <c r="B511" s="5" t="n">
@@ -6646,7 +6693,7 @@
       </c>
     </row>
     <row r="512" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A512" s="0" t="s">
+      <c r="A512" s="1" t="s">
         <v>513</v>
       </c>
       <c r="B512" s="5" t="n">
@@ -6657,37 +6704,37 @@
       </c>
     </row>
     <row r="513" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A513" s="0" t="s">
+      <c r="A513" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="B513" s="0"/>
+      <c r="B513" s="1"/>
     </row>
     <row r="514" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A514" s="0" t="s">
+      <c r="A514" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="B514" s="0"/>
+      <c r="B514" s="1"/>
     </row>
     <row r="515" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A515" s="0" t="s">
+      <c r="A515" s="1" t="s">
         <v>516</v>
       </c>
-      <c r="B515" s="0"/>
+      <c r="B515" s="1"/>
     </row>
     <row r="516" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A516" s="0" t="s">
+      <c r="A516" s="1" t="s">
         <v>517</v>
       </c>
-      <c r="B516" s="0"/>
+      <c r="B516" s="1"/>
     </row>
     <row r="517" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A517" s="0" t="s">
+      <c r="A517" s="1" t="s">
         <v>518</v>
       </c>
-      <c r="B517" s="0"/>
+      <c r="B517" s="1"/>
     </row>
     <row r="518" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A518" s="0" t="s">
+      <c r="A518" s="1" t="s">
         <v>519</v>
       </c>
       <c r="B518" s="5" t="n">
@@ -6698,79 +6745,167 @@
       </c>
     </row>
     <row r="519" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B519" s="1"/>
+      <c r="A519" s="0" t="s">
+        <v>520</v>
+      </c>
+      <c r="B519" s="0" t="n">
+        <v>45.8248</v>
+      </c>
+      <c r="C519" s="0" t="n">
+        <v>53.4042</v>
+      </c>
     </row>
     <row r="520" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B520" s="6"/>
-      <c r="C520" s="6"/>
+      <c r="A520" s="0" t="s">
+        <v>521</v>
+      </c>
+      <c r="B520" s="0" t="n">
+        <v>45.8402</v>
+      </c>
+      <c r="C520" s="0" t="n">
+        <v>53.3878</v>
+      </c>
     </row>
     <row r="521" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B521" s="6"/>
-      <c r="C521" s="6"/>
+      <c r="A521" s="0" t="s">
+        <v>522</v>
+      </c>
+      <c r="B521" s="0" t="n">
+        <v>45.8696</v>
+      </c>
+      <c r="C521" s="0" t="n">
+        <v>53.2768</v>
+      </c>
     </row>
     <row r="522" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B522" s="6"/>
-      <c r="C522" s="6"/>
+      <c r="A522" s="0" t="s">
+        <v>523</v>
+      </c>
+      <c r="B522" s="0" t="n">
+        <v>45.8873</v>
+      </c>
+      <c r="C522" s="0" t="n">
+        <v>53.3268</v>
+      </c>
     </row>
     <row r="523" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B523" s="6"/>
-      <c r="C523" s="6"/>
+      <c r="A523" s="0" t="s">
+        <v>524</v>
+      </c>
+      <c r="B523" s="0"/>
+      <c r="C523" s="0"/>
     </row>
     <row r="524" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B524" s="6"/>
-      <c r="C524" s="6"/>
+      <c r="A524" s="0" t="s">
+        <v>525</v>
+      </c>
+      <c r="B524" s="0"/>
+      <c r="C524" s="0"/>
     </row>
     <row r="525" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B525" s="1"/>
+      <c r="A525" s="0" t="s">
+        <v>526</v>
+      </c>
+      <c r="B525" s="0" t="n">
+        <v>45.9084</v>
+      </c>
+      <c r="C525" s="0" t="n">
+        <v>53.4156</v>
+      </c>
     </row>
     <row r="526" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B526" s="1"/>
+      <c r="A526" s="0" t="s">
+        <v>527</v>
+      </c>
+      <c r="B526" s="0" t="n">
+        <v>46.0144</v>
+      </c>
+      <c r="C526" s="0" t="n">
+        <v>53.0044</v>
+      </c>
     </row>
     <row r="527" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B527" s="6"/>
-      <c r="C527" s="6"/>
+      <c r="A527" s="0" t="s">
+        <v>528</v>
+      </c>
+      <c r="B527" s="0" t="n">
+        <v>46.0328</v>
+      </c>
+      <c r="C527" s="0" t="n">
+        <v>53.194</v>
+      </c>
     </row>
     <row r="528" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B528" s="6"/>
-      <c r="C528" s="6"/>
+      <c r="A528" s="0" t="s">
+        <v>529</v>
+      </c>
+      <c r="B528" s="0" t="n">
+        <v>46.0491</v>
+      </c>
+      <c r="C528" s="0" t="n">
+        <v>53.1886</v>
+      </c>
     </row>
     <row r="529" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B529" s="6"/>
-      <c r="C529" s="6"/>
+      <c r="A529" s="0" t="s">
+        <v>530</v>
+      </c>
+      <c r="B529" s="0" t="n">
+        <v>46.0669</v>
+      </c>
+      <c r="C529" s="0" t="n">
+        <v>53.1485</v>
+      </c>
     </row>
     <row r="530" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B530" s="6"/>
-      <c r="C530" s="6"/>
+      <c r="A530" s="0" t="s">
+        <v>531</v>
+      </c>
+      <c r="B530" s="0"/>
+      <c r="C530" s="0"/>
     </row>
     <row r="531" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B531" s="6"/>
-      <c r="C531" s="6"/>
+      <c r="A531" s="0" t="s">
+        <v>532</v>
+      </c>
+      <c r="B531" s="0"/>
+      <c r="C531" s="0"/>
     </row>
     <row r="532" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B532" s="1"/>
+      <c r="A532" s="0" t="s">
+        <v>533</v>
+      </c>
+      <c r="B532" s="0" t="n">
+        <v>46.0857</v>
+      </c>
+      <c r="C532" s="0" t="n">
+        <v>53.3419</v>
+      </c>
     </row>
     <row r="533" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B533" s="1"/>
+      <c r="A533" s="0"/>
+      <c r="B533" s="0"/>
+      <c r="C533" s="0"/>
     </row>
     <row r="534" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B534" s="6"/>
-      <c r="C534" s="6"/>
+      <c r="B534" s="5"/>
+      <c r="C534" s="5"/>
     </row>
     <row r="535" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B535" s="6"/>
-      <c r="C535" s="6"/>
+      <c r="B535" s="5"/>
+      <c r="C535" s="5"/>
     </row>
     <row r="536" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B536" s="6"/>
-      <c r="C536" s="6"/>
+      <c r="B536" s="5"/>
+      <c r="C536" s="5"/>
     </row>
     <row r="537" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B537" s="6"/>
-      <c r="C537" s="6"/>
+      <c r="B537" s="5"/>
+      <c r="C537" s="5"/>
     </row>
     <row r="538" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B538" s="6"/>
-      <c r="C538" s="6"/>
+      <c r="B538" s="5"/>
+      <c r="C538" s="5"/>
     </row>
     <row r="539" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B539" s="1"/>
@@ -6779,24 +6914,24 @@
       <c r="B540" s="1"/>
     </row>
     <row r="541" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B541" s="6"/>
-      <c r="C541" s="6"/>
+      <c r="B541" s="5"/>
+      <c r="C541" s="5"/>
     </row>
     <row r="542" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B542" s="6"/>
-      <c r="C542" s="6"/>
+      <c r="B542" s="5"/>
+      <c r="C542" s="5"/>
     </row>
     <row r="543" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B543" s="6"/>
-      <c r="C543" s="6"/>
+      <c r="B543" s="5"/>
+      <c r="C543" s="5"/>
     </row>
     <row r="544" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B544" s="6"/>
-      <c r="C544" s="6"/>
+      <c r="B544" s="5"/>
+      <c r="C544" s="5"/>
     </row>
     <row r="545" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B545" s="6"/>
-      <c r="C545" s="6"/>
+      <c r="B545" s="5"/>
+      <c r="C545" s="5"/>
     </row>
     <row r="546" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B546" s="1"/>
@@ -6805,24 +6940,24 @@
       <c r="B547" s="1"/>
     </row>
     <row r="548" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B548" s="6"/>
-      <c r="C548" s="6"/>
+      <c r="B548" s="5"/>
+      <c r="C548" s="5"/>
     </row>
     <row r="549" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B549" s="6"/>
-      <c r="C549" s="6"/>
+      <c r="B549" s="5"/>
+      <c r="C549" s="5"/>
     </row>
     <row r="550" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B550" s="6"/>
-      <c r="C550" s="6"/>
+      <c r="B550" s="5"/>
+      <c r="C550" s="5"/>
     </row>
     <row r="551" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B551" s="6"/>
-      <c r="C551" s="6"/>
+      <c r="B551" s="5"/>
+      <c r="C551" s="5"/>
     </row>
     <row r="552" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B552" s="6"/>
-      <c r="C552" s="6"/>
+      <c r="B552" s="5"/>
+      <c r="C552" s="5"/>
     </row>
     <row r="553" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B553" s="1"/>
@@ -6831,24 +6966,24 @@
       <c r="B554" s="1"/>
     </row>
     <row r="555" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B555" s="6"/>
-      <c r="C555" s="6"/>
+      <c r="B555" s="5"/>
+      <c r="C555" s="5"/>
     </row>
     <row r="556" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B556" s="6"/>
-      <c r="C556" s="6"/>
+      <c r="B556" s="5"/>
+      <c r="C556" s="5"/>
     </row>
     <row r="557" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B557" s="6"/>
-      <c r="C557" s="6"/>
+      <c r="B557" s="5"/>
+      <c r="C557" s="5"/>
     </row>
     <row r="558" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B558" s="6"/>
-      <c r="C558" s="6"/>
+      <c r="B558" s="5"/>
+      <c r="C558" s="5"/>
     </row>
     <row r="559" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B559" s="6"/>
-      <c r="C559" s="6"/>
+      <c r="B559" s="5"/>
+      <c r="C559" s="5"/>
     </row>
     <row r="560" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B560" s="1"/>
@@ -6857,24 +6992,24 @@
       <c r="B561" s="1"/>
     </row>
     <row r="562" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B562" s="6"/>
-      <c r="C562" s="6"/>
+      <c r="B562" s="5"/>
+      <c r="C562" s="5"/>
     </row>
     <row r="563" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B563" s="6"/>
-      <c r="C563" s="6"/>
+      <c r="B563" s="5"/>
+      <c r="C563" s="5"/>
     </row>
     <row r="564" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B564" s="6"/>
-      <c r="C564" s="6"/>
+      <c r="B564" s="5"/>
+      <c r="C564" s="5"/>
     </row>
     <row r="565" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B565" s="6"/>
-      <c r="C565" s="6"/>
+      <c r="B565" s="5"/>
+      <c r="C565" s="5"/>
     </row>
     <row r="566" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B566" s="6"/>
-      <c r="C566" s="6"/>
+      <c r="B566" s="5"/>
+      <c r="C566" s="5"/>
     </row>
     <row r="567" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B567" s="1"/>
@@ -6883,24 +7018,24 @@
       <c r="B568" s="1"/>
     </row>
     <row r="569" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B569" s="6"/>
-      <c r="C569" s="6"/>
+      <c r="B569" s="5"/>
+      <c r="C569" s="5"/>
     </row>
     <row r="570" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B570" s="6"/>
-      <c r="C570" s="6"/>
+      <c r="B570" s="5"/>
+      <c r="C570" s="5"/>
     </row>
     <row r="571" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B571" s="6"/>
-      <c r="C571" s="6"/>
+      <c r="B571" s="5"/>
+      <c r="C571" s="5"/>
     </row>
     <row r="572" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B572" s="6"/>
-      <c r="C572" s="6"/>
+      <c r="B572" s="5"/>
+      <c r="C572" s="5"/>
     </row>
     <row r="573" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B573" s="6"/>
-      <c r="C573" s="6"/>
+      <c r="B573" s="5"/>
+      <c r="C573" s="5"/>
     </row>
     <row r="574" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B574" s="1"/>
@@ -6909,24 +7044,24 @@
       <c r="B575" s="1"/>
     </row>
     <row r="576" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B576" s="6"/>
-      <c r="C576" s="6"/>
+      <c r="B576" s="5"/>
+      <c r="C576" s="5"/>
     </row>
     <row r="577" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B577" s="6"/>
-      <c r="C577" s="6"/>
+      <c r="B577" s="5"/>
+      <c r="C577" s="5"/>
     </row>
     <row r="578" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B578" s="6"/>
-      <c r="C578" s="6"/>
+      <c r="B578" s="5"/>
+      <c r="C578" s="5"/>
     </row>
     <row r="579" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B579" s="6"/>
-      <c r="C579" s="6"/>
+      <c r="B579" s="5"/>
+      <c r="C579" s="5"/>
     </row>
     <row r="580" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B580" s="6"/>
-      <c r="C580" s="6"/>
+      <c r="B580" s="5"/>
+      <c r="C580" s="5"/>
     </row>
     <row r="581" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B581" s="1"/>
@@ -6935,24 +7070,24 @@
       <c r="B582" s="1"/>
     </row>
     <row r="583" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B583" s="6"/>
-      <c r="C583" s="6"/>
+      <c r="B583" s="5"/>
+      <c r="C583" s="5"/>
     </row>
     <row r="584" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B584" s="6"/>
-      <c r="C584" s="6"/>
+      <c r="B584" s="5"/>
+      <c r="C584" s="5"/>
     </row>
     <row r="585" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B585" s="6"/>
-      <c r="C585" s="6"/>
+      <c r="B585" s="5"/>
+      <c r="C585" s="5"/>
     </row>
     <row r="586" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B586" s="6"/>
-      <c r="C586" s="6"/>
+      <c r="B586" s="5"/>
+      <c r="C586" s="5"/>
     </row>
     <row r="587" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B587" s="6"/>
-      <c r="C587" s="6"/>
+      <c r="B587" s="5"/>
+      <c r="C587" s="5"/>
     </row>
     <row r="588" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B588" s="1"/>
@@ -6961,24 +7096,24 @@
       <c r="B589" s="1"/>
     </row>
     <row r="590" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B590" s="6"/>
-      <c r="C590" s="6"/>
+      <c r="B590" s="5"/>
+      <c r="C590" s="5"/>
     </row>
     <row r="591" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B591" s="6"/>
-      <c r="C591" s="6"/>
+      <c r="B591" s="5"/>
+      <c r="C591" s="5"/>
     </row>
     <row r="592" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B592" s="6"/>
-      <c r="C592" s="6"/>
+      <c r="B592" s="5"/>
+      <c r="C592" s="5"/>
     </row>
     <row r="593" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B593" s="6"/>
-      <c r="C593" s="6"/>
+      <c r="B593" s="5"/>
+      <c r="C593" s="5"/>
     </row>
     <row r="594" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B594" s="6"/>
-      <c r="C594" s="6"/>
+      <c r="B594" s="5"/>
+      <c r="C594" s="5"/>
     </row>
     <row r="595" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B595" s="1"/>
@@ -6987,24 +7122,24 @@
       <c r="B596" s="1"/>
     </row>
     <row r="597" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B597" s="6"/>
-      <c r="C597" s="6"/>
+      <c r="B597" s="5"/>
+      <c r="C597" s="5"/>
     </row>
     <row r="598" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B598" s="6"/>
-      <c r="C598" s="6"/>
+      <c r="B598" s="5"/>
+      <c r="C598" s="5"/>
     </row>
     <row r="599" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B599" s="6"/>
-      <c r="C599" s="6"/>
+      <c r="B599" s="5"/>
+      <c r="C599" s="5"/>
     </row>
     <row r="600" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B600" s="6"/>
-      <c r="C600" s="6"/>
+      <c r="B600" s="5"/>
+      <c r="C600" s="5"/>
     </row>
     <row r="601" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B601" s="6"/>
-      <c r="C601" s="6"/>
+      <c r="B601" s="5"/>
+      <c r="C601" s="5"/>
     </row>
     <row r="602" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B602" s="1"/>
@@ -7013,24 +7148,24 @@
       <c r="B603" s="1"/>
     </row>
     <row r="604" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B604" s="6"/>
-      <c r="C604" s="6"/>
+      <c r="B604" s="5"/>
+      <c r="C604" s="5"/>
     </row>
     <row r="605" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B605" s="6"/>
-      <c r="C605" s="6"/>
+      <c r="B605" s="5"/>
+      <c r="C605" s="5"/>
     </row>
     <row r="606" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B606" s="6"/>
-      <c r="C606" s="6"/>
+      <c r="B606" s="5"/>
+      <c r="C606" s="5"/>
     </row>
     <row r="607" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B607" s="6"/>
-      <c r="C607" s="6"/>
+      <c r="B607" s="5"/>
+      <c r="C607" s="5"/>
     </row>
     <row r="608" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B608" s="6"/>
-      <c r="C608" s="6"/>
+      <c r="B608" s="5"/>
+      <c r="C608" s="5"/>
     </row>
     <row r="609" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B609" s="1"/>
@@ -7039,24 +7174,24 @@
       <c r="B610" s="1"/>
     </row>
     <row r="611" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B611" s="6"/>
-      <c r="C611" s="6"/>
+      <c r="B611" s="5"/>
+      <c r="C611" s="5"/>
     </row>
     <row r="612" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B612" s="6"/>
-      <c r="C612" s="6"/>
+      <c r="B612" s="5"/>
+      <c r="C612" s="5"/>
     </row>
     <row r="613" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B613" s="6"/>
-      <c r="C613" s="6"/>
+      <c r="B613" s="5"/>
+      <c r="C613" s="5"/>
     </row>
     <row r="614" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B614" s="6"/>
-      <c r="C614" s="6"/>
+      <c r="B614" s="5"/>
+      <c r="C614" s="5"/>
     </row>
     <row r="615" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B615" s="6"/>
-      <c r="C615" s="6"/>
+      <c r="B615" s="5"/>
+      <c r="C615" s="5"/>
     </row>
     <row r="616" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B616" s="1"/>
@@ -7065,24 +7200,24 @@
       <c r="B617" s="1"/>
     </row>
     <row r="618" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B618" s="6"/>
-      <c r="C618" s="6"/>
+      <c r="B618" s="5"/>
+      <c r="C618" s="5"/>
     </row>
     <row r="619" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B619" s="6"/>
-      <c r="C619" s="6"/>
+      <c r="B619" s="5"/>
+      <c r="C619" s="5"/>
     </row>
     <row r="620" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B620" s="6"/>
-      <c r="C620" s="6"/>
+      <c r="B620" s="5"/>
+      <c r="C620" s="5"/>
     </row>
     <row r="621" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B621" s="6"/>
-      <c r="C621" s="6"/>
+      <c r="B621" s="5"/>
+      <c r="C621" s="5"/>
     </row>
     <row r="622" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B622" s="6"/>
-      <c r="C622" s="6"/>
+      <c r="B622" s="5"/>
+      <c r="C622" s="5"/>
     </row>
     <row r="623" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B623" s="1"/>
@@ -7091,24 +7226,24 @@
       <c r="B624" s="1"/>
     </row>
     <row r="625" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B625" s="6"/>
-      <c r="C625" s="6"/>
+      <c r="B625" s="5"/>
+      <c r="C625" s="5"/>
     </row>
     <row r="626" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B626" s="6"/>
-      <c r="C626" s="6"/>
+      <c r="B626" s="5"/>
+      <c r="C626" s="5"/>
     </row>
     <row r="627" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B627" s="6"/>
-      <c r="C627" s="6"/>
+      <c r="B627" s="5"/>
+      <c r="C627" s="5"/>
     </row>
     <row r="628" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B628" s="6"/>
-      <c r="C628" s="6"/>
+      <c r="B628" s="5"/>
+      <c r="C628" s="5"/>
     </row>
     <row r="629" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B629" s="6"/>
-      <c r="C629" s="6"/>
+      <c r="B629" s="5"/>
+      <c r="C629" s="5"/>
     </row>
     <row r="630" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B630" s="1"/>
@@ -7117,24 +7252,24 @@
       <c r="B631" s="1"/>
     </row>
     <row r="632" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B632" s="6"/>
-      <c r="C632" s="6"/>
+      <c r="B632" s="5"/>
+      <c r="C632" s="5"/>
     </row>
     <row r="633" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B633" s="6"/>
-      <c r="C633" s="6"/>
+      <c r="B633" s="5"/>
+      <c r="C633" s="5"/>
     </row>
     <row r="634" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B634" s="6"/>
-      <c r="C634" s="6"/>
+      <c r="B634" s="5"/>
+      <c r="C634" s="5"/>
     </row>
     <row r="635" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B635" s="6"/>
-      <c r="C635" s="6"/>
+      <c r="B635" s="5"/>
+      <c r="C635" s="5"/>
     </row>
     <row r="636" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B636" s="6"/>
-      <c r="C636" s="6"/>
+      <c r="B636" s="5"/>
+      <c r="C636" s="5"/>
     </row>
     <row r="637" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B637" s="1"/>
@@ -7143,24 +7278,24 @@
       <c r="B638" s="1"/>
     </row>
     <row r="639" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B639" s="6"/>
-      <c r="C639" s="6"/>
+      <c r="B639" s="5"/>
+      <c r="C639" s="5"/>
     </row>
     <row r="640" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B640" s="6"/>
-      <c r="C640" s="6"/>
+      <c r="B640" s="5"/>
+      <c r="C640" s="5"/>
     </row>
     <row r="641" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B641" s="6"/>
-      <c r="C641" s="6"/>
+      <c r="B641" s="5"/>
+      <c r="C641" s="5"/>
     </row>
     <row r="642" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B642" s="6"/>
-      <c r="C642" s="6"/>
+      <c r="B642" s="5"/>
+      <c r="C642" s="5"/>
     </row>
     <row r="643" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B643" s="6"/>
-      <c r="C643" s="6"/>
+      <c r="B643" s="5"/>
+      <c r="C643" s="5"/>
     </row>
     <row r="644" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B644" s="1"/>
@@ -7169,24 +7304,24 @@
       <c r="B645" s="1"/>
     </row>
     <row r="646" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B646" s="6"/>
-      <c r="C646" s="6"/>
+      <c r="B646" s="5"/>
+      <c r="C646" s="5"/>
     </row>
     <row r="647" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B647" s="6"/>
-      <c r="C647" s="6"/>
+      <c r="B647" s="5"/>
+      <c r="C647" s="5"/>
     </row>
     <row r="648" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B648" s="6"/>
-      <c r="C648" s="6"/>
+      <c r="B648" s="5"/>
+      <c r="C648" s="5"/>
     </row>
     <row r="649" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B649" s="6"/>
-      <c r="C649" s="6"/>
+      <c r="B649" s="5"/>
+      <c r="C649" s="5"/>
     </row>
     <row r="650" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B650" s="6"/>
-      <c r="C650" s="6"/>
+      <c r="B650" s="5"/>
+      <c r="C650" s="5"/>
     </row>
     <row r="651" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B651" s="1"/>
@@ -7195,24 +7330,24 @@
       <c r="B652" s="1"/>
     </row>
     <row r="653" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B653" s="6"/>
-      <c r="C653" s="6"/>
+      <c r="B653" s="5"/>
+      <c r="C653" s="5"/>
     </row>
     <row r="654" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B654" s="6"/>
-      <c r="C654" s="6"/>
+      <c r="B654" s="5"/>
+      <c r="C654" s="5"/>
     </row>
     <row r="655" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B655" s="6"/>
-      <c r="C655" s="6"/>
+      <c r="B655" s="5"/>
+      <c r="C655" s="5"/>
     </row>
     <row r="656" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B656" s="6"/>
-      <c r="C656" s="6"/>
+      <c r="B656" s="5"/>
+      <c r="C656" s="5"/>
     </row>
     <row r="657" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B657" s="6"/>
-      <c r="C657" s="6"/>
+      <c r="B657" s="5"/>
+      <c r="C657" s="5"/>
     </row>
     <row r="658" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B658" s="1"/>
@@ -7221,24 +7356,24 @@
       <c r="B659" s="1"/>
     </row>
     <row r="660" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B660" s="6"/>
-      <c r="C660" s="6"/>
+      <c r="B660" s="5"/>
+      <c r="C660" s="5"/>
     </row>
     <row r="661" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B661" s="6"/>
-      <c r="C661" s="6"/>
+      <c r="B661" s="5"/>
+      <c r="C661" s="5"/>
     </row>
     <row r="662" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B662" s="6"/>
-      <c r="C662" s="6"/>
+      <c r="B662" s="5"/>
+      <c r="C662" s="5"/>
     </row>
     <row r="663" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B663" s="6"/>
-      <c r="C663" s="6"/>
+      <c r="B663" s="5"/>
+      <c r="C663" s="5"/>
     </row>
     <row r="664" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B664" s="6"/>
-      <c r="C664" s="6"/>
+      <c r="B664" s="5"/>
+      <c r="C664" s="5"/>
     </row>
     <row r="665" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B665" s="1"/>
@@ -7247,24 +7382,24 @@
       <c r="B666" s="1"/>
     </row>
     <row r="667" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B667" s="6"/>
-      <c r="C667" s="6"/>
+      <c r="B667" s="5"/>
+      <c r="C667" s="5"/>
     </row>
     <row r="668" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B668" s="6"/>
-      <c r="C668" s="6"/>
+      <c r="B668" s="5"/>
+      <c r="C668" s="5"/>
     </row>
     <row r="669" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B669" s="6"/>
-      <c r="C669" s="6"/>
+      <c r="B669" s="5"/>
+      <c r="C669" s="5"/>
     </row>
     <row r="670" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B670" s="6"/>
-      <c r="C670" s="6"/>
+      <c r="B670" s="5"/>
+      <c r="C670" s="5"/>
     </row>
     <row r="671" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B671" s="6"/>
-      <c r="C671" s="6"/>
+      <c r="B671" s="5"/>
+      <c r="C671" s="5"/>
     </row>
     <row r="672" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B672" s="1"/>
@@ -7273,24 +7408,24 @@
       <c r="B673" s="1"/>
     </row>
     <row r="674" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B674" s="6"/>
-      <c r="C674" s="6"/>
+      <c r="B674" s="5"/>
+      <c r="C674" s="5"/>
     </row>
     <row r="675" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B675" s="6"/>
-      <c r="C675" s="6"/>
+      <c r="B675" s="5"/>
+      <c r="C675" s="5"/>
     </row>
     <row r="676" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B676" s="6"/>
-      <c r="C676" s="6"/>
+      <c r="B676" s="5"/>
+      <c r="C676" s="5"/>
     </row>
     <row r="677" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B677" s="6"/>
-      <c r="C677" s="6"/>
+      <c r="B677" s="5"/>
+      <c r="C677" s="5"/>
     </row>
     <row r="678" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B678" s="6"/>
-      <c r="C678" s="6"/>
+      <c r="B678" s="5"/>
+      <c r="C678" s="5"/>
     </row>
     <row r="679" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B679" s="1"/>
@@ -7299,24 +7434,24 @@
       <c r="B680" s="1"/>
     </row>
     <row r="681" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B681" s="6"/>
-      <c r="C681" s="6"/>
+      <c r="B681" s="5"/>
+      <c r="C681" s="5"/>
     </row>
     <row r="682" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B682" s="6"/>
-      <c r="C682" s="6"/>
+      <c r="B682" s="5"/>
+      <c r="C682" s="5"/>
     </row>
     <row r="683" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B683" s="6"/>
-      <c r="C683" s="6"/>
+      <c r="B683" s="5"/>
+      <c r="C683" s="5"/>
     </row>
     <row r="684" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B684" s="6"/>
-      <c r="C684" s="6"/>
+      <c r="B684" s="5"/>
+      <c r="C684" s="5"/>
     </row>
     <row r="685" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B685" s="6"/>
-      <c r="C685" s="6"/>
+      <c r="B685" s="5"/>
+      <c r="C685" s="5"/>
     </row>
     <row r="686" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B686" s="1"/>
@@ -7325,24 +7460,24 @@
       <c r="B687" s="1"/>
     </row>
     <row r="688" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B688" s="6"/>
-      <c r="C688" s="6"/>
+      <c r="B688" s="5"/>
+      <c r="C688" s="5"/>
     </row>
     <row r="689" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B689" s="6"/>
-      <c r="C689" s="6"/>
+      <c r="B689" s="5"/>
+      <c r="C689" s="5"/>
     </row>
     <row r="690" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B690" s="6"/>
-      <c r="C690" s="6"/>
+      <c r="B690" s="5"/>
+      <c r="C690" s="5"/>
     </row>
     <row r="691" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B691" s="6"/>
-      <c r="C691" s="6"/>
+      <c r="B691" s="5"/>
+      <c r="C691" s="5"/>
     </row>
     <row r="692" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B692" s="6"/>
-      <c r="C692" s="6"/>
+      <c r="B692" s="5"/>
+      <c r="C692" s="5"/>
     </row>
     <row r="693" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B693" s="1"/>
@@ -7351,20 +7486,20 @@
       <c r="B694" s="1"/>
     </row>
     <row r="695" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B695" s="6"/>
-      <c r="C695" s="6"/>
+      <c r="B695" s="5"/>
+      <c r="C695" s="5"/>
     </row>
     <row r="696" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B696" s="6"/>
-      <c r="C696" s="6"/>
+      <c r="B696" s="5"/>
+      <c r="C696" s="5"/>
     </row>
     <row r="697" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B697" s="6"/>
-      <c r="C697" s="6"/>
+      <c r="B697" s="5"/>
+      <c r="C697" s="5"/>
     </row>
     <row r="698" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B698" s="6"/>
-      <c r="C698" s="6"/>
+      <c r="B698" s="5"/>
+      <c r="C698" s="5"/>
     </row>
     <row r="699" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B699" s="1"/>
@@ -7376,24 +7511,24 @@
       <c r="B701" s="1"/>
     </row>
     <row r="702" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B702" s="6"/>
-      <c r="C702" s="6"/>
+      <c r="B702" s="5"/>
+      <c r="C702" s="5"/>
     </row>
     <row r="703" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B703" s="6"/>
-      <c r="C703" s="6"/>
+      <c r="B703" s="5"/>
+      <c r="C703" s="5"/>
     </row>
     <row r="704" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B704" s="6"/>
-      <c r="C704" s="6"/>
+      <c r="B704" s="5"/>
+      <c r="C704" s="5"/>
     </row>
     <row r="705" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B705" s="6"/>
-      <c r="C705" s="6"/>
+      <c r="B705" s="5"/>
+      <c r="C705" s="5"/>
     </row>
     <row r="706" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B706" s="6"/>
-      <c r="C706" s="6"/>
+      <c r="B706" s="5"/>
+      <c r="C706" s="5"/>
     </row>
     <row r="707" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B707" s="1"/>
@@ -7405,20 +7540,20 @@
       <c r="B709" s="1"/>
     </row>
     <row r="710" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B710" s="6"/>
-      <c r="C710" s="6"/>
+      <c r="B710" s="5"/>
+      <c r="C710" s="5"/>
     </row>
     <row r="711" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B711" s="6"/>
-      <c r="C711" s="6"/>
+      <c r="B711" s="5"/>
+      <c r="C711" s="5"/>
     </row>
     <row r="712" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B712" s="6"/>
-      <c r="C712" s="6"/>
+      <c r="B712" s="5"/>
+      <c r="C712" s="5"/>
     </row>
     <row r="713" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B713" s="6"/>
-      <c r="C713" s="6"/>
+      <c r="B713" s="5"/>
+      <c r="C713" s="5"/>
     </row>
     <row r="714" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B714" s="1"/>
@@ -7427,24 +7562,24 @@
       <c r="B715" s="1"/>
     </row>
     <row r="716" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B716" s="6"/>
-      <c r="C716" s="6"/>
+      <c r="B716" s="5"/>
+      <c r="C716" s="5"/>
     </row>
     <row r="717" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B717" s="6"/>
-      <c r="C717" s="6"/>
+      <c r="B717" s="5"/>
+      <c r="C717" s="5"/>
     </row>
     <row r="718" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B718" s="6"/>
-      <c r="C718" s="6"/>
+      <c r="B718" s="5"/>
+      <c r="C718" s="5"/>
     </row>
     <row r="719" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B719" s="6"/>
-      <c r="C719" s="6"/>
+      <c r="B719" s="5"/>
+      <c r="C719" s="5"/>
     </row>
     <row r="720" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B720" s="6"/>
-      <c r="C720" s="6"/>
+      <c r="B720" s="5"/>
+      <c r="C720" s="5"/>
     </row>
     <row r="721" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B721" s="1"/>
@@ -7453,20 +7588,20 @@
       <c r="B722" s="1"/>
     </row>
     <row r="723" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B723" s="6"/>
-      <c r="C723" s="6"/>
+      <c r="B723" s="5"/>
+      <c r="C723" s="5"/>
     </row>
     <row r="724" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B724" s="6"/>
-      <c r="C724" s="6"/>
+      <c r="B724" s="5"/>
+      <c r="C724" s="5"/>
     </row>
     <row r="725" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B725" s="6"/>
-      <c r="C725" s="6"/>
+      <c r="B725" s="5"/>
+      <c r="C725" s="5"/>
     </row>
     <row r="726" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B726" s="6"/>
-      <c r="C726" s="6"/>
+      <c r="B726" s="5"/>
+      <c r="C726" s="5"/>
     </row>
     <row r="727" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B727" s="1"/>
@@ -7478,24 +7613,24 @@
       <c r="B729" s="1"/>
     </row>
     <row r="730" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B730" s="6"/>
-      <c r="C730" s="6"/>
+      <c r="B730" s="5"/>
+      <c r="C730" s="5"/>
     </row>
     <row r="731" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B731" s="6"/>
-      <c r="C731" s="6"/>
+      <c r="B731" s="5"/>
+      <c r="C731" s="5"/>
     </row>
     <row r="732" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B732" s="6"/>
-      <c r="C732" s="6"/>
+      <c r="B732" s="5"/>
+      <c r="C732" s="5"/>
     </row>
     <row r="733" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B733" s="6"/>
-      <c r="C733" s="6"/>
+      <c r="B733" s="5"/>
+      <c r="C733" s="5"/>
     </row>
     <row r="734" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B734" s="6"/>
-      <c r="C734" s="6"/>
+      <c r="B734" s="5"/>
+      <c r="C734" s="5"/>
     </row>
     <row r="735" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B735" s="1"/>
@@ -7504,24 +7639,24 @@
       <c r="B736" s="1"/>
     </row>
     <row r="737" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B737" s="6"/>
-      <c r="C737" s="6"/>
+      <c r="B737" s="5"/>
+      <c r="C737" s="5"/>
     </row>
     <row r="738" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B738" s="6"/>
-      <c r="C738" s="6"/>
+      <c r="B738" s="5"/>
+      <c r="C738" s="5"/>
     </row>
     <row r="739" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B739" s="6"/>
-      <c r="C739" s="6"/>
+      <c r="B739" s="5"/>
+      <c r="C739" s="5"/>
     </row>
     <row r="740" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B740" s="6"/>
-      <c r="C740" s="6"/>
+      <c r="B740" s="5"/>
+      <c r="C740" s="5"/>
     </row>
     <row r="741" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B741" s="6"/>
-      <c r="C741" s="6"/>
+      <c r="B741" s="5"/>
+      <c r="C741" s="5"/>
     </row>
     <row r="742" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B742" s="1"/>
@@ -7530,24 +7665,24 @@
       <c r="B743" s="1"/>
     </row>
     <row r="744" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B744" s="6"/>
-      <c r="C744" s="6"/>
+      <c r="B744" s="5"/>
+      <c r="C744" s="5"/>
     </row>
     <row r="745" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B745" s="6"/>
-      <c r="C745" s="6"/>
+      <c r="B745" s="5"/>
+      <c r="C745" s="5"/>
     </row>
     <row r="746" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B746" s="6"/>
-      <c r="C746" s="6"/>
+      <c r="B746" s="5"/>
+      <c r="C746" s="5"/>
     </row>
     <row r="747" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B747" s="6"/>
-      <c r="C747" s="6"/>
+      <c r="B747" s="5"/>
+      <c r="C747" s="5"/>
     </row>
     <row r="748" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B748" s="6"/>
-      <c r="C748" s="6"/>
+      <c r="B748" s="5"/>
+      <c r="C748" s="5"/>
     </row>
     <row r="749" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B749" s="1"/>
@@ -7556,24 +7691,24 @@
       <c r="B750" s="1"/>
     </row>
     <row r="751" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B751" s="6"/>
-      <c r="C751" s="6"/>
+      <c r="B751" s="5"/>
+      <c r="C751" s="5"/>
     </row>
     <row r="752" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B752" s="6"/>
-      <c r="C752" s="6"/>
+      <c r="B752" s="5"/>
+      <c r="C752" s="5"/>
     </row>
     <row r="753" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B753" s="6"/>
-      <c r="C753" s="6"/>
+      <c r="B753" s="5"/>
+      <c r="C753" s="5"/>
     </row>
     <row r="754" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B754" s="6"/>
-      <c r="C754" s="6"/>
+      <c r="B754" s="5"/>
+      <c r="C754" s="5"/>
     </row>
     <row r="755" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B755" s="6"/>
-      <c r="C755" s="6"/>
+      <c r="B755" s="5"/>
+      <c r="C755" s="5"/>
     </row>
     <row r="756" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B756" s="1"/>
@@ -7582,24 +7717,24 @@
       <c r="B757" s="1"/>
     </row>
     <row r="758" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B758" s="6"/>
-      <c r="C758" s="6"/>
+      <c r="B758" s="5"/>
+      <c r="C758" s="5"/>
     </row>
     <row r="759" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B759" s="6"/>
-      <c r="C759" s="6"/>
+      <c r="B759" s="5"/>
+      <c r="C759" s="5"/>
     </row>
     <row r="760" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B760" s="6"/>
-      <c r="C760" s="6"/>
+      <c r="B760" s="5"/>
+      <c r="C760" s="5"/>
     </row>
     <row r="761" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B761" s="6"/>
-      <c r="C761" s="6"/>
+      <c r="B761" s="5"/>
+      <c r="C761" s="5"/>
     </row>
     <row r="762" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B762" s="6"/>
-      <c r="C762" s="6"/>
+      <c r="B762" s="5"/>
+      <c r="C762" s="5"/>
     </row>
     <row r="763" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B763" s="1"/>
@@ -7608,12 +7743,12 @@
       <c r="B764" s="1"/>
     </row>
     <row r="765" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B765" s="6"/>
-      <c r="C765" s="6"/>
+      <c r="B765" s="5"/>
+      <c r="C765" s="5"/>
     </row>
     <row r="766" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B766" s="6"/>
-      <c r="C766" s="6"/>
+      <c r="B766" s="5"/>
+      <c r="C766" s="5"/>
     </row>
     <row r="767" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B767" s="1"/>
@@ -7631,24 +7766,24 @@
       <c r="B771" s="1"/>
     </row>
     <row r="772" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B772" s="6"/>
-      <c r="C772" s="6"/>
+      <c r="B772" s="5"/>
+      <c r="C772" s="5"/>
     </row>
     <row r="773" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B773" s="6"/>
-      <c r="C773" s="6"/>
+      <c r="B773" s="5"/>
+      <c r="C773" s="5"/>
     </row>
     <row r="774" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B774" s="6"/>
-      <c r="C774" s="6"/>
+      <c r="B774" s="5"/>
+      <c r="C774" s="5"/>
     </row>
     <row r="775" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B775" s="6"/>
-      <c r="C775" s="6"/>
+      <c r="B775" s="5"/>
+      <c r="C775" s="5"/>
     </row>
     <row r="776" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B776" s="6"/>
-      <c r="C776" s="6"/>
+      <c r="B776" s="5"/>
+      <c r="C776" s="5"/>
     </row>
     <row r="777" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B777" s="1"/>
@@ -7657,24 +7792,24 @@
       <c r="B778" s="1"/>
     </row>
     <row r="779" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B779" s="6"/>
-      <c r="C779" s="6"/>
+      <c r="B779" s="5"/>
+      <c r="C779" s="5"/>
     </row>
     <row r="780" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B780" s="6"/>
-      <c r="C780" s="6"/>
+      <c r="B780" s="5"/>
+      <c r="C780" s="5"/>
     </row>
     <row r="781" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B781" s="6"/>
-      <c r="C781" s="6"/>
+      <c r="B781" s="5"/>
+      <c r="C781" s="5"/>
     </row>
     <row r="782" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B782" s="6"/>
-      <c r="C782" s="6"/>
+      <c r="B782" s="5"/>
+      <c r="C782" s="5"/>
     </row>
     <row r="783" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B783" s="6"/>
-      <c r="C783" s="6"/>
+      <c r="B783" s="5"/>
+      <c r="C783" s="5"/>
     </row>
     <row r="784" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B784" s="1"/>
@@ -7683,24 +7818,24 @@
       <c r="B785" s="1"/>
     </row>
     <row r="786" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B786" s="6"/>
-      <c r="C786" s="6"/>
+      <c r="B786" s="5"/>
+      <c r="C786" s="5"/>
     </row>
     <row r="787" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B787" s="6"/>
-      <c r="C787" s="6"/>
+      <c r="B787" s="5"/>
+      <c r="C787" s="5"/>
     </row>
     <row r="788" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B788" s="6"/>
-      <c r="C788" s="6"/>
+      <c r="B788" s="5"/>
+      <c r="C788" s="5"/>
     </row>
     <row r="789" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B789" s="6"/>
-      <c r="C789" s="6"/>
+      <c r="B789" s="5"/>
+      <c r="C789" s="5"/>
     </row>
     <row r="790" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B790" s="6"/>
-      <c r="C790" s="6"/>
+      <c r="B790" s="5"/>
+      <c r="C790" s="5"/>
     </row>
     <row r="791" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B791" s="1"/>
@@ -7709,24 +7844,24 @@
       <c r="B792" s="1"/>
     </row>
     <row r="793" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B793" s="6"/>
-      <c r="C793" s="6"/>
+      <c r="B793" s="5"/>
+      <c r="C793" s="5"/>
     </row>
     <row r="794" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B794" s="6"/>
-      <c r="C794" s="6"/>
+      <c r="B794" s="5"/>
+      <c r="C794" s="5"/>
     </row>
     <row r="795" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B795" s="6"/>
-      <c r="C795" s="6"/>
+      <c r="B795" s="5"/>
+      <c r="C795" s="5"/>
     </row>
     <row r="796" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B796" s="6"/>
-      <c r="C796" s="6"/>
+      <c r="B796" s="5"/>
+      <c r="C796" s="5"/>
     </row>
     <row r="797" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B797" s="6"/>
-      <c r="C797" s="6"/>
+      <c r="B797" s="5"/>
+      <c r="C797" s="5"/>
     </row>
     <row r="798" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B798" s="1"/>
@@ -7735,24 +7870,24 @@
       <c r="B799" s="1"/>
     </row>
     <row r="800" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B800" s="6"/>
-      <c r="C800" s="6"/>
+      <c r="B800" s="5"/>
+      <c r="C800" s="5"/>
     </row>
     <row r="801" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B801" s="6"/>
-      <c r="C801" s="6"/>
+      <c r="B801" s="5"/>
+      <c r="C801" s="5"/>
     </row>
     <row r="802" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B802" s="6"/>
-      <c r="C802" s="6"/>
+      <c r="B802" s="5"/>
+      <c r="C802" s="5"/>
     </row>
     <row r="803" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B803" s="6"/>
-      <c r="C803" s="6"/>
+      <c r="B803" s="5"/>
+      <c r="C803" s="5"/>
     </row>
     <row r="804" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B804" s="6"/>
-      <c r="C804" s="6"/>
+      <c r="B804" s="5"/>
+      <c r="C804" s="5"/>
     </row>
     <row r="805" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B805" s="1"/>
@@ -7761,24 +7896,24 @@
       <c r="B806" s="1"/>
     </row>
     <row r="807" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B807" s="6"/>
-      <c r="C807" s="6"/>
+      <c r="B807" s="5"/>
+      <c r="C807" s="5"/>
     </row>
     <row r="808" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B808" s="6"/>
-      <c r="C808" s="6"/>
+      <c r="B808" s="5"/>
+      <c r="C808" s="5"/>
     </row>
     <row r="809" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B809" s="6"/>
-      <c r="C809" s="6"/>
+      <c r="B809" s="5"/>
+      <c r="C809" s="5"/>
     </row>
     <row r="810" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B810" s="6"/>
-      <c r="C810" s="6"/>
+      <c r="B810" s="5"/>
+      <c r="C810" s="5"/>
     </row>
     <row r="811" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B811" s="6"/>
-      <c r="C811" s="6"/>
+      <c r="B811" s="5"/>
+      <c r="C811" s="5"/>
     </row>
     <row r="812" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B812" s="1"/>
@@ -7787,24 +7922,24 @@
       <c r="B813" s="1"/>
     </row>
     <row r="814" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B814" s="6"/>
-      <c r="C814" s="6"/>
+      <c r="B814" s="5"/>
+      <c r="C814" s="5"/>
     </row>
     <row r="815" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B815" s="6"/>
-      <c r="C815" s="6"/>
+      <c r="B815" s="5"/>
+      <c r="C815" s="5"/>
     </row>
     <row r="816" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B816" s="6"/>
-      <c r="C816" s="6"/>
+      <c r="B816" s="5"/>
+      <c r="C816" s="5"/>
     </row>
     <row r="817" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B817" s="6"/>
-      <c r="C817" s="6"/>
+      <c r="B817" s="5"/>
+      <c r="C817" s="5"/>
     </row>
     <row r="818" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B818" s="6"/>
-      <c r="C818" s="6"/>
+      <c r="B818" s="5"/>
+      <c r="C818" s="5"/>
     </row>
     <row r="819" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B819" s="1"/>
@@ -7813,24 +7948,24 @@
       <c r="B820" s="1"/>
     </row>
     <row r="821" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B821" s="6"/>
-      <c r="C821" s="6"/>
+      <c r="B821" s="5"/>
+      <c r="C821" s="5"/>
     </row>
     <row r="822" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B822" s="6"/>
-      <c r="C822" s="6"/>
+      <c r="B822" s="5"/>
+      <c r="C822" s="5"/>
     </row>
     <row r="823" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B823" s="6"/>
-      <c r="C823" s="6"/>
+      <c r="B823" s="5"/>
+      <c r="C823" s="5"/>
     </row>
     <row r="824" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B824" s="6"/>
-      <c r="C824" s="6"/>
+      <c r="B824" s="5"/>
+      <c r="C824" s="5"/>
     </row>
     <row r="825" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B825" s="6"/>
-      <c r="C825" s="6"/>
+      <c r="B825" s="5"/>
+      <c r="C825" s="5"/>
     </row>
     <row r="826" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B826" s="1"/>
@@ -7839,23 +7974,23 @@
       <c r="B827" s="1"/>
     </row>
     <row r="828" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B828" s="6"/>
-      <c r="C828" s="6"/>
+      <c r="B828" s="5"/>
+      <c r="C828" s="5"/>
     </row>
     <row r="829" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B829" s="6"/>
-      <c r="C829" s="6"/>
+      <c r="B829" s="5"/>
+      <c r="C829" s="5"/>
     </row>
     <row r="830" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B830" s="1"/>
     </row>
     <row r="831" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B831" s="6"/>
-      <c r="C831" s="6"/>
+      <c r="B831" s="5"/>
+      <c r="C831" s="5"/>
     </row>
     <row r="832" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B832" s="6"/>
-      <c r="C832" s="6"/>
+      <c r="B832" s="5"/>
+      <c r="C832" s="5"/>
     </row>
     <row r="833" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B833" s="1"/>
@@ -7864,24 +7999,24 @@
       <c r="B834" s="1"/>
     </row>
     <row r="835" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B835" s="6"/>
-      <c r="C835" s="6"/>
+      <c r="B835" s="5"/>
+      <c r="C835" s="5"/>
     </row>
     <row r="836" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B836" s="6"/>
-      <c r="C836" s="6"/>
+      <c r="B836" s="5"/>
+      <c r="C836" s="5"/>
     </row>
     <row r="837" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B837" s="6"/>
-      <c r="C837" s="6"/>
+      <c r="B837" s="5"/>
+      <c r="C837" s="5"/>
     </row>
     <row r="838" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B838" s="6"/>
-      <c r="C838" s="6"/>
+      <c r="B838" s="5"/>
+      <c r="C838" s="5"/>
     </row>
     <row r="839" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B839" s="6"/>
-      <c r="C839" s="6"/>
+      <c r="B839" s="5"/>
+      <c r="C839" s="5"/>
     </row>
     <row r="840" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B840" s="1"/>
@@ -7890,24 +8025,24 @@
       <c r="B841" s="1"/>
     </row>
     <row r="842" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B842" s="6"/>
-      <c r="C842" s="6"/>
+      <c r="B842" s="5"/>
+      <c r="C842" s="5"/>
     </row>
     <row r="843" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B843" s="6"/>
-      <c r="C843" s="6"/>
+      <c r="B843" s="5"/>
+      <c r="C843" s="5"/>
     </row>
     <row r="844" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B844" s="6"/>
-      <c r="C844" s="6"/>
+      <c r="B844" s="5"/>
+      <c r="C844" s="5"/>
     </row>
     <row r="845" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B845" s="6"/>
-      <c r="C845" s="6"/>
+      <c r="B845" s="5"/>
+      <c r="C845" s="5"/>
     </row>
     <row r="846" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B846" s="6"/>
-      <c r="C846" s="6"/>
+      <c r="B846" s="5"/>
+      <c r="C846" s="5"/>
     </row>
     <row r="847" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B847" s="1"/>
@@ -7916,24 +8051,24 @@
       <c r="B848" s="1"/>
     </row>
     <row r="849" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B849" s="6"/>
-      <c r="C849" s="6"/>
+      <c r="B849" s="5"/>
+      <c r="C849" s="5"/>
     </row>
     <row r="850" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B850" s="6"/>
-      <c r="C850" s="6"/>
+      <c r="B850" s="5"/>
+      <c r="C850" s="5"/>
     </row>
     <row r="851" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B851" s="6"/>
-      <c r="C851" s="6"/>
+      <c r="B851" s="5"/>
+      <c r="C851" s="5"/>
     </row>
     <row r="852" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B852" s="6"/>
-      <c r="C852" s="6"/>
+      <c r="B852" s="5"/>
+      <c r="C852" s="5"/>
     </row>
     <row r="853" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B853" s="6"/>
-      <c r="C853" s="6"/>
+      <c r="B853" s="5"/>
+      <c r="C853" s="5"/>
     </row>
     <row r="854" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B854" s="1"/>
@@ -7942,24 +8077,24 @@
       <c r="B855" s="1"/>
     </row>
     <row r="856" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B856" s="6"/>
-      <c r="C856" s="6"/>
+      <c r="B856" s="5"/>
+      <c r="C856" s="5"/>
     </row>
     <row r="857" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B857" s="6"/>
-      <c r="C857" s="6"/>
+      <c r="B857" s="5"/>
+      <c r="C857" s="5"/>
     </row>
     <row r="858" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B858" s="6"/>
-      <c r="C858" s="6"/>
+      <c r="B858" s="5"/>
+      <c r="C858" s="5"/>
     </row>
     <row r="859" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B859" s="6"/>
-      <c r="C859" s="6"/>
+      <c r="B859" s="5"/>
+      <c r="C859" s="5"/>
     </row>
     <row r="860" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B860" s="6"/>
-      <c r="C860" s="6"/>
+      <c r="B860" s="5"/>
+      <c r="C860" s="5"/>
     </row>
     <row r="861" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B861" s="1"/>
@@ -7968,24 +8103,24 @@
       <c r="B862" s="1"/>
     </row>
     <row r="863" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B863" s="6"/>
-      <c r="C863" s="6"/>
+      <c r="B863" s="5"/>
+      <c r="C863" s="5"/>
     </row>
     <row r="864" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B864" s="6"/>
-      <c r="C864" s="6"/>
+      <c r="B864" s="5"/>
+      <c r="C864" s="5"/>
     </row>
     <row r="865" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B865" s="6"/>
-      <c r="C865" s="6"/>
+      <c r="B865" s="5"/>
+      <c r="C865" s="5"/>
     </row>
     <row r="866" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B866" s="6"/>
-      <c r="C866" s="6"/>
+      <c r="B866" s="5"/>
+      <c r="C866" s="5"/>
     </row>
     <row r="867" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B867" s="6"/>
-      <c r="C867" s="6"/>
+      <c r="B867" s="5"/>
+      <c r="C867" s="5"/>
     </row>
     <row r="868" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B868" s="1"/>
@@ -7994,24 +8129,24 @@
       <c r="B869" s="1"/>
     </row>
     <row r="870" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B870" s="6"/>
-      <c r="C870" s="6"/>
+      <c r="B870" s="5"/>
+      <c r="C870" s="5"/>
     </row>
     <row r="871" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B871" s="6"/>
-      <c r="C871" s="6"/>
+      <c r="B871" s="5"/>
+      <c r="C871" s="5"/>
     </row>
     <row r="872" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B872" s="6"/>
-      <c r="C872" s="6"/>
+      <c r="B872" s="5"/>
+      <c r="C872" s="5"/>
     </row>
     <row r="873" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B873" s="6"/>
-      <c r="C873" s="6"/>
+      <c r="B873" s="5"/>
+      <c r="C873" s="5"/>
     </row>
     <row r="874" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B874" s="6"/>
-      <c r="C874" s="6"/>
+      <c r="B874" s="5"/>
+      <c r="C874" s="5"/>
     </row>
     <row r="875" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B875" s="1"/>
@@ -8020,24 +8155,24 @@
       <c r="B876" s="1"/>
     </row>
     <row r="877" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B877" s="6"/>
-      <c r="C877" s="6"/>
+      <c r="B877" s="5"/>
+      <c r="C877" s="5"/>
     </row>
     <row r="878" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B878" s="6"/>
-      <c r="C878" s="6"/>
+      <c r="B878" s="5"/>
+      <c r="C878" s="5"/>
     </row>
     <row r="879" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B879" s="6"/>
-      <c r="C879" s="6"/>
+      <c r="B879" s="5"/>
+      <c r="C879" s="5"/>
     </row>
     <row r="880" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B880" s="6"/>
-      <c r="C880" s="6"/>
+      <c r="B880" s="5"/>
+      <c r="C880" s="5"/>
     </row>
     <row r="881" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B881" s="6"/>
-      <c r="C881" s="6"/>
+      <c r="B881" s="5"/>
+      <c r="C881" s="5"/>
     </row>
     <row r="882" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B882" s="1"/>
@@ -8046,24 +8181,24 @@
       <c r="B883" s="1"/>
     </row>
     <row r="884" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B884" s="6"/>
-      <c r="C884" s="6"/>
+      <c r="B884" s="5"/>
+      <c r="C884" s="5"/>
     </row>
     <row r="885" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B885" s="6"/>
-      <c r="C885" s="6"/>
+      <c r="B885" s="5"/>
+      <c r="C885" s="5"/>
     </row>
     <row r="886" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B886" s="6"/>
-      <c r="C886" s="6"/>
+      <c r="B886" s="5"/>
+      <c r="C886" s="5"/>
     </row>
     <row r="887" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B887" s="6"/>
-      <c r="C887" s="6"/>
+      <c r="B887" s="5"/>
+      <c r="C887" s="5"/>
     </row>
     <row r="888" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B888" s="6"/>
-      <c r="C888" s="6"/>
+      <c r="B888" s="5"/>
+      <c r="C888" s="5"/>
     </row>
     <row r="889" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B889" s="1"/>
@@ -8072,24 +8207,24 @@
       <c r="B890" s="1"/>
     </row>
     <row r="891" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B891" s="6"/>
-      <c r="C891" s="6"/>
+      <c r="B891" s="5"/>
+      <c r="C891" s="5"/>
     </row>
     <row r="892" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B892" s="6"/>
-      <c r="C892" s="6"/>
+      <c r="B892" s="5"/>
+      <c r="C892" s="5"/>
     </row>
     <row r="893" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B893" s="6"/>
-      <c r="C893" s="6"/>
+      <c r="B893" s="5"/>
+      <c r="C893" s="5"/>
     </row>
     <row r="894" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B894" s="6"/>
-      <c r="C894" s="6"/>
+      <c r="B894" s="5"/>
+      <c r="C894" s="5"/>
     </row>
     <row r="895" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B895" s="6"/>
-      <c r="C895" s="6"/>
+      <c r="B895" s="5"/>
+      <c r="C895" s="5"/>
     </row>
     <row r="896" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B896" s="1"/>
@@ -8098,24 +8233,24 @@
       <c r="B897" s="1"/>
     </row>
     <row r="898" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B898" s="6"/>
-      <c r="C898" s="6"/>
+      <c r="B898" s="5"/>
+      <c r="C898" s="5"/>
     </row>
     <row r="899" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B899" s="6"/>
-      <c r="C899" s="6"/>
+      <c r="B899" s="5"/>
+      <c r="C899" s="5"/>
     </row>
     <row r="900" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B900" s="6"/>
-      <c r="C900" s="6"/>
+      <c r="B900" s="5"/>
+      <c r="C900" s="5"/>
     </row>
     <row r="901" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B901" s="6"/>
-      <c r="C901" s="6"/>
+      <c r="B901" s="5"/>
+      <c r="C901" s="5"/>
     </row>
     <row r="902" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B902" s="6"/>
-      <c r="C902" s="6"/>
+      <c r="B902" s="5"/>
+      <c r="C902" s="5"/>
     </row>
     <row r="903" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B903" s="1"/>
@@ -8124,24 +8259,24 @@
       <c r="B904" s="1"/>
     </row>
     <row r="905" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B905" s="6"/>
-      <c r="C905" s="6"/>
+      <c r="B905" s="5"/>
+      <c r="C905" s="5"/>
     </row>
     <row r="906" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B906" s="6"/>
-      <c r="C906" s="6"/>
+      <c r="B906" s="5"/>
+      <c r="C906" s="5"/>
     </row>
     <row r="907" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B907" s="6"/>
-      <c r="C907" s="6"/>
+      <c r="B907" s="5"/>
+      <c r="C907" s="5"/>
     </row>
     <row r="908" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B908" s="6"/>
-      <c r="C908" s="6"/>
+      <c r="B908" s="5"/>
+      <c r="C908" s="5"/>
     </row>
     <row r="909" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B909" s="6"/>
-      <c r="C909" s="6"/>
+      <c r="B909" s="5"/>
+      <c r="C909" s="5"/>
     </row>
     <row r="910" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B910" s="1"/>
@@ -8150,24 +8285,24 @@
       <c r="B911" s="1"/>
     </row>
     <row r="912" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B912" s="6"/>
-      <c r="C912" s="6"/>
+      <c r="B912" s="5"/>
+      <c r="C912" s="5"/>
     </row>
     <row r="913" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B913" s="6"/>
-      <c r="C913" s="6"/>
+      <c r="B913" s="5"/>
+      <c r="C913" s="5"/>
     </row>
     <row r="914" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B914" s="6"/>
-      <c r="C914" s="6"/>
+      <c r="B914" s="5"/>
+      <c r="C914" s="5"/>
     </row>
     <row r="915" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B915" s="6"/>
-      <c r="C915" s="6"/>
+      <c r="B915" s="5"/>
+      <c r="C915" s="5"/>
     </row>
     <row r="916" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B916" s="6"/>
-      <c r="C916" s="6"/>
+      <c r="B916" s="5"/>
+      <c r="C916" s="5"/>
     </row>
     <row r="917" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B917" s="1"/>
@@ -8176,24 +8311,24 @@
       <c r="B918" s="1"/>
     </row>
     <row r="919" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B919" s="6"/>
-      <c r="C919" s="6"/>
+      <c r="B919" s="5"/>
+      <c r="C919" s="5"/>
     </row>
     <row r="920" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B920" s="6"/>
-      <c r="C920" s="6"/>
+      <c r="B920" s="5"/>
+      <c r="C920" s="5"/>
     </row>
     <row r="921" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B921" s="6"/>
-      <c r="C921" s="6"/>
+      <c r="B921" s="5"/>
+      <c r="C921" s="5"/>
     </row>
     <row r="922" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B922" s="6"/>
-      <c r="C922" s="6"/>
+      <c r="B922" s="5"/>
+      <c r="C922" s="5"/>
     </row>
     <row r="923" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B923" s="6"/>
-      <c r="C923" s="6"/>
+      <c r="B923" s="5"/>
+      <c r="C923" s="5"/>
     </row>
     <row r="924" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B924" s="1"/>
@@ -8202,24 +8337,24 @@
       <c r="B925" s="1"/>
     </row>
     <row r="926" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B926" s="6"/>
-      <c r="C926" s="6"/>
+      <c r="B926" s="5"/>
+      <c r="C926" s="5"/>
     </row>
     <row r="927" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B927" s="6"/>
-      <c r="C927" s="6"/>
+      <c r="B927" s="5"/>
+      <c r="C927" s="5"/>
     </row>
     <row r="928" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B928" s="6"/>
-      <c r="C928" s="6"/>
+      <c r="B928" s="5"/>
+      <c r="C928" s="5"/>
     </row>
     <row r="929" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B929" s="6"/>
-      <c r="C929" s="6"/>
+      <c r="B929" s="5"/>
+      <c r="C929" s="5"/>
     </row>
     <row r="930" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B930" s="6"/>
-      <c r="C930" s="6"/>
+      <c r="B930" s="5"/>
+      <c r="C930" s="5"/>
     </row>
     <row r="931" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B931" s="1"/>
@@ -8228,24 +8363,24 @@
       <c r="B932" s="1"/>
     </row>
     <row r="933" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B933" s="6"/>
-      <c r="C933" s="6"/>
+      <c r="B933" s="5"/>
+      <c r="C933" s="5"/>
     </row>
     <row r="934" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B934" s="6"/>
-      <c r="C934" s="6"/>
+      <c r="B934" s="5"/>
+      <c r="C934" s="5"/>
     </row>
     <row r="935" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B935" s="6"/>
-      <c r="C935" s="6"/>
+      <c r="B935" s="5"/>
+      <c r="C935" s="5"/>
     </row>
     <row r="936" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B936" s="6"/>
-      <c r="C936" s="6"/>
+      <c r="B936" s="5"/>
+      <c r="C936" s="5"/>
     </row>
     <row r="937" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B937" s="6"/>
-      <c r="C937" s="6"/>
+      <c r="B937" s="5"/>
+      <c r="C937" s="5"/>
     </row>
     <row r="938" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B938" s="1"/>
@@ -8254,24 +8389,24 @@
       <c r="B939" s="1"/>
     </row>
     <row r="940" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B940" s="6"/>
-      <c r="C940" s="6"/>
+      <c r="B940" s="5"/>
+      <c r="C940" s="5"/>
     </row>
     <row r="941" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B941" s="6"/>
-      <c r="C941" s="6"/>
+      <c r="B941" s="5"/>
+      <c r="C941" s="5"/>
     </row>
     <row r="942" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B942" s="6"/>
-      <c r="C942" s="6"/>
+      <c r="B942" s="5"/>
+      <c r="C942" s="5"/>
     </row>
     <row r="943" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B943" s="6"/>
-      <c r="C943" s="6"/>
+      <c r="B943" s="5"/>
+      <c r="C943" s="5"/>
     </row>
     <row r="944" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B944" s="6"/>
-      <c r="C944" s="6"/>
+      <c r="B944" s="5"/>
+      <c r="C944" s="5"/>
     </row>
     <row r="945" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B945" s="1"/>
@@ -8280,24 +8415,24 @@
       <c r="B946" s="1"/>
     </row>
     <row r="947" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B947" s="6"/>
-      <c r="C947" s="6"/>
+      <c r="B947" s="5"/>
+      <c r="C947" s="5"/>
     </row>
     <row r="948" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B948" s="6"/>
-      <c r="C948" s="6"/>
+      <c r="B948" s="5"/>
+      <c r="C948" s="5"/>
     </row>
     <row r="949" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B949" s="6"/>
-      <c r="C949" s="6"/>
+      <c r="B949" s="5"/>
+      <c r="C949" s="5"/>
     </row>
     <row r="950" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B950" s="6"/>
-      <c r="C950" s="6"/>
+      <c r="B950" s="5"/>
+      <c r="C950" s="5"/>
     </row>
     <row r="951" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B951" s="6"/>
-      <c r="C951" s="6"/>
+      <c r="B951" s="5"/>
+      <c r="C951" s="5"/>
     </row>
     <row r="952" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B952" s="1"/>
@@ -8309,20 +8444,20 @@
       <c r="B954" s="1"/>
     </row>
     <row r="955" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B955" s="6"/>
-      <c r="C955" s="6"/>
+      <c r="B955" s="5"/>
+      <c r="C955" s="5"/>
     </row>
     <row r="956" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B956" s="6"/>
-      <c r="C956" s="6"/>
+      <c r="B956" s="5"/>
+      <c r="C956" s="5"/>
     </row>
     <row r="957" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B957" s="6"/>
-      <c r="C957" s="6"/>
+      <c r="B957" s="5"/>
+      <c r="C957" s="5"/>
     </row>
     <row r="958" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B958" s="6"/>
-      <c r="C958" s="6"/>
+      <c r="B958" s="5"/>
+      <c r="C958" s="5"/>
     </row>
     <row r="959" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B959" s="1"/>
@@ -8331,24 +8466,24 @@
       <c r="B960" s="1"/>
     </row>
     <row r="961" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B961" s="6"/>
-      <c r="C961" s="6"/>
+      <c r="B961" s="5"/>
+      <c r="C961" s="5"/>
     </row>
     <row r="962" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B962" s="6"/>
-      <c r="C962" s="6"/>
+      <c r="B962" s="5"/>
+      <c r="C962" s="5"/>
     </row>
     <row r="963" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B963" s="6"/>
-      <c r="C963" s="6"/>
+      <c r="B963" s="5"/>
+      <c r="C963" s="5"/>
     </row>
     <row r="964" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B964" s="6"/>
-      <c r="C964" s="6"/>
+      <c r="B964" s="5"/>
+      <c r="C964" s="5"/>
     </row>
     <row r="965" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B965" s="6"/>
-      <c r="C965" s="6"/>
+      <c r="B965" s="5"/>
+      <c r="C965" s="5"/>
     </row>
     <row r="966" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B966" s="1"/>
@@ -8357,24 +8492,24 @@
       <c r="B967" s="1"/>
     </row>
     <row r="968" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B968" s="6"/>
-      <c r="C968" s="6"/>
+      <c r="B968" s="5"/>
+      <c r="C968" s="5"/>
     </row>
     <row r="969" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B969" s="6"/>
-      <c r="C969" s="6"/>
+      <c r="B969" s="5"/>
+      <c r="C969" s="5"/>
     </row>
     <row r="970" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B970" s="6"/>
-      <c r="C970" s="6"/>
+      <c r="B970" s="5"/>
+      <c r="C970" s="5"/>
     </row>
     <row r="971" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B971" s="6"/>
-      <c r="C971" s="6"/>
+      <c r="B971" s="5"/>
+      <c r="C971" s="5"/>
     </row>
     <row r="972" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B972" s="6"/>
-      <c r="C972" s="6"/>
+      <c r="B972" s="5"/>
+      <c r="C972" s="5"/>
     </row>
     <row r="973" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B973" s="1"/>
@@ -8383,24 +8518,24 @@
       <c r="B974" s="1"/>
     </row>
     <row r="975" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B975" s="6"/>
-      <c r="C975" s="6"/>
+      <c r="B975" s="5"/>
+      <c r="C975" s="5"/>
     </row>
     <row r="976" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B976" s="6"/>
-      <c r="C976" s="6"/>
+      <c r="B976" s="5"/>
+      <c r="C976" s="5"/>
     </row>
     <row r="977" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B977" s="6"/>
-      <c r="C977" s="6"/>
+      <c r="B977" s="5"/>
+      <c r="C977" s="5"/>
     </row>
     <row r="978" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B978" s="6"/>
-      <c r="C978" s="6"/>
+      <c r="B978" s="5"/>
+      <c r="C978" s="5"/>
     </row>
     <row r="979" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B979" s="6"/>
-      <c r="C979" s="6"/>
+      <c r="B979" s="5"/>
+      <c r="C979" s="5"/>
     </row>
     <row r="980" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B980" s="1"/>
@@ -8409,24 +8544,24 @@
       <c r="B981" s="1"/>
     </row>
     <row r="982" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B982" s="6"/>
-      <c r="C982" s="6"/>
+      <c r="B982" s="5"/>
+      <c r="C982" s="5"/>
     </row>
     <row r="983" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B983" s="6"/>
-      <c r="C983" s="6"/>
+      <c r="B983" s="5"/>
+      <c r="C983" s="5"/>
     </row>
     <row r="984" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B984" s="6"/>
-      <c r="C984" s="6"/>
+      <c r="B984" s="5"/>
+      <c r="C984" s="5"/>
     </row>
     <row r="985" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B985" s="6"/>
-      <c r="C985" s="6"/>
+      <c r="B985" s="5"/>
+      <c r="C985" s="5"/>
     </row>
     <row r="986" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B986" s="6"/>
-      <c r="C986" s="6"/>
+      <c r="B986" s="5"/>
+      <c r="C986" s="5"/>
     </row>
     <row r="987" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B987" s="1"/>
@@ -8435,24 +8570,24 @@
       <c r="B988" s="1"/>
     </row>
     <row r="989" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B989" s="6"/>
-      <c r="C989" s="6"/>
+      <c r="B989" s="5"/>
+      <c r="C989" s="5"/>
     </row>
     <row r="990" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B990" s="6"/>
-      <c r="C990" s="6"/>
+      <c r="B990" s="5"/>
+      <c r="C990" s="5"/>
     </row>
     <row r="991" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B991" s="6"/>
-      <c r="C991" s="6"/>
+      <c r="B991" s="5"/>
+      <c r="C991" s="5"/>
     </row>
     <row r="992" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B992" s="6"/>
-      <c r="C992" s="6"/>
+      <c r="B992" s="5"/>
+      <c r="C992" s="5"/>
     </row>
     <row r="993" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B993" s="6"/>
-      <c r="C993" s="6"/>
+      <c r="B993" s="5"/>
+      <c r="C993" s="5"/>
     </row>
     <row r="994" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B994" s="1"/>
@@ -8461,24 +8596,24 @@
       <c r="B995" s="1"/>
     </row>
     <row r="996" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B996" s="6"/>
-      <c r="C996" s="6"/>
+      <c r="B996" s="5"/>
+      <c r="C996" s="5"/>
     </row>
     <row r="997" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B997" s="6"/>
-      <c r="C997" s="6"/>
+      <c r="B997" s="5"/>
+      <c r="C997" s="5"/>
     </row>
     <row r="998" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B998" s="6"/>
-      <c r="C998" s="6"/>
+      <c r="B998" s="5"/>
+      <c r="C998" s="5"/>
     </row>
     <row r="999" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B999" s="6"/>
-      <c r="C999" s="6"/>
+      <c r="B999" s="5"/>
+      <c r="C999" s="5"/>
     </row>
     <row r="1000" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1000" s="6"/>
-      <c r="C1000" s="6"/>
+      <c r="B1000" s="5"/>
+      <c r="C1000" s="5"/>
     </row>
     <row r="1001" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1001" s="1"/>
@@ -8487,24 +8622,24 @@
       <c r="B1002" s="1"/>
     </row>
     <row r="1003" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1003" s="6"/>
-      <c r="C1003" s="6"/>
+      <c r="B1003" s="5"/>
+      <c r="C1003" s="5"/>
     </row>
     <row r="1004" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1004" s="6"/>
-      <c r="C1004" s="6"/>
+      <c r="B1004" s="5"/>
+      <c r="C1004" s="5"/>
     </row>
     <row r="1005" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1005" s="6"/>
-      <c r="C1005" s="6"/>
+      <c r="B1005" s="5"/>
+      <c r="C1005" s="5"/>
     </row>
     <row r="1006" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1006" s="6"/>
-      <c r="C1006" s="6"/>
+      <c r="B1006" s="5"/>
+      <c r="C1006" s="5"/>
     </row>
     <row r="1007" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1007" s="6"/>
-      <c r="C1007" s="6"/>
+      <c r="B1007" s="5"/>
+      <c r="C1007" s="5"/>
     </row>
     <row r="1008" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1008" s="1"/>
@@ -8513,24 +8648,24 @@
       <c r="B1009" s="1"/>
     </row>
     <row r="1010" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1010" s="6"/>
-      <c r="C1010" s="6"/>
+      <c r="B1010" s="5"/>
+      <c r="C1010" s="5"/>
     </row>
     <row r="1011" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1011" s="6"/>
-      <c r="C1011" s="6"/>
+      <c r="B1011" s="5"/>
+      <c r="C1011" s="5"/>
     </row>
     <row r="1012" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1012" s="6"/>
-      <c r="C1012" s="6"/>
+      <c r="B1012" s="5"/>
+      <c r="C1012" s="5"/>
     </row>
     <row r="1013" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1013" s="6"/>
-      <c r="C1013" s="6"/>
+      <c r="B1013" s="5"/>
+      <c r="C1013" s="5"/>
     </row>
     <row r="1014" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1014" s="6"/>
-      <c r="C1014" s="6"/>
+      <c r="B1014" s="5"/>
+      <c r="C1014" s="5"/>
     </row>
     <row r="1015" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1015" s="1"/>
@@ -8539,24 +8674,24 @@
       <c r="B1016" s="1"/>
     </row>
     <row r="1017" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1017" s="6"/>
-      <c r="C1017" s="6"/>
+      <c r="B1017" s="5"/>
+      <c r="C1017" s="5"/>
     </row>
     <row r="1018" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1018" s="6"/>
-      <c r="C1018" s="6"/>
+      <c r="B1018" s="5"/>
+      <c r="C1018" s="5"/>
     </row>
     <row r="1019" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1019" s="6"/>
-      <c r="C1019" s="6"/>
+      <c r="B1019" s="5"/>
+      <c r="C1019" s="5"/>
     </row>
     <row r="1020" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1020" s="6"/>
-      <c r="C1020" s="6"/>
+      <c r="B1020" s="5"/>
+      <c r="C1020" s="5"/>
     </row>
     <row r="1021" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1021" s="6"/>
-      <c r="C1021" s="6"/>
+      <c r="B1021" s="5"/>
+      <c r="C1021" s="5"/>
     </row>
     <row r="1022" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1022" s="1"/>
@@ -8565,24 +8700,24 @@
       <c r="B1023" s="1"/>
     </row>
     <row r="1024" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1024" s="6"/>
-      <c r="C1024" s="6"/>
+      <c r="B1024" s="5"/>
+      <c r="C1024" s="5"/>
     </row>
     <row r="1025" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1025" s="6"/>
-      <c r="C1025" s="6"/>
+      <c r="B1025" s="5"/>
+      <c r="C1025" s="5"/>
     </row>
     <row r="1026" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1026" s="6"/>
-      <c r="C1026" s="6"/>
+      <c r="B1026" s="5"/>
+      <c r="C1026" s="5"/>
     </row>
     <row r="1027" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1027" s="6"/>
-      <c r="C1027" s="6"/>
+      <c r="B1027" s="5"/>
+      <c r="C1027" s="5"/>
     </row>
     <row r="1028" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1028" s="6"/>
-      <c r="C1028" s="6"/>
+      <c r="B1028" s="5"/>
+      <c r="C1028" s="5"/>
     </row>
     <row r="1029" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1029" s="1"/>
@@ -8591,24 +8726,24 @@
       <c r="B1030" s="1"/>
     </row>
     <row r="1031" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1031" s="6"/>
-      <c r="C1031" s="6"/>
+      <c r="B1031" s="5"/>
+      <c r="C1031" s="5"/>
     </row>
     <row r="1032" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1032" s="6"/>
-      <c r="C1032" s="6"/>
+      <c r="B1032" s="5"/>
+      <c r="C1032" s="5"/>
     </row>
     <row r="1033" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1033" s="6"/>
-      <c r="C1033" s="6"/>
+      <c r="B1033" s="5"/>
+      <c r="C1033" s="5"/>
     </row>
     <row r="1034" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1034" s="6"/>
-      <c r="C1034" s="6"/>
+      <c r="B1034" s="5"/>
+      <c r="C1034" s="5"/>
     </row>
     <row r="1035" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1035" s="6"/>
-      <c r="C1035" s="6"/>
+      <c r="B1035" s="5"/>
+      <c r="C1035" s="5"/>
     </row>
     <row r="1036" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1036" s="1"/>
@@ -8617,24 +8752,24 @@
       <c r="B1037" s="1"/>
     </row>
     <row r="1038" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1038" s="6"/>
-      <c r="C1038" s="6"/>
+      <c r="B1038" s="5"/>
+      <c r="C1038" s="5"/>
     </row>
     <row r="1039" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1039" s="6"/>
-      <c r="C1039" s="6"/>
+      <c r="B1039" s="5"/>
+      <c r="C1039" s="5"/>
     </row>
     <row r="1040" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1040" s="6"/>
-      <c r="C1040" s="6"/>
+      <c r="B1040" s="5"/>
+      <c r="C1040" s="5"/>
     </row>
     <row r="1041" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1041" s="6"/>
-      <c r="C1041" s="6"/>
+      <c r="B1041" s="5"/>
+      <c r="C1041" s="5"/>
     </row>
     <row r="1042" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1042" s="6"/>
-      <c r="C1042" s="6"/>
+      <c r="B1042" s="5"/>
+      <c r="C1042" s="5"/>
     </row>
     <row r="1043" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1043" s="1"/>
@@ -8643,24 +8778,24 @@
       <c r="B1044" s="1"/>
     </row>
     <row r="1045" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1045" s="6"/>
-      <c r="C1045" s="6"/>
+      <c r="B1045" s="5"/>
+      <c r="C1045" s="5"/>
     </row>
     <row r="1046" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1046" s="6"/>
-      <c r="C1046" s="6"/>
+      <c r="B1046" s="5"/>
+      <c r="C1046" s="5"/>
     </row>
     <row r="1047" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1047" s="6"/>
-      <c r="C1047" s="6"/>
+      <c r="B1047" s="5"/>
+      <c r="C1047" s="5"/>
     </row>
     <row r="1048" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1048" s="6"/>
-      <c r="C1048" s="6"/>
+      <c r="B1048" s="5"/>
+      <c r="C1048" s="5"/>
     </row>
     <row r="1049" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1049" s="6"/>
-      <c r="C1049" s="6"/>
+      <c r="B1049" s="5"/>
+      <c r="C1049" s="5"/>
     </row>
     <row r="1050" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1050" s="1"/>
@@ -8669,12 +8804,12 @@
       <c r="B1051" s="1"/>
     </row>
     <row r="1052" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1052" s="6"/>
-      <c r="C1052" s="6"/>
+      <c r="B1052" s="5"/>
+      <c r="C1052" s="5"/>
     </row>
     <row r="1053" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1053" s="6"/>
-      <c r="C1053" s="6"/>
+      <c r="B1053" s="5"/>
+      <c r="C1053" s="5"/>
     </row>
     <row r="1054" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1054" s="1"/>
@@ -8692,24 +8827,24 @@
       <c r="B1058" s="1"/>
     </row>
     <row r="1059" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1059" s="6"/>
-      <c r="C1059" s="6"/>
+      <c r="B1059" s="5"/>
+      <c r="C1059" s="5"/>
     </row>
     <row r="1060" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1060" s="6"/>
-      <c r="C1060" s="6"/>
+      <c r="B1060" s="5"/>
+      <c r="C1060" s="5"/>
     </row>
     <row r="1061" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1061" s="6"/>
-      <c r="C1061" s="6"/>
+      <c r="B1061" s="5"/>
+      <c r="C1061" s="5"/>
     </row>
     <row r="1062" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1062" s="6"/>
-      <c r="C1062" s="6"/>
+      <c r="B1062" s="5"/>
+      <c r="C1062" s="5"/>
     </row>
     <row r="1063" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1063" s="6"/>
-      <c r="C1063" s="6"/>
+      <c r="B1063" s="5"/>
+      <c r="C1063" s="5"/>
     </row>
     <row r="1064" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1064" s="1"/>
@@ -8718,23 +8853,23 @@
       <c r="B1065" s="1"/>
     </row>
     <row r="1066" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1066" s="6"/>
-      <c r="C1066" s="6"/>
+      <c r="B1066" s="5"/>
+      <c r="C1066" s="5"/>
     </row>
     <row r="1067" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1067" s="1"/>
     </row>
     <row r="1068" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1068" s="6"/>
-      <c r="C1068" s="6"/>
+      <c r="B1068" s="5"/>
+      <c r="C1068" s="5"/>
     </row>
     <row r="1069" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1069" s="6"/>
-      <c r="C1069" s="6"/>
+      <c r="B1069" s="5"/>
+      <c r="C1069" s="5"/>
     </row>
     <row r="1070" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1070" s="6"/>
-      <c r="C1070" s="6"/>
+      <c r="B1070" s="5"/>
+      <c r="C1070" s="5"/>
     </row>
     <row r="1071" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1071" s="1"/>
@@ -8743,23 +8878,23 @@
       <c r="B1072" s="1"/>
     </row>
     <row r="1073" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1073" s="6"/>
-      <c r="C1073" s="6"/>
+      <c r="B1073" s="5"/>
+      <c r="C1073" s="5"/>
     </row>
     <row r="1074" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1074" s="6"/>
-      <c r="C1074" s="6"/>
+      <c r="B1074" s="5"/>
+      <c r="C1074" s="5"/>
     </row>
     <row r="1075" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1075" s="1"/>
     </row>
     <row r="1076" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1076" s="6"/>
-      <c r="C1076" s="6"/>
+      <c r="B1076" s="5"/>
+      <c r="C1076" s="5"/>
     </row>
     <row r="1077" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1077" s="6"/>
-      <c r="C1077" s="6"/>
+      <c r="B1077" s="5"/>
+      <c r="C1077" s="5"/>
     </row>
     <row r="1078" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1078" s="1"/>
@@ -8768,24 +8903,24 @@
       <c r="B1079" s="1"/>
     </row>
     <row r="1080" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1080" s="6"/>
-      <c r="C1080" s="6"/>
+      <c r="B1080" s="5"/>
+      <c r="C1080" s="5"/>
     </row>
     <row r="1081" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1081" s="6"/>
-      <c r="C1081" s="6"/>
+      <c r="B1081" s="5"/>
+      <c r="C1081" s="5"/>
     </row>
     <row r="1082" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1082" s="6"/>
-      <c r="C1082" s="6"/>
+      <c r="B1082" s="5"/>
+      <c r="C1082" s="5"/>
     </row>
     <row r="1083" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1083" s="6"/>
-      <c r="C1083" s="6"/>
+      <c r="B1083" s="5"/>
+      <c r="C1083" s="5"/>
     </row>
     <row r="1084" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1084" s="6"/>
-      <c r="C1084" s="6"/>
+      <c r="B1084" s="5"/>
+      <c r="C1084" s="5"/>
     </row>
     <row r="1085" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1085" s="1"/>
@@ -8794,24 +8929,24 @@
       <c r="B1086" s="1"/>
     </row>
     <row r="1087" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1087" s="6"/>
-      <c r="C1087" s="6"/>
+      <c r="B1087" s="5"/>
+      <c r="C1087" s="5"/>
     </row>
     <row r="1088" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1088" s="6"/>
-      <c r="C1088" s="6"/>
+      <c r="B1088" s="5"/>
+      <c r="C1088" s="5"/>
     </row>
     <row r="1089" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1089" s="6"/>
-      <c r="C1089" s="6"/>
+      <c r="B1089" s="5"/>
+      <c r="C1089" s="5"/>
     </row>
     <row r="1090" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1090" s="6"/>
-      <c r="C1090" s="6"/>
+      <c r="B1090" s="5"/>
+      <c r="C1090" s="5"/>
     </row>
     <row r="1091" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1091" s="6"/>
-      <c r="C1091" s="6"/>
+      <c r="B1091" s="5"/>
+      <c r="C1091" s="5"/>
     </row>
     <row r="1092" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1092" s="1"/>
@@ -8820,24 +8955,24 @@
       <c r="B1093" s="1"/>
     </row>
     <row r="1094" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1094" s="6"/>
-      <c r="C1094" s="6"/>
+      <c r="B1094" s="5"/>
+      <c r="C1094" s="5"/>
     </row>
     <row r="1095" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1095" s="6"/>
-      <c r="C1095" s="6"/>
+      <c r="B1095" s="5"/>
+      <c r="C1095" s="5"/>
     </row>
     <row r="1096" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1096" s="6"/>
-      <c r="C1096" s="6"/>
+      <c r="B1096" s="5"/>
+      <c r="C1096" s="5"/>
     </row>
     <row r="1097" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1097" s="6"/>
-      <c r="C1097" s="6"/>
+      <c r="B1097" s="5"/>
+      <c r="C1097" s="5"/>
     </row>
     <row r="1098" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1098" s="6"/>
-      <c r="C1098" s="6"/>
+      <c r="B1098" s="5"/>
+      <c r="C1098" s="5"/>
     </row>
     <row r="1099" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1099" s="1"/>
@@ -8846,24 +8981,24 @@
       <c r="B1100" s="1"/>
     </row>
     <row r="1101" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1101" s="6"/>
-      <c r="C1101" s="6"/>
+      <c r="B1101" s="5"/>
+      <c r="C1101" s="5"/>
     </row>
     <row r="1102" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1102" s="6"/>
-      <c r="C1102" s="6"/>
+      <c r="B1102" s="5"/>
+      <c r="C1102" s="5"/>
     </row>
     <row r="1103" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1103" s="6"/>
-      <c r="C1103" s="6"/>
+      <c r="B1103" s="5"/>
+      <c r="C1103" s="5"/>
     </row>
     <row r="1104" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1104" s="6"/>
-      <c r="C1104" s="6"/>
+      <c r="B1104" s="5"/>
+      <c r="C1104" s="5"/>
     </row>
     <row r="1105" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1105" s="6"/>
-      <c r="C1105" s="6"/>
+      <c r="B1105" s="5"/>
+      <c r="C1105" s="5"/>
     </row>
     <row r="1106" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1106" s="1"/>
@@ -8872,24 +9007,24 @@
       <c r="B1107" s="1"/>
     </row>
     <row r="1108" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1108" s="6"/>
-      <c r="C1108" s="6"/>
+      <c r="B1108" s="5"/>
+      <c r="C1108" s="5"/>
     </row>
     <row r="1109" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1109" s="6"/>
-      <c r="C1109" s="6"/>
+      <c r="B1109" s="5"/>
+      <c r="C1109" s="5"/>
     </row>
     <row r="1110" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1110" s="6"/>
-      <c r="C1110" s="6"/>
+      <c r="B1110" s="5"/>
+      <c r="C1110" s="5"/>
     </row>
     <row r="1111" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1111" s="6"/>
-      <c r="C1111" s="6"/>
+      <c r="B1111" s="5"/>
+      <c r="C1111" s="5"/>
     </row>
     <row r="1112" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1112" s="6"/>
-      <c r="C1112" s="6"/>
+      <c r="B1112" s="5"/>
+      <c r="C1112" s="5"/>
     </row>
     <row r="1113" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1113" s="1"/>
@@ -8898,24 +9033,24 @@
       <c r="B1114" s="1"/>
     </row>
     <row r="1115" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1115" s="6"/>
-      <c r="C1115" s="6"/>
+      <c r="B1115" s="5"/>
+      <c r="C1115" s="5"/>
     </row>
     <row r="1116" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1116" s="6"/>
-      <c r="C1116" s="6"/>
+      <c r="B1116" s="5"/>
+      <c r="C1116" s="5"/>
     </row>
     <row r="1117" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1117" s="6"/>
-      <c r="C1117" s="6"/>
+      <c r="B1117" s="5"/>
+      <c r="C1117" s="5"/>
     </row>
     <row r="1118" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1118" s="6"/>
-      <c r="C1118" s="6"/>
+      <c r="B1118" s="5"/>
+      <c r="C1118" s="5"/>
     </row>
     <row r="1119" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1119" s="6"/>
-      <c r="C1119" s="6"/>
+      <c r="B1119" s="5"/>
+      <c r="C1119" s="5"/>
     </row>
     <row r="1120" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1120" s="1"/>
@@ -8933,12 +9068,12 @@
       <c r="B1124" s="1"/>
     </row>
     <row r="1125" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1125" s="6"/>
-      <c r="C1125" s="6"/>
+      <c r="B1125" s="5"/>
+      <c r="C1125" s="5"/>
     </row>
     <row r="1126" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1126" s="6"/>
-      <c r="C1126" s="6"/>
+      <c r="B1126" s="5"/>
+      <c r="C1126" s="5"/>
     </row>
     <row r="1127" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1127" s="1"/>
@@ -8947,24 +9082,24 @@
       <c r="B1128" s="1"/>
     </row>
     <row r="1129" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1129" s="6"/>
-      <c r="C1129" s="6"/>
+      <c r="B1129" s="5"/>
+      <c r="C1129" s="5"/>
     </row>
     <row r="1130" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1130" s="6"/>
-      <c r="C1130" s="6"/>
+      <c r="B1130" s="5"/>
+      <c r="C1130" s="5"/>
     </row>
     <row r="1131" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1131" s="6"/>
-      <c r="C1131" s="6"/>
+      <c r="B1131" s="5"/>
+      <c r="C1131" s="5"/>
     </row>
     <row r="1132" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1132" s="6"/>
-      <c r="C1132" s="6"/>
+      <c r="B1132" s="5"/>
+      <c r="C1132" s="5"/>
     </row>
     <row r="1133" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1133" s="6"/>
-      <c r="C1133" s="6"/>
+      <c r="B1133" s="5"/>
+      <c r="C1133" s="5"/>
     </row>
     <row r="1134" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1134" s="1"/>
@@ -8973,24 +9108,24 @@
       <c r="B1135" s="1"/>
     </row>
     <row r="1136" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1136" s="6"/>
-      <c r="C1136" s="6"/>
+      <c r="B1136" s="5"/>
+      <c r="C1136" s="5"/>
     </row>
     <row r="1137" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1137" s="6"/>
-      <c r="C1137" s="6"/>
+      <c r="B1137" s="5"/>
+      <c r="C1137" s="5"/>
     </row>
     <row r="1138" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1138" s="6"/>
-      <c r="C1138" s="6"/>
+      <c r="B1138" s="5"/>
+      <c r="C1138" s="5"/>
     </row>
     <row r="1139" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1139" s="6"/>
-      <c r="C1139" s="6"/>
+      <c r="B1139" s="5"/>
+      <c r="C1139" s="5"/>
     </row>
     <row r="1140" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1140" s="6"/>
-      <c r="C1140" s="6"/>
+      <c r="B1140" s="5"/>
+      <c r="C1140" s="5"/>
     </row>
     <row r="1141" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1141" s="1"/>
@@ -8999,24 +9134,24 @@
       <c r="B1142" s="1"/>
     </row>
     <row r="1143" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1143" s="6"/>
-      <c r="C1143" s="6"/>
+      <c r="B1143" s="5"/>
+      <c r="C1143" s="5"/>
     </row>
     <row r="1144" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1144" s="6"/>
-      <c r="C1144" s="6"/>
+      <c r="B1144" s="5"/>
+      <c r="C1144" s="5"/>
     </row>
     <row r="1145" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1145" s="6"/>
-      <c r="C1145" s="6"/>
+      <c r="B1145" s="5"/>
+      <c r="C1145" s="5"/>
     </row>
     <row r="1146" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1146" s="6"/>
-      <c r="C1146" s="6"/>
+      <c r="B1146" s="5"/>
+      <c r="C1146" s="5"/>
     </row>
     <row r="1147" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1147" s="6"/>
-      <c r="C1147" s="6"/>
+      <c r="B1147" s="5"/>
+      <c r="C1147" s="5"/>
     </row>
     <row r="1148" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1148" s="1"/>
@@ -9028,20 +9163,20 @@
       <c r="B1150" s="1"/>
     </row>
     <row r="1151" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1151" s="6"/>
-      <c r="C1151" s="6"/>
+      <c r="B1151" s="5"/>
+      <c r="C1151" s="5"/>
     </row>
     <row r="1152" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1152" s="6"/>
-      <c r="C1152" s="6"/>
+      <c r="B1152" s="5"/>
+      <c r="C1152" s="5"/>
     </row>
     <row r="1153" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1153" s="6"/>
-      <c r="C1153" s="6"/>
+      <c r="B1153" s="5"/>
+      <c r="C1153" s="5"/>
     </row>
     <row r="1154" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1154" s="6"/>
-      <c r="C1154" s="6"/>
+      <c r="B1154" s="5"/>
+      <c r="C1154" s="5"/>
     </row>
     <row r="1155" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1155" s="1"/>
@@ -9050,24 +9185,24 @@
       <c r="B1156" s="1"/>
     </row>
     <row r="1157" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1157" s="6"/>
-      <c r="C1157" s="6"/>
+      <c r="B1157" s="5"/>
+      <c r="C1157" s="5"/>
     </row>
     <row r="1158" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1158" s="6"/>
-      <c r="C1158" s="6"/>
+      <c r="B1158" s="5"/>
+      <c r="C1158" s="5"/>
     </row>
     <row r="1159" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1159" s="6"/>
-      <c r="C1159" s="6"/>
+      <c r="B1159" s="5"/>
+      <c r="C1159" s="5"/>
     </row>
     <row r="1160" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1160" s="6"/>
-      <c r="C1160" s="6"/>
+      <c r="B1160" s="5"/>
+      <c r="C1160" s="5"/>
     </row>
     <row r="1161" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1161" s="6"/>
-      <c r="C1161" s="6"/>
+      <c r="B1161" s="5"/>
+      <c r="C1161" s="5"/>
     </row>
     <row r="1162" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1162" s="1"/>
@@ -9076,24 +9211,24 @@
       <c r="B1163" s="1"/>
     </row>
     <row r="1164" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1164" s="6"/>
-      <c r="C1164" s="6"/>
+      <c r="B1164" s="5"/>
+      <c r="C1164" s="5"/>
     </row>
     <row r="1165" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1165" s="6"/>
-      <c r="C1165" s="6"/>
+      <c r="B1165" s="5"/>
+      <c r="C1165" s="5"/>
     </row>
     <row r="1166" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1166" s="6"/>
-      <c r="C1166" s="6"/>
+      <c r="B1166" s="5"/>
+      <c r="C1166" s="5"/>
     </row>
     <row r="1167" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1167" s="6"/>
-      <c r="C1167" s="6"/>
+      <c r="B1167" s="5"/>
+      <c r="C1167" s="5"/>
     </row>
     <row r="1168" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1168" s="6"/>
-      <c r="C1168" s="6"/>
+      <c r="B1168" s="5"/>
+      <c r="C1168" s="5"/>
     </row>
     <row r="1169" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1169" s="1"/>
@@ -9102,24 +9237,24 @@
       <c r="B1170" s="1"/>
     </row>
     <row r="1171" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1171" s="6"/>
-      <c r="C1171" s="6"/>
+      <c r="B1171" s="5"/>
+      <c r="C1171" s="5"/>
     </row>
     <row r="1172" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1172" s="6"/>
-      <c r="C1172" s="6"/>
+      <c r="B1172" s="5"/>
+      <c r="C1172" s="5"/>
     </row>
     <row r="1173" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1173" s="6"/>
-      <c r="C1173" s="6"/>
+      <c r="B1173" s="5"/>
+      <c r="C1173" s="5"/>
     </row>
     <row r="1174" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1174" s="6"/>
-      <c r="C1174" s="6"/>
+      <c r="B1174" s="5"/>
+      <c r="C1174" s="5"/>
     </row>
     <row r="1175" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1175" s="6"/>
-      <c r="C1175" s="6"/>
+      <c r="B1175" s="5"/>
+      <c r="C1175" s="5"/>
     </row>
     <row r="1176" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1176" s="1"/>
@@ -9128,24 +9263,24 @@
       <c r="B1177" s="1"/>
     </row>
     <row r="1178" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1178" s="6"/>
-      <c r="C1178" s="6"/>
+      <c r="B1178" s="5"/>
+      <c r="C1178" s="5"/>
     </row>
     <row r="1179" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1179" s="6"/>
-      <c r="C1179" s="6"/>
+      <c r="B1179" s="5"/>
+      <c r="C1179" s="5"/>
     </row>
     <row r="1180" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1180" s="6"/>
-      <c r="C1180" s="6"/>
+      <c r="B1180" s="5"/>
+      <c r="C1180" s="5"/>
     </row>
     <row r="1181" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1181" s="6"/>
-      <c r="C1181" s="6"/>
+      <c r="B1181" s="5"/>
+      <c r="C1181" s="5"/>
     </row>
     <row r="1182" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1182" s="6"/>
-      <c r="C1182" s="6"/>
+      <c r="B1182" s="5"/>
+      <c r="C1182" s="5"/>
     </row>
     <row r="1183" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1183" s="1"/>
@@ -9154,24 +9289,24 @@
       <c r="B1184" s="1"/>
     </row>
     <row r="1185" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1185" s="6"/>
-      <c r="C1185" s="6"/>
+      <c r="B1185" s="5"/>
+      <c r="C1185" s="5"/>
     </row>
     <row r="1186" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1186" s="6"/>
-      <c r="C1186" s="6"/>
+      <c r="B1186" s="5"/>
+      <c r="C1186" s="5"/>
     </row>
     <row r="1187" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1187" s="6"/>
-      <c r="C1187" s="6"/>
+      <c r="B1187" s="5"/>
+      <c r="C1187" s="5"/>
     </row>
     <row r="1188" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1188" s="6"/>
-      <c r="C1188" s="6"/>
+      <c r="B1188" s="5"/>
+      <c r="C1188" s="5"/>
     </row>
     <row r="1189" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1189" s="6"/>
-      <c r="C1189" s="6"/>
+      <c r="B1189" s="5"/>
+      <c r="C1189" s="5"/>
     </row>
     <row r="1190" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1190" s="1"/>
@@ -9180,20 +9315,20 @@
       <c r="B1191" s="1"/>
     </row>
     <row r="1192" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1192" s="6"/>
-      <c r="C1192" s="6"/>
+      <c r="B1192" s="5"/>
+      <c r="C1192" s="5"/>
     </row>
     <row r="1193" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1193" s="6"/>
-      <c r="C1193" s="6"/>
+      <c r="B1193" s="5"/>
+      <c r="C1193" s="5"/>
     </row>
     <row r="1194" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1194" s="6"/>
-      <c r="C1194" s="6"/>
+      <c r="B1194" s="5"/>
+      <c r="C1194" s="5"/>
     </row>
     <row r="1195" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1195" s="6"/>
-      <c r="C1195" s="6"/>
+      <c r="B1195" s="5"/>
+      <c r="C1195" s="5"/>
     </row>
     <row r="1196" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1196" s="1"/>
@@ -9205,24 +9340,24 @@
       <c r="B1198" s="1"/>
     </row>
     <row r="1199" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1199" s="6"/>
-      <c r="C1199" s="6"/>
+      <c r="B1199" s="5"/>
+      <c r="C1199" s="5"/>
     </row>
     <row r="1200" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1200" s="6"/>
-      <c r="C1200" s="6"/>
+      <c r="B1200" s="5"/>
+      <c r="C1200" s="5"/>
     </row>
     <row r="1201" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1201" s="6"/>
-      <c r="C1201" s="6"/>
+      <c r="B1201" s="5"/>
+      <c r="C1201" s="5"/>
     </row>
     <row r="1202" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1202" s="6"/>
-      <c r="C1202" s="6"/>
+      <c r="B1202" s="5"/>
+      <c r="C1202" s="5"/>
     </row>
     <row r="1203" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1203" s="6"/>
-      <c r="C1203" s="6"/>
+      <c r="B1203" s="5"/>
+      <c r="C1203" s="5"/>
     </row>
     <row r="1204" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1204" s="1"/>
@@ -9231,24 +9366,24 @@
       <c r="B1205" s="1"/>
     </row>
     <row r="1206" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1206" s="6"/>
-      <c r="C1206" s="6"/>
+      <c r="B1206" s="5"/>
+      <c r="C1206" s="5"/>
     </row>
     <row r="1207" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1207" s="6"/>
-      <c r="C1207" s="6"/>
+      <c r="B1207" s="5"/>
+      <c r="C1207" s="5"/>
     </row>
     <row r="1208" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1208" s="6"/>
-      <c r="C1208" s="6"/>
+      <c r="B1208" s="5"/>
+      <c r="C1208" s="5"/>
     </row>
     <row r="1209" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1209" s="6"/>
-      <c r="C1209" s="6"/>
+      <c r="B1209" s="5"/>
+      <c r="C1209" s="5"/>
     </row>
     <row r="1210" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1210" s="6"/>
-      <c r="C1210" s="6"/>
+      <c r="B1210" s="5"/>
+      <c r="C1210" s="5"/>
     </row>
     <row r="1211" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1211" s="1"/>
@@ -9257,24 +9392,24 @@
       <c r="B1212" s="1"/>
     </row>
     <row r="1213" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1213" s="6"/>
-      <c r="C1213" s="6"/>
+      <c r="B1213" s="5"/>
+      <c r="C1213" s="5"/>
     </row>
     <row r="1214" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1214" s="6"/>
-      <c r="C1214" s="6"/>
+      <c r="B1214" s="5"/>
+      <c r="C1214" s="5"/>
     </row>
     <row r="1215" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1215" s="6"/>
-      <c r="C1215" s="6"/>
+      <c r="B1215" s="5"/>
+      <c r="C1215" s="5"/>
     </row>
     <row r="1216" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1216" s="6"/>
-      <c r="C1216" s="6"/>
+      <c r="B1216" s="5"/>
+      <c r="C1216" s="5"/>
     </row>
     <row r="1217" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1217" s="6"/>
-      <c r="C1217" s="6"/>
+      <c r="B1217" s="5"/>
+      <c r="C1217" s="5"/>
     </row>
     <row r="1218" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1218" s="1"/>
@@ -9283,24 +9418,24 @@
       <c r="B1219" s="1"/>
     </row>
     <row r="1220" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1220" s="6"/>
-      <c r="C1220" s="6"/>
+      <c r="B1220" s="5"/>
+      <c r="C1220" s="5"/>
     </row>
     <row r="1221" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1221" s="6"/>
-      <c r="C1221" s="6"/>
+      <c r="B1221" s="5"/>
+      <c r="C1221" s="5"/>
     </row>
     <row r="1222" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1222" s="6"/>
-      <c r="C1222" s="6"/>
+      <c r="B1222" s="5"/>
+      <c r="C1222" s="5"/>
     </row>
     <row r="1223" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1223" s="6"/>
-      <c r="C1223" s="6"/>
+      <c r="B1223" s="5"/>
+      <c r="C1223" s="5"/>
     </row>
     <row r="1224" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1224" s="6"/>
-      <c r="C1224" s="6"/>
+      <c r="B1224" s="5"/>
+      <c r="C1224" s="5"/>
     </row>
     <row r="1225" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1225" s="1"/>
@@ -9309,24 +9444,24 @@
       <c r="B1226" s="1"/>
     </row>
     <row r="1227" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1227" s="6"/>
-      <c r="C1227" s="6"/>
+      <c r="B1227" s="5"/>
+      <c r="C1227" s="5"/>
     </row>
     <row r="1228" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1228" s="6"/>
-      <c r="C1228" s="6"/>
+      <c r="B1228" s="5"/>
+      <c r="C1228" s="5"/>
     </row>
     <row r="1229" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1229" s="6"/>
-      <c r="C1229" s="6"/>
+      <c r="B1229" s="5"/>
+      <c r="C1229" s="5"/>
     </row>
     <row r="1230" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1230" s="6"/>
-      <c r="C1230" s="6"/>
+      <c r="B1230" s="5"/>
+      <c r="C1230" s="5"/>
     </row>
     <row r="1231" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1231" s="6"/>
-      <c r="C1231" s="6"/>
+      <c r="B1231" s="5"/>
+      <c r="C1231" s="5"/>
     </row>
     <row r="1232" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1232" s="1"/>
@@ -9335,24 +9470,24 @@
       <c r="B1233" s="1"/>
     </row>
     <row r="1234" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1234" s="6"/>
-      <c r="C1234" s="6"/>
+      <c r="B1234" s="5"/>
+      <c r="C1234" s="5"/>
     </row>
     <row r="1235" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1235" s="6"/>
-      <c r="C1235" s="6"/>
+      <c r="B1235" s="5"/>
+      <c r="C1235" s="5"/>
     </row>
     <row r="1236" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1236" s="6"/>
-      <c r="C1236" s="6"/>
+      <c r="B1236" s="5"/>
+      <c r="C1236" s="5"/>
     </row>
     <row r="1237" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1237" s="6"/>
-      <c r="C1237" s="6"/>
+      <c r="B1237" s="5"/>
+      <c r="C1237" s="5"/>
     </row>
     <row r="1238" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1238" s="6"/>
-      <c r="C1238" s="6"/>
+      <c r="B1238" s="5"/>
+      <c r="C1238" s="5"/>
     </row>
     <row r="1239" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1239" s="1"/>
@@ -9361,24 +9496,24 @@
       <c r="B1240" s="1"/>
     </row>
     <row r="1241" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1241" s="6"/>
-      <c r="C1241" s="6"/>
+      <c r="B1241" s="5"/>
+      <c r="C1241" s="5"/>
     </row>
     <row r="1242" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1242" s="6"/>
-      <c r="C1242" s="6"/>
+      <c r="B1242" s="5"/>
+      <c r="C1242" s="5"/>
     </row>
     <row r="1243" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1243" s="6"/>
-      <c r="C1243" s="6"/>
+      <c r="B1243" s="5"/>
+      <c r="C1243" s="5"/>
     </row>
     <row r="1244" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1244" s="6"/>
-      <c r="C1244" s="6"/>
+      <c r="B1244" s="5"/>
+      <c r="C1244" s="5"/>
     </row>
     <row r="1245" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1245" s="6"/>
-      <c r="C1245" s="6"/>
+      <c r="B1245" s="5"/>
+      <c r="C1245" s="5"/>
     </row>
     <row r="1246" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1246" s="1"/>
@@ -9387,24 +9522,24 @@
       <c r="B1247" s="1"/>
     </row>
     <row r="1248" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1248" s="6"/>
-      <c r="C1248" s="6"/>
+      <c r="B1248" s="5"/>
+      <c r="C1248" s="5"/>
     </row>
     <row r="1249" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1249" s="6"/>
-      <c r="C1249" s="6"/>
+      <c r="B1249" s="5"/>
+      <c r="C1249" s="5"/>
     </row>
     <row r="1250" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1250" s="6"/>
-      <c r="C1250" s="6"/>
+      <c r="B1250" s="5"/>
+      <c r="C1250" s="5"/>
     </row>
     <row r="1251" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1251" s="6"/>
-      <c r="C1251" s="6"/>
+      <c r="B1251" s="5"/>
+      <c r="C1251" s="5"/>
     </row>
     <row r="1252" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1252" s="6"/>
-      <c r="C1252" s="6"/>
+      <c r="B1252" s="5"/>
+      <c r="C1252" s="5"/>
     </row>
     <row r="1253" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1253" s="1"/>
@@ -9413,23 +9548,23 @@
       <c r="B1254" s="1"/>
     </row>
     <row r="1255" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1255" s="6"/>
-      <c r="C1255" s="6"/>
+      <c r="B1255" s="5"/>
+      <c r="C1255" s="5"/>
     </row>
     <row r="1256" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1256" s="1"/>
     </row>
     <row r="1257" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1257" s="6"/>
-      <c r="C1257" s="6"/>
+      <c r="B1257" s="5"/>
+      <c r="C1257" s="5"/>
     </row>
     <row r="1258" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1258" s="6"/>
-      <c r="C1258" s="6"/>
+      <c r="B1258" s="5"/>
+      <c r="C1258" s="5"/>
     </row>
     <row r="1259" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1259" s="6"/>
-      <c r="C1259" s="6"/>
+      <c r="B1259" s="5"/>
+      <c r="C1259" s="5"/>
     </row>
     <row r="1260" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1260" s="1"/>
@@ -9438,24 +9573,24 @@
       <c r="B1261" s="1"/>
     </row>
     <row r="1262" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1262" s="6"/>
-      <c r="C1262" s="6"/>
+      <c r="B1262" s="5"/>
+      <c r="C1262" s="5"/>
     </row>
     <row r="1263" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1263" s="6"/>
-      <c r="C1263" s="6"/>
+      <c r="B1263" s="5"/>
+      <c r="C1263" s="5"/>
     </row>
     <row r="1264" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1264" s="6"/>
-      <c r="C1264" s="6"/>
+      <c r="B1264" s="5"/>
+      <c r="C1264" s="5"/>
     </row>
     <row r="1265" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1265" s="6"/>
-      <c r="C1265" s="6"/>
+      <c r="B1265" s="5"/>
+      <c r="C1265" s="5"/>
     </row>
     <row r="1266" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1266" s="6"/>
-      <c r="C1266" s="6"/>
+      <c r="B1266" s="5"/>
+      <c r="C1266" s="5"/>
     </row>
     <row r="1267" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1267" s="1"/>
@@ -9464,24 +9599,24 @@
       <c r="B1268" s="1"/>
     </row>
     <row r="1269" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1269" s="6"/>
-      <c r="C1269" s="6"/>
+      <c r="B1269" s="5"/>
+      <c r="C1269" s="5"/>
     </row>
     <row r="1270" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1270" s="6"/>
-      <c r="C1270" s="6"/>
+      <c r="B1270" s="5"/>
+      <c r="C1270" s="5"/>
     </row>
     <row r="1271" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1271" s="6"/>
-      <c r="C1271" s="6"/>
+      <c r="B1271" s="5"/>
+      <c r="C1271" s="5"/>
     </row>
     <row r="1272" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1272" s="6"/>
-      <c r="C1272" s="6"/>
+      <c r="B1272" s="5"/>
+      <c r="C1272" s="5"/>
     </row>
     <row r="1273" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1273" s="6"/>
-      <c r="C1273" s="6"/>
+      <c r="B1273" s="5"/>
+      <c r="C1273" s="5"/>
     </row>
     <row r="1274" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1274" s="1"/>
@@ -9490,24 +9625,24 @@
       <c r="B1275" s="1"/>
     </row>
     <row r="1276" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1276" s="6"/>
-      <c r="C1276" s="6"/>
+      <c r="B1276" s="5"/>
+      <c r="C1276" s="5"/>
     </row>
     <row r="1277" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1277" s="6"/>
-      <c r="C1277" s="6"/>
+      <c r="B1277" s="5"/>
+      <c r="C1277" s="5"/>
     </row>
     <row r="1278" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1278" s="6"/>
-      <c r="C1278" s="6"/>
+      <c r="B1278" s="5"/>
+      <c r="C1278" s="5"/>
     </row>
     <row r="1279" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1279" s="6"/>
-      <c r="C1279" s="6"/>
+      <c r="B1279" s="5"/>
+      <c r="C1279" s="5"/>
     </row>
     <row r="1280" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1280" s="6"/>
-      <c r="C1280" s="6"/>
+      <c r="B1280" s="5"/>
+      <c r="C1280" s="5"/>
     </row>
     <row r="1281" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1281" s="1"/>
@@ -9516,24 +9651,24 @@
       <c r="B1282" s="1"/>
     </row>
     <row r="1283" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1283" s="6"/>
-      <c r="C1283" s="6"/>
+      <c r="B1283" s="5"/>
+      <c r="C1283" s="5"/>
     </row>
     <row r="1284" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1284" s="6"/>
-      <c r="C1284" s="6"/>
+      <c r="B1284" s="5"/>
+      <c r="C1284" s="5"/>
     </row>
     <row r="1285" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1285" s="6"/>
-      <c r="C1285" s="6"/>
+      <c r="B1285" s="5"/>
+      <c r="C1285" s="5"/>
     </row>
     <row r="1286" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1286" s="6"/>
-      <c r="C1286" s="6"/>
+      <c r="B1286" s="5"/>
+      <c r="C1286" s="5"/>
     </row>
     <row r="1287" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1287" s="6"/>
-      <c r="C1287" s="6"/>
+      <c r="B1287" s="5"/>
+      <c r="C1287" s="5"/>
     </row>
     <row r="1288" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1288" s="1"/>
@@ -9542,24 +9677,24 @@
       <c r="B1289" s="1"/>
     </row>
     <row r="1290" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1290" s="6"/>
-      <c r="C1290" s="6"/>
+      <c r="B1290" s="5"/>
+      <c r="C1290" s="5"/>
     </row>
     <row r="1291" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1291" s="6"/>
-      <c r="C1291" s="6"/>
+      <c r="B1291" s="5"/>
+      <c r="C1291" s="5"/>
     </row>
     <row r="1292" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1292" s="6"/>
-      <c r="C1292" s="6"/>
+      <c r="B1292" s="5"/>
+      <c r="C1292" s="5"/>
     </row>
     <row r="1293" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1293" s="6"/>
-      <c r="C1293" s="6"/>
+      <c r="B1293" s="5"/>
+      <c r="C1293" s="5"/>
     </row>
     <row r="1294" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1294" s="6"/>
-      <c r="C1294" s="6"/>
+      <c r="B1294" s="5"/>
+      <c r="C1294" s="5"/>
     </row>
     <row r="1295" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1295" s="1"/>
@@ -9568,24 +9703,24 @@
       <c r="B1296" s="1"/>
     </row>
     <row r="1297" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1297" s="6"/>
-      <c r="C1297" s="6"/>
+      <c r="B1297" s="5"/>
+      <c r="C1297" s="5"/>
     </row>
     <row r="1298" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1298" s="6"/>
-      <c r="C1298" s="6"/>
+      <c r="B1298" s="5"/>
+      <c r="C1298" s="5"/>
     </row>
     <row r="1299" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1299" s="6"/>
-      <c r="C1299" s="6"/>
+      <c r="B1299" s="5"/>
+      <c r="C1299" s="5"/>
     </row>
     <row r="1300" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1300" s="6"/>
-      <c r="C1300" s="6"/>
+      <c r="B1300" s="5"/>
+      <c r="C1300" s="5"/>
     </row>
     <row r="1301" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1301" s="6"/>
-      <c r="C1301" s="6"/>
+      <c r="B1301" s="5"/>
+      <c r="C1301" s="5"/>
     </row>
     <row r="1302" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1302" s="1"/>
@@ -9594,24 +9729,24 @@
       <c r="B1303" s="1"/>
     </row>
     <row r="1304" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1304" s="6"/>
-      <c r="C1304" s="6"/>
+      <c r="B1304" s="5"/>
+      <c r="C1304" s="5"/>
     </row>
     <row r="1305" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1305" s="6"/>
-      <c r="C1305" s="6"/>
+      <c r="B1305" s="5"/>
+      <c r="C1305" s="5"/>
     </row>
     <row r="1306" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1306" s="6"/>
-      <c r="C1306" s="6"/>
+      <c r="B1306" s="5"/>
+      <c r="C1306" s="5"/>
     </row>
     <row r="1307" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1307" s="6"/>
-      <c r="C1307" s="6"/>
+      <c r="B1307" s="5"/>
+      <c r="C1307" s="5"/>
     </row>
     <row r="1308" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1308" s="6"/>
-      <c r="C1308" s="6"/>
+      <c r="B1308" s="5"/>
+      <c r="C1308" s="5"/>
     </row>
     <row r="1309" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1309" s="1"/>
@@ -9620,24 +9755,24 @@
       <c r="B1310" s="1"/>
     </row>
     <row r="1311" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1311" s="6"/>
-      <c r="C1311" s="6"/>
+      <c r="B1311" s="5"/>
+      <c r="C1311" s="5"/>
     </row>
     <row r="1312" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1312" s="6"/>
-      <c r="C1312" s="6"/>
+      <c r="B1312" s="5"/>
+      <c r="C1312" s="5"/>
     </row>
     <row r="1313" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1313" s="6"/>
-      <c r="C1313" s="6"/>
+      <c r="B1313" s="5"/>
+      <c r="C1313" s="5"/>
     </row>
     <row r="1314" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1314" s="6"/>
-      <c r="C1314" s="6"/>
+      <c r="B1314" s="5"/>
+      <c r="C1314" s="5"/>
     </row>
     <row r="1315" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1315" s="6"/>
-      <c r="C1315" s="6"/>
+      <c r="B1315" s="5"/>
+      <c r="C1315" s="5"/>
     </row>
     <row r="1316" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1316" s="1"/>
@@ -9646,23 +9781,23 @@
       <c r="B1317" s="1"/>
     </row>
     <row r="1318" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1318" s="6"/>
-      <c r="C1318" s="6"/>
+      <c r="B1318" s="5"/>
+      <c r="C1318" s="5"/>
     </row>
     <row r="1319" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1319" s="6"/>
-      <c r="C1319" s="6"/>
+      <c r="B1319" s="5"/>
+      <c r="C1319" s="5"/>
     </row>
     <row r="1320" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1320" s="1"/>
     </row>
     <row r="1321" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1321" s="6"/>
-      <c r="C1321" s="6"/>
+      <c r="B1321" s="5"/>
+      <c r="C1321" s="5"/>
     </row>
     <row r="1322" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1322" s="6"/>
-      <c r="C1322" s="6"/>
+      <c r="B1322" s="5"/>
+      <c r="C1322" s="5"/>
     </row>
     <row r="1323" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1323" s="1"/>
@@ -9671,24 +9806,24 @@
       <c r="B1324" s="1"/>
     </row>
     <row r="1325" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1325" s="6"/>
-      <c r="C1325" s="6"/>
+      <c r="B1325" s="5"/>
+      <c r="C1325" s="5"/>
     </row>
     <row r="1326" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1326" s="6"/>
-      <c r="C1326" s="6"/>
+      <c r="B1326" s="5"/>
+      <c r="C1326" s="5"/>
     </row>
     <row r="1327" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1327" s="6"/>
-      <c r="C1327" s="6"/>
+      <c r="B1327" s="5"/>
+      <c r="C1327" s="5"/>
     </row>
     <row r="1328" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1328" s="6"/>
-      <c r="C1328" s="6"/>
+      <c r="B1328" s="5"/>
+      <c r="C1328" s="5"/>
     </row>
     <row r="1329" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1329" s="6"/>
-      <c r="C1329" s="6"/>
+      <c r="B1329" s="5"/>
+      <c r="C1329" s="5"/>
     </row>
     <row r="1330" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1330" s="1"/>
@@ -9697,24 +9832,24 @@
       <c r="B1331" s="1"/>
     </row>
     <row r="1332" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1332" s="6"/>
-      <c r="C1332" s="6"/>
+      <c r="B1332" s="5"/>
+      <c r="C1332" s="5"/>
     </row>
     <row r="1333" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1333" s="6"/>
-      <c r="C1333" s="6"/>
+      <c r="B1333" s="5"/>
+      <c r="C1333" s="5"/>
     </row>
     <row r="1334" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1334" s="6"/>
-      <c r="C1334" s="6"/>
+      <c r="B1334" s="5"/>
+      <c r="C1334" s="5"/>
     </row>
     <row r="1335" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1335" s="6"/>
-      <c r="C1335" s="6"/>
+      <c r="B1335" s="5"/>
+      <c r="C1335" s="5"/>
     </row>
     <row r="1336" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1336" s="6"/>
-      <c r="C1336" s="6"/>
+      <c r="B1336" s="5"/>
+      <c r="C1336" s="5"/>
     </row>
     <row r="1337" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1337" s="1"/>
@@ -9723,24 +9858,24 @@
       <c r="B1338" s="1"/>
     </row>
     <row r="1339" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1339" s="6"/>
-      <c r="C1339" s="6"/>
+      <c r="B1339" s="5"/>
+      <c r="C1339" s="5"/>
     </row>
     <row r="1340" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1340" s="6"/>
-      <c r="C1340" s="6"/>
+      <c r="B1340" s="5"/>
+      <c r="C1340" s="5"/>
     </row>
     <row r="1341" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1341" s="6"/>
-      <c r="C1341" s="6"/>
+      <c r="B1341" s="5"/>
+      <c r="C1341" s="5"/>
     </row>
     <row r="1342" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1342" s="6"/>
-      <c r="C1342" s="6"/>
+      <c r="B1342" s="5"/>
+      <c r="C1342" s="5"/>
     </row>
     <row r="1343" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1343" s="6"/>
-      <c r="C1343" s="6"/>
+      <c r="B1343" s="5"/>
+      <c r="C1343" s="5"/>
     </row>
     <row r="1344" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1344" s="1"/>
@@ -9749,24 +9884,24 @@
       <c r="B1345" s="1"/>
     </row>
     <row r="1346" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1346" s="6"/>
-      <c r="C1346" s="6"/>
+      <c r="B1346" s="5"/>
+      <c r="C1346" s="5"/>
     </row>
     <row r="1347" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1347" s="6"/>
-      <c r="C1347" s="6"/>
+      <c r="B1347" s="5"/>
+      <c r="C1347" s="5"/>
     </row>
     <row r="1348" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1348" s="6"/>
-      <c r="C1348" s="6"/>
+      <c r="B1348" s="5"/>
+      <c r="C1348" s="5"/>
     </row>
     <row r="1349" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1349" s="6"/>
-      <c r="C1349" s="6"/>
+      <c r="B1349" s="5"/>
+      <c r="C1349" s="5"/>
     </row>
     <row r="1350" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1350" s="6"/>
-      <c r="C1350" s="6"/>
+      <c r="B1350" s="5"/>
+      <c r="C1350" s="5"/>
     </row>
     <row r="1351" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1351" s="1"/>
@@ -9775,24 +9910,24 @@
       <c r="B1352" s="1"/>
     </row>
     <row r="1353" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1353" s="6"/>
-      <c r="C1353" s="6"/>
+      <c r="B1353" s="5"/>
+      <c r="C1353" s="5"/>
     </row>
     <row r="1354" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1354" s="6"/>
-      <c r="C1354" s="6"/>
+      <c r="B1354" s="5"/>
+      <c r="C1354" s="5"/>
     </row>
     <row r="1355" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1355" s="6"/>
-      <c r="C1355" s="6"/>
+      <c r="B1355" s="5"/>
+      <c r="C1355" s="5"/>
     </row>
     <row r="1356" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1356" s="6"/>
-      <c r="C1356" s="6"/>
+      <c r="B1356" s="5"/>
+      <c r="C1356" s="5"/>
     </row>
     <row r="1357" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1357" s="6"/>
-      <c r="C1357" s="6"/>
+      <c r="B1357" s="5"/>
+      <c r="C1357" s="5"/>
     </row>
     <row r="1358" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1358" s="1"/>
@@ -9801,24 +9936,24 @@
       <c r="B1359" s="1"/>
     </row>
     <row r="1360" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1360" s="6"/>
-      <c r="C1360" s="6"/>
+      <c r="B1360" s="5"/>
+      <c r="C1360" s="5"/>
     </row>
     <row r="1361" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1361" s="6"/>
-      <c r="C1361" s="6"/>
+      <c r="B1361" s="5"/>
+      <c r="C1361" s="5"/>
     </row>
     <row r="1362" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1362" s="6"/>
-      <c r="C1362" s="6"/>
+      <c r="B1362" s="5"/>
+      <c r="C1362" s="5"/>
     </row>
     <row r="1363" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1363" s="6"/>
-      <c r="C1363" s="6"/>
+      <c r="B1363" s="5"/>
+      <c r="C1363" s="5"/>
     </row>
     <row r="1364" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1364" s="6"/>
-      <c r="C1364" s="6"/>
+      <c r="B1364" s="5"/>
+      <c r="C1364" s="5"/>
     </row>
     <row r="1365" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1365" s="1"/>
@@ -9827,24 +9962,24 @@
       <c r="B1366" s="1"/>
     </row>
     <row r="1367" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1367" s="6"/>
-      <c r="C1367" s="6"/>
+      <c r="B1367" s="5"/>
+      <c r="C1367" s="5"/>
     </row>
     <row r="1368" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1368" s="6"/>
-      <c r="C1368" s="6"/>
+      <c r="B1368" s="5"/>
+      <c r="C1368" s="5"/>
     </row>
     <row r="1369" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1369" s="6"/>
-      <c r="C1369" s="6"/>
+      <c r="B1369" s="5"/>
+      <c r="C1369" s="5"/>
     </row>
     <row r="1370" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1370" s="6"/>
-      <c r="C1370" s="6"/>
+      <c r="B1370" s="5"/>
+      <c r="C1370" s="5"/>
     </row>
     <row r="1371" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1371" s="6"/>
-      <c r="C1371" s="6"/>
+      <c r="B1371" s="5"/>
+      <c r="C1371" s="5"/>
     </row>
     <row r="1372" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1372" s="1"/>
@@ -9853,24 +9988,24 @@
       <c r="B1373" s="1"/>
     </row>
     <row r="1374" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1374" s="6"/>
-      <c r="C1374" s="6"/>
+      <c r="B1374" s="5"/>
+      <c r="C1374" s="5"/>
     </row>
     <row r="1375" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1375" s="6"/>
-      <c r="C1375" s="6"/>
+      <c r="B1375" s="5"/>
+      <c r="C1375" s="5"/>
     </row>
     <row r="1376" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1376" s="6"/>
-      <c r="C1376" s="6"/>
+      <c r="B1376" s="5"/>
+      <c r="C1376" s="5"/>
     </row>
     <row r="1377" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1377" s="6"/>
-      <c r="C1377" s="6"/>
+      <c r="B1377" s="5"/>
+      <c r="C1377" s="5"/>
     </row>
     <row r="1378" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1378" s="6"/>
-      <c r="C1378" s="6"/>
+      <c r="B1378" s="5"/>
+      <c r="C1378" s="5"/>
     </row>
     <row r="1379" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1379" s="1"/>
@@ -9879,24 +10014,24 @@
       <c r="B1380" s="1"/>
     </row>
     <row r="1381" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1381" s="6"/>
-      <c r="C1381" s="6"/>
+      <c r="B1381" s="5"/>
+      <c r="C1381" s="5"/>
     </row>
     <row r="1382" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1382" s="6"/>
-      <c r="C1382" s="6"/>
+      <c r="B1382" s="5"/>
+      <c r="C1382" s="5"/>
     </row>
     <row r="1383" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1383" s="6"/>
-      <c r="C1383" s="6"/>
+      <c r="B1383" s="5"/>
+      <c r="C1383" s="5"/>
     </row>
     <row r="1384" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1384" s="6"/>
-      <c r="C1384" s="6"/>
+      <c r="B1384" s="5"/>
+      <c r="C1384" s="5"/>
     </row>
     <row r="1385" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1385" s="6"/>
-      <c r="C1385" s="6"/>
+      <c r="B1385" s="5"/>
+      <c r="C1385" s="5"/>
     </row>
     <row r="1386" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1386" s="1"/>
@@ -9905,24 +10040,24 @@
       <c r="B1387" s="1"/>
     </row>
     <row r="1388" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1388" s="6"/>
-      <c r="C1388" s="6"/>
+      <c r="B1388" s="5"/>
+      <c r="C1388" s="5"/>
     </row>
     <row r="1389" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1389" s="6"/>
-      <c r="C1389" s="6"/>
+      <c r="B1389" s="5"/>
+      <c r="C1389" s="5"/>
     </row>
     <row r="1390" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1390" s="6"/>
-      <c r="C1390" s="6"/>
+      <c r="B1390" s="5"/>
+      <c r="C1390" s="5"/>
     </row>
     <row r="1391" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1391" s="6"/>
-      <c r="C1391" s="6"/>
+      <c r="B1391" s="5"/>
+      <c r="C1391" s="5"/>
     </row>
     <row r="1392" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1392" s="6"/>
-      <c r="C1392" s="6"/>
+      <c r="B1392" s="5"/>
+      <c r="C1392" s="5"/>
     </row>
     <row r="1393" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1393" s="1"/>
@@ -9931,24 +10066,24 @@
       <c r="B1394" s="1"/>
     </row>
     <row r="1395" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1395" s="6"/>
-      <c r="C1395" s="6"/>
+      <c r="B1395" s="5"/>
+      <c r="C1395" s="5"/>
     </row>
     <row r="1396" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1396" s="6"/>
-      <c r="C1396" s="6"/>
+      <c r="B1396" s="5"/>
+      <c r="C1396" s="5"/>
     </row>
     <row r="1397" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1397" s="6"/>
-      <c r="C1397" s="6"/>
+      <c r="B1397" s="5"/>
+      <c r="C1397" s="5"/>
     </row>
     <row r="1398" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1398" s="6"/>
-      <c r="C1398" s="6"/>
+      <c r="B1398" s="5"/>
+      <c r="C1398" s="5"/>
     </row>
     <row r="1399" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1399" s="6"/>
-      <c r="C1399" s="6"/>
+      <c r="B1399" s="5"/>
+      <c r="C1399" s="5"/>
     </row>
     <row r="1400" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1400" s="1"/>
@@ -9957,24 +10092,24 @@
       <c r="B1401" s="1"/>
     </row>
     <row r="1402" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1402" s="6"/>
-      <c r="C1402" s="6"/>
+      <c r="B1402" s="5"/>
+      <c r="C1402" s="5"/>
     </row>
     <row r="1403" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1403" s="6"/>
-      <c r="C1403" s="6"/>
+      <c r="B1403" s="5"/>
+      <c r="C1403" s="5"/>
     </row>
     <row r="1404" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1404" s="6"/>
-      <c r="C1404" s="6"/>
+      <c r="B1404" s="5"/>
+      <c r="C1404" s="5"/>
     </row>
     <row r="1405" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1405" s="6"/>
-      <c r="C1405" s="6"/>
+      <c r="B1405" s="5"/>
+      <c r="C1405" s="5"/>
     </row>
     <row r="1406" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1406" s="6"/>
-      <c r="C1406" s="6"/>
+      <c r="B1406" s="5"/>
+      <c r="C1406" s="5"/>
     </row>
     <row r="1407" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1407" s="1"/>
@@ -9989,16 +10124,16 @@
       <c r="B1410" s="1"/>
     </row>
     <row r="1411" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1411" s="6"/>
-      <c r="C1411" s="6"/>
+      <c r="B1411" s="5"/>
+      <c r="C1411" s="5"/>
     </row>
     <row r="1412" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1412" s="6"/>
-      <c r="C1412" s="6"/>
+      <c r="B1412" s="5"/>
+      <c r="C1412" s="5"/>
     </row>
     <row r="1413" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1413" s="6"/>
-      <c r="C1413" s="6"/>
+      <c r="B1413" s="5"/>
+      <c r="C1413" s="5"/>
     </row>
     <row r="1414" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1414" s="1"/>
@@ -10007,24 +10142,24 @@
       <c r="B1415" s="1"/>
     </row>
     <row r="1416" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1416" s="6"/>
-      <c r="C1416" s="6"/>
+      <c r="B1416" s="5"/>
+      <c r="C1416" s="5"/>
     </row>
     <row r="1417" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1417" s="6"/>
-      <c r="C1417" s="6"/>
+      <c r="B1417" s="5"/>
+      <c r="C1417" s="5"/>
     </row>
     <row r="1418" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1418" s="6"/>
-      <c r="C1418" s="6"/>
+      <c r="B1418" s="5"/>
+      <c r="C1418" s="5"/>
     </row>
     <row r="1419" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1419" s="6"/>
-      <c r="C1419" s="6"/>
+      <c r="B1419" s="5"/>
+      <c r="C1419" s="5"/>
     </row>
     <row r="1420" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1420" s="6"/>
-      <c r="C1420" s="6"/>
+      <c r="B1420" s="5"/>
+      <c r="C1420" s="5"/>
     </row>
     <row r="1421" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1421" s="1"/>
@@ -10033,24 +10168,24 @@
       <c r="B1422" s="1"/>
     </row>
     <row r="1423" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1423" s="6"/>
-      <c r="C1423" s="6"/>
+      <c r="B1423" s="5"/>
+      <c r="C1423" s="5"/>
     </row>
     <row r="1424" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1424" s="6"/>
-      <c r="C1424" s="6"/>
+      <c r="B1424" s="5"/>
+      <c r="C1424" s="5"/>
     </row>
     <row r="1425" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1425" s="6"/>
-      <c r="C1425" s="6"/>
+      <c r="B1425" s="5"/>
+      <c r="C1425" s="5"/>
     </row>
     <row r="1426" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1426" s="6"/>
-      <c r="C1426" s="6"/>
+      <c r="B1426" s="5"/>
+      <c r="C1426" s="5"/>
     </row>
     <row r="1427" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1427" s="6"/>
-      <c r="C1427" s="6"/>
+      <c r="B1427" s="5"/>
+      <c r="C1427" s="5"/>
     </row>
     <row r="1428" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1428" s="1"/>
@@ -10059,23 +10194,23 @@
       <c r="B1429" s="1"/>
     </row>
     <row r="1430" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1430" s="6"/>
-      <c r="C1430" s="6"/>
+      <c r="B1430" s="5"/>
+      <c r="C1430" s="5"/>
     </row>
     <row r="1431" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1431" s="6"/>
-      <c r="C1431" s="6"/>
+      <c r="B1431" s="5"/>
+      <c r="C1431" s="5"/>
     </row>
     <row r="1432" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1432" s="1"/>
     </row>
     <row r="1433" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1433" s="6"/>
-      <c r="C1433" s="6"/>
+      <c r="B1433" s="5"/>
+      <c r="C1433" s="5"/>
     </row>
     <row r="1434" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1434" s="6"/>
-      <c r="C1434" s="6"/>
+      <c r="B1434" s="5"/>
+      <c r="C1434" s="5"/>
     </row>
     <row r="1435" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1435" s="1"/>
@@ -10084,23 +10219,23 @@
       <c r="B1436" s="1"/>
     </row>
     <row r="1437" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1437" s="6"/>
-      <c r="C1437" s="6"/>
+      <c r="B1437" s="5"/>
+      <c r="C1437" s="5"/>
     </row>
     <row r="1438" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1438" s="6"/>
-      <c r="C1438" s="6"/>
+      <c r="B1438" s="5"/>
+      <c r="C1438" s="5"/>
     </row>
     <row r="1439" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1439" s="6"/>
-      <c r="C1439" s="6"/>
+      <c r="B1439" s="5"/>
+      <c r="C1439" s="5"/>
     </row>
     <row r="1440" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1440" s="1"/>
     </row>
     <row r="1441" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1441" s="6"/>
-      <c r="C1441" s="6"/>
+      <c r="B1441" s="5"/>
+      <c r="C1441" s="5"/>
     </row>
     <row r="1442" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1442" s="1"/>
@@ -10109,24 +10244,24 @@
       <c r="B1443" s="1"/>
     </row>
     <row r="1444" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1444" s="6"/>
-      <c r="C1444" s="6"/>
+      <c r="B1444" s="5"/>
+      <c r="C1444" s="5"/>
     </row>
     <row r="1445" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1445" s="6"/>
-      <c r="C1445" s="6"/>
+      <c r="B1445" s="5"/>
+      <c r="C1445" s="5"/>
     </row>
     <row r="1446" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1446" s="6"/>
-      <c r="C1446" s="6"/>
+      <c r="B1446" s="5"/>
+      <c r="C1446" s="5"/>
     </row>
     <row r="1447" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1447" s="6"/>
-      <c r="C1447" s="6"/>
+      <c r="B1447" s="5"/>
+      <c r="C1447" s="5"/>
     </row>
     <row r="1448" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1448" s="6"/>
-      <c r="C1448" s="6"/>
+      <c r="B1448" s="5"/>
+      <c r="C1448" s="5"/>
     </row>
     <row r="1449" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1449" s="1"/>
@@ -10135,24 +10270,24 @@
       <c r="B1450" s="1"/>
     </row>
     <row r="1451" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1451" s="6"/>
-      <c r="C1451" s="6"/>
+      <c r="B1451" s="5"/>
+      <c r="C1451" s="5"/>
     </row>
     <row r="1452" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1452" s="6"/>
-      <c r="C1452" s="6"/>
+      <c r="B1452" s="5"/>
+      <c r="C1452" s="5"/>
     </row>
     <row r="1453" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1453" s="6"/>
-      <c r="C1453" s="6"/>
+      <c r="B1453" s="5"/>
+      <c r="C1453" s="5"/>
     </row>
     <row r="1454" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1454" s="6"/>
-      <c r="C1454" s="6"/>
+      <c r="B1454" s="5"/>
+      <c r="C1454" s="5"/>
     </row>
     <row r="1455" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1455" s="6"/>
-      <c r="C1455" s="6"/>
+      <c r="B1455" s="5"/>
+      <c r="C1455" s="5"/>
     </row>
     <row r="1456" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1456" s="1"/>
@@ -10164,20 +10299,20 @@
       <c r="B1458" s="1"/>
     </row>
     <row r="1459" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1459" s="6"/>
-      <c r="C1459" s="6"/>
+      <c r="B1459" s="5"/>
+      <c r="C1459" s="5"/>
     </row>
     <row r="1460" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1460" s="6"/>
-      <c r="C1460" s="6"/>
+      <c r="B1460" s="5"/>
+      <c r="C1460" s="5"/>
     </row>
     <row r="1461" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1461" s="6"/>
-      <c r="C1461" s="6"/>
+      <c r="B1461" s="5"/>
+      <c r="C1461" s="5"/>
     </row>
     <row r="1462" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1462" s="6"/>
-      <c r="C1462" s="6"/>
+      <c r="B1462" s="5"/>
+      <c r="C1462" s="5"/>
     </row>
     <row r="1463" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1463" s="1"/>
@@ -10186,24 +10321,24 @@
       <c r="B1464" s="1"/>
     </row>
     <row r="1465" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1465" s="6"/>
-      <c r="C1465" s="6"/>
+      <c r="B1465" s="5"/>
+      <c r="C1465" s="5"/>
     </row>
     <row r="1466" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1466" s="6"/>
-      <c r="C1466" s="6"/>
+      <c r="B1466" s="5"/>
+      <c r="C1466" s="5"/>
     </row>
     <row r="1467" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1467" s="6"/>
-      <c r="C1467" s="6"/>
+      <c r="B1467" s="5"/>
+      <c r="C1467" s="5"/>
     </row>
     <row r="1468" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1468" s="6"/>
-      <c r="C1468" s="6"/>
+      <c r="B1468" s="5"/>
+      <c r="C1468" s="5"/>
     </row>
     <row r="1469" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1469" s="6"/>
-      <c r="C1469" s="6"/>
+      <c r="B1469" s="5"/>
+      <c r="C1469" s="5"/>
     </row>
     <row r="1470" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1470" s="1"/>
@@ -10212,20 +10347,20 @@
       <c r="B1471" s="1"/>
     </row>
     <row r="1472" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1472" s="6"/>
-      <c r="C1472" s="6"/>
+      <c r="B1472" s="5"/>
+      <c r="C1472" s="5"/>
     </row>
     <row r="1473" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1473" s="6"/>
-      <c r="C1473" s="6"/>
+      <c r="B1473" s="5"/>
+      <c r="C1473" s="5"/>
     </row>
     <row r="1474" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1474" s="6"/>
-      <c r="C1474" s="6"/>
+      <c r="B1474" s="5"/>
+      <c r="C1474" s="5"/>
     </row>
     <row r="1475" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1475" s="6"/>
-      <c r="C1475" s="6"/>
+      <c r="B1475" s="5"/>
+      <c r="C1475" s="5"/>
     </row>
     <row r="1476" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1476" s="1"/>
@@ -10240,20 +10375,20 @@
       <c r="B1479" s="1"/>
     </row>
     <row r="1480" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1480" s="6"/>
-      <c r="C1480" s="6"/>
+      <c r="B1480" s="5"/>
+      <c r="C1480" s="5"/>
     </row>
     <row r="1481" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1481" s="6"/>
-      <c r="C1481" s="6"/>
+      <c r="B1481" s="5"/>
+      <c r="C1481" s="5"/>
     </row>
     <row r="1482" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1482" s="6"/>
-      <c r="C1482" s="6"/>
+      <c r="B1482" s="5"/>
+      <c r="C1482" s="5"/>
     </row>
     <row r="1483" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1483" s="6"/>
-      <c r="C1483" s="6"/>
+      <c r="B1483" s="5"/>
+      <c r="C1483" s="5"/>
     </row>
     <row r="1484" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1484" s="1"/>
@@ -10262,24 +10397,24 @@
       <c r="B1485" s="1"/>
     </row>
     <row r="1486" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1486" s="6"/>
-      <c r="C1486" s="6"/>
+      <c r="B1486" s="5"/>
+      <c r="C1486" s="5"/>
     </row>
     <row r="1487" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1487" s="6"/>
-      <c r="C1487" s="6"/>
+      <c r="B1487" s="5"/>
+      <c r="C1487" s="5"/>
     </row>
     <row r="1488" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1488" s="6"/>
-      <c r="C1488" s="6"/>
+      <c r="B1488" s="5"/>
+      <c r="C1488" s="5"/>
     </row>
     <row r="1489" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1489" s="6"/>
-      <c r="C1489" s="6"/>
+      <c r="B1489" s="5"/>
+      <c r="C1489" s="5"/>
     </row>
     <row r="1490" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1490" s="6"/>
-      <c r="C1490" s="6"/>
+      <c r="B1490" s="5"/>
+      <c r="C1490" s="5"/>
     </row>
     <row r="1491" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1491" s="1"/>
@@ -10288,24 +10423,24 @@
       <c r="B1492" s="1"/>
     </row>
     <row r="1493" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1493" s="6"/>
-      <c r="C1493" s="6"/>
+      <c r="B1493" s="5"/>
+      <c r="C1493" s="5"/>
     </row>
     <row r="1494" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1494" s="6"/>
-      <c r="C1494" s="6"/>
+      <c r="B1494" s="5"/>
+      <c r="C1494" s="5"/>
     </row>
     <row r="1495" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1495" s="6"/>
-      <c r="C1495" s="6"/>
+      <c r="B1495" s="5"/>
+      <c r="C1495" s="5"/>
     </row>
     <row r="1496" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1496" s="6"/>
-      <c r="C1496" s="6"/>
+      <c r="B1496" s="5"/>
+      <c r="C1496" s="5"/>
     </row>
     <row r="1497" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1497" s="6"/>
-      <c r="C1497" s="6"/>
+      <c r="B1497" s="5"/>
+      <c r="C1497" s="5"/>
     </row>
     <row r="1498" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1498" s="1"/>
@@ -10314,24 +10449,24 @@
       <c r="B1499" s="1"/>
     </row>
     <row r="1500" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1500" s="6"/>
-      <c r="C1500" s="6"/>
+      <c r="B1500" s="5"/>
+      <c r="C1500" s="5"/>
     </row>
     <row r="1501" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1501" s="6"/>
-      <c r="C1501" s="6"/>
+      <c r="B1501" s="5"/>
+      <c r="C1501" s="5"/>
     </row>
     <row r="1502" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1502" s="6"/>
-      <c r="C1502" s="6"/>
+      <c r="B1502" s="5"/>
+      <c r="C1502" s="5"/>
     </row>
     <row r="1503" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1503" s="6"/>
-      <c r="C1503" s="6"/>
+      <c r="B1503" s="5"/>
+      <c r="C1503" s="5"/>
     </row>
     <row r="1504" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1504" s="6"/>
-      <c r="C1504" s="6"/>
+      <c r="B1504" s="5"/>
+      <c r="C1504" s="5"/>
     </row>
     <row r="1505" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1505" s="1"/>
@@ -10340,24 +10475,24 @@
       <c r="B1506" s="1"/>
     </row>
     <row r="1507" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1507" s="6"/>
-      <c r="C1507" s="6"/>
+      <c r="B1507" s="5"/>
+      <c r="C1507" s="5"/>
     </row>
     <row r="1508" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1508" s="6"/>
-      <c r="C1508" s="6"/>
+      <c r="B1508" s="5"/>
+      <c r="C1508" s="5"/>
     </row>
     <row r="1509" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1509" s="6"/>
-      <c r="C1509" s="6"/>
+      <c r="B1509" s="5"/>
+      <c r="C1509" s="5"/>
     </row>
     <row r="1510" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1510" s="6"/>
-      <c r="C1510" s="6"/>
+      <c r="B1510" s="5"/>
+      <c r="C1510" s="5"/>
     </row>
     <row r="1511" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1511" s="6"/>
-      <c r="C1511" s="6"/>
+      <c r="B1511" s="5"/>
+      <c r="C1511" s="5"/>
     </row>
     <row r="1512" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1512" s="1"/>
@@ -10366,23 +10501,23 @@
       <c r="B1513" s="1"/>
     </row>
     <row r="1514" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1514" s="6"/>
-      <c r="C1514" s="6"/>
+      <c r="B1514" s="5"/>
+      <c r="C1514" s="5"/>
     </row>
     <row r="1515" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1515" s="1"/>
     </row>
     <row r="1516" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1516" s="6"/>
-      <c r="C1516" s="6"/>
+      <c r="B1516" s="5"/>
+      <c r="C1516" s="5"/>
     </row>
     <row r="1517" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1517" s="6"/>
-      <c r="C1517" s="6"/>
+      <c r="B1517" s="5"/>
+      <c r="C1517" s="5"/>
     </row>
     <row r="1518" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1518" s="6"/>
-      <c r="C1518" s="6"/>
+      <c r="B1518" s="5"/>
+      <c r="C1518" s="5"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/tcmb_kur_verileri.xlsx
+++ b/tcmb_kur_verileri.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="534">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="538">
   <si>
     <t xml:space="preserve">Tarih</t>
   </si>
@@ -1622,6 +1622,18 @@
   </si>
   <si>
     <t xml:space="preserve">15-06-2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16-06-2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17-06-2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18-06-2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19-06-2026</t>
   </si>
 </sst>
 </file>
@@ -6745,163 +6757,187 @@
       </c>
     </row>
     <row r="519" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A519" s="0" t="s">
+      <c r="A519" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="B519" s="0" t="n">
+      <c r="B519" s="1" t="n">
         <v>45.8248</v>
       </c>
-      <c r="C519" s="0" t="n">
+      <c r="C519" s="1" t="n">
         <v>53.4042</v>
       </c>
     </row>
     <row r="520" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A520" s="0" t="s">
+      <c r="A520" s="1" t="s">
         <v>521</v>
       </c>
-      <c r="B520" s="0" t="n">
+      <c r="B520" s="1" t="n">
         <v>45.8402</v>
       </c>
-      <c r="C520" s="0" t="n">
+      <c r="C520" s="1" t="n">
         <v>53.3878</v>
       </c>
     </row>
     <row r="521" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A521" s="0" t="s">
+      <c r="A521" s="1" t="s">
         <v>522</v>
       </c>
-      <c r="B521" s="0" t="n">
+      <c r="B521" s="1" t="n">
         <v>45.8696</v>
       </c>
-      <c r="C521" s="0" t="n">
+      <c r="C521" s="1" t="n">
         <v>53.2768</v>
       </c>
     </row>
     <row r="522" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A522" s="0" t="s">
+      <c r="A522" s="1" t="s">
         <v>523</v>
       </c>
-      <c r="B522" s="0" t="n">
+      <c r="B522" s="1" t="n">
         <v>45.8873</v>
       </c>
-      <c r="C522" s="0" t="n">
+      <c r="C522" s="1" t="n">
         <v>53.3268</v>
       </c>
     </row>
     <row r="523" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A523" s="0" t="s">
+      <c r="A523" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="B523" s="0"/>
-      <c r="C523" s="0"/>
+      <c r="B523" s="1"/>
     </row>
     <row r="524" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A524" s="0" t="s">
+      <c r="A524" s="1" t="s">
         <v>525</v>
       </c>
-      <c r="B524" s="0"/>
-      <c r="C524" s="0"/>
+      <c r="B524" s="1"/>
     </row>
     <row r="525" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A525" s="0" t="s">
+      <c r="A525" s="1" t="s">
         <v>526</v>
       </c>
-      <c r="B525" s="0" t="n">
+      <c r="B525" s="1" t="n">
         <v>45.9084</v>
       </c>
-      <c r="C525" s="0" t="n">
+      <c r="C525" s="1" t="n">
         <v>53.4156</v>
       </c>
     </row>
     <row r="526" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A526" s="0" t="s">
+      <c r="A526" s="1" t="s">
         <v>527</v>
       </c>
-      <c r="B526" s="0" t="n">
+      <c r="B526" s="1" t="n">
         <v>46.0144</v>
       </c>
-      <c r="C526" s="0" t="n">
+      <c r="C526" s="1" t="n">
         <v>53.0044</v>
       </c>
     </row>
     <row r="527" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A527" s="0" t="s">
+      <c r="A527" s="1" t="s">
         <v>528</v>
       </c>
-      <c r="B527" s="0" t="n">
+      <c r="B527" s="1" t="n">
         <v>46.0328</v>
       </c>
-      <c r="C527" s="0" t="n">
+      <c r="C527" s="1" t="n">
         <v>53.194</v>
       </c>
     </row>
     <row r="528" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A528" s="0" t="s">
+      <c r="A528" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="B528" s="0" t="n">
+      <c r="B528" s="1" t="n">
         <v>46.0491</v>
       </c>
-      <c r="C528" s="0" t="n">
+      <c r="C528" s="1" t="n">
         <v>53.1886</v>
       </c>
     </row>
     <row r="529" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A529" s="0" t="s">
+      <c r="A529" s="1" t="s">
         <v>530</v>
       </c>
-      <c r="B529" s="0" t="n">
+      <c r="B529" s="1" t="n">
         <v>46.0669</v>
       </c>
-      <c r="C529" s="0" t="n">
+      <c r="C529" s="1" t="n">
         <v>53.1485</v>
       </c>
     </row>
     <row r="530" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A530" s="0" t="s">
+      <c r="A530" s="1" t="s">
         <v>531</v>
       </c>
-      <c r="B530" s="0"/>
-      <c r="C530" s="0"/>
+      <c r="B530" s="1"/>
     </row>
     <row r="531" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A531" s="0" t="s">
+      <c r="A531" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="B531" s="0"/>
-      <c r="C531" s="0"/>
+      <c r="B531" s="1"/>
     </row>
     <row r="532" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A532" s="0" t="s">
+      <c r="A532" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="B532" s="0" t="n">
+      <c r="B532" s="1" t="n">
         <v>46.0857</v>
       </c>
-      <c r="C532" s="0" t="n">
+      <c r="C532" s="1" t="n">
         <v>53.3419</v>
       </c>
     </row>
     <row r="533" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A533" s="0"/>
-      <c r="B533" s="0"/>
-      <c r="C533" s="0"/>
+      <c r="A533" s="0" t="s">
+        <v>534</v>
+      </c>
+      <c r="B533" s="0" t="n">
+        <v>46.1932</v>
+      </c>
+      <c r="C533" s="0" t="n">
+        <v>53.6157</v>
+      </c>
     </row>
     <row r="534" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B534" s="5"/>
-      <c r="C534" s="5"/>
+      <c r="A534" s="0" t="s">
+        <v>535</v>
+      </c>
+      <c r="B534" s="0" t="n">
+        <v>46.2125</v>
+      </c>
+      <c r="C534" s="0" t="n">
+        <v>53.6077</v>
+      </c>
     </row>
     <row r="535" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B535" s="5"/>
-      <c r="C535" s="5"/>
+      <c r="A535" s="0" t="s">
+        <v>536</v>
+      </c>
+      <c r="B535" s="0" t="n">
+        <v>46.2307</v>
+      </c>
+      <c r="C535" s="0" t="n">
+        <v>53.6365</v>
+      </c>
     </row>
     <row r="536" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B536" s="5"/>
-      <c r="C536" s="5"/>
+      <c r="A536" s="0" t="s">
+        <v>537</v>
+      </c>
+      <c r="B536" s="0" t="n">
+        <v>46.246</v>
+      </c>
+      <c r="C536" s="0" t="n">
+        <v>53.1143</v>
+      </c>
     </row>
     <row r="537" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B537" s="5"/>
-      <c r="C537" s="5"/>
+      <c r="A537" s="0"/>
+      <c r="B537" s="0"/>
+      <c r="C537" s="0"/>
     </row>
     <row r="538" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B538" s="5"/>
